--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10459705-71F9-463B-A5A6-AFBCC997D1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77A7FD1-1250-4450-9EDF-C8E6BE721DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2240" yWindow="2240" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29940" yWindow="5970" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -281,9 +281,6 @@
     <t>废料堆</t>
   </si>
   <si>
-    <t>硬质纤维</t>
-  </si>
-  <si>
     <t>废金属</t>
   </si>
   <si>
@@ -405,6 +402,10 @@
   </si>
   <si>
     <t>燃烧期间的氧烛会不断产生氧气,可以作为探索时的氧气来源,当氧烛快要燃烧殆尽时,记得及时返回。</t>
+  </si>
+  <si>
+    <t>韧性胶管</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1808,10 +1809,10 @@
     </row>
     <row r="15" spans="1:27">
       <c r="A15" s="6" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="14" t="s">
@@ -1874,10 +1875,10 @@
     </row>
     <row r="16" spans="1:27" ht="42">
       <c r="A16" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="14" t="s">
@@ -1940,14 +1941,14 @@
     </row>
     <row r="17" spans="1:24" ht="28">
       <c r="A17" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E17" s="4">
         <v>2</v>
@@ -2006,14 +2007,14 @@
     </row>
     <row r="18" spans="1:24" ht="70">
       <c r="A18" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" s="4">
         <v>3</v>
@@ -2072,14 +2073,14 @@
     </row>
     <row r="19" spans="1:24" ht="42">
       <c r="A19" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19" s="4">
         <v>4</v>
@@ -2138,10 +2139,10 @@
     </row>
     <row r="20" spans="1:24">
       <c r="A20" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="14" t="s">
@@ -2204,14 +2205,14 @@
     </row>
     <row r="21" spans="1:24" ht="70">
       <c r="A21" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E21" s="4">
         <v>6</v>
@@ -2270,10 +2271,10 @@
     </row>
     <row r="22" spans="1:24" ht="42">
       <c r="A22" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="14" t="s">
@@ -2336,16 +2337,16 @@
     </row>
     <row r="23" spans="1:24" ht="98">
       <c r="A23" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E23" s="8">
         <v>0</v>
@@ -2404,16 +2405,16 @@
     </row>
     <row r="24" spans="1:24" ht="98">
       <c r="A24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E24" s="8">
         <v>1</v>
@@ -2472,16 +2473,16 @@
     </row>
     <row r="25" spans="1:24" ht="56">
       <c r="A25" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E25" s="8">
         <v>2</v>
@@ -2540,16 +2541,16 @@
     </row>
     <row r="26" spans="1:24" ht="56">
       <c r="A26" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E26" s="8">
         <v>3</v>
@@ -2608,16 +2609,16 @@
     </row>
     <row r="27" spans="1:24" ht="42">
       <c r="A27" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>26</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E27" s="8">
         <v>4</v>
@@ -2676,16 +2677,16 @@
     </row>
     <row r="28" spans="1:24" ht="42">
       <c r="A28" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E28" s="8">
         <v>5</v>
@@ -2744,10 +2745,10 @@
     </row>
     <row r="29" spans="1:24">
       <c r="A29" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C29" s="6"/>
       <c r="E29" s="4">
@@ -2809,10 +2810,10 @@
     </row>
     <row r="30" spans="1:24" ht="42">
       <c r="A30" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="14" t="s">
@@ -2877,10 +2878,10 @@
     </row>
     <row r="31" spans="1:24" ht="56">
       <c r="A31" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="14" t="s">
@@ -2943,10 +2944,10 @@
     </row>
     <row r="32" spans="1:24" ht="56">
       <c r="A32" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="7" t="s">
@@ -3011,10 +3012,10 @@
     </row>
     <row r="33" spans="1:25">
       <c r="A33" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="6"/>
       <c r="E33" s="8">
@@ -3076,10 +3077,10 @@
     </row>
     <row r="34" spans="1:25" ht="28">
       <c r="A34" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="14" t="s">
@@ -3144,10 +3145,10 @@
     </row>
     <row r="35" spans="1:25" ht="84">
       <c r="A35" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="14" t="s">
@@ -3215,13 +3216,13 @@
         <v>39</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>40</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E36" s="4">
         <v>0</v>
@@ -3284,13 +3285,13 @@
     <row r="37" spans="1:25" ht="42">
       <c r="A37" s="7"/>
       <c r="B37" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>42</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E37" s="4">
         <v>1</v>
@@ -3352,14 +3353,14 @@
     </row>
     <row r="38" spans="1:25" ht="70">
       <c r="A38" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E38" s="4">
         <v>2</v>
@@ -3418,13 +3419,13 @@
     </row>
     <row r="39" spans="1:25" ht="70">
       <c r="A39" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>122</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>123</v>
       </c>
       <c r="E39" s="8">
         <v>1</v>
@@ -3483,14 +3484,14 @@
     </row>
     <row r="40" spans="1:25" ht="42">
       <c r="A40" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E40" s="8">
         <v>0</v>
@@ -3549,14 +3550,14 @@
     </row>
     <row r="41" spans="1:25" ht="42">
       <c r="A41" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E41" s="8">
         <v>2</v>
@@ -3615,7 +3616,7 @@
     </row>
     <row r="42" spans="1:25" ht="56">
       <c r="A42" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>44</v>
@@ -3624,7 +3625,7 @@
         <v>45</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E42" s="8">
         <v>3</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77A7FD1-1250-4450-9EDF-C8E6BE721DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267CA9F0-EE30-44C8-B09F-34DBE7A8B139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29940" yWindow="5970" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="130">
   <si>
     <t>ExtraInfo</t>
   </si>
@@ -2654,8 +2654,8 @@
       <c r="P27" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="13" t="s">
-        <v>7</v>
+      <c r="Q27" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="R27" s="4">
         <v>3600</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A298AAFC-2B43-471F-BD87-2A685597CCA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBEB0AA-4686-4B49-9502-FB8C5309F5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4370" yWindow="2050" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2238" uniqueCount="225">
   <si>
     <t>ExtraInfo</t>
   </si>
@@ -1248,31 +1248,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AO77"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="28.58203125" style="25" customWidth="1"/>
-    <col min="2" max="3" width="11.4140625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="28.08203125" style="25" customWidth="1"/>
-    <col min="5" max="5" width="15.58203125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="7.83203125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10.9140625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="13.08203125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="28.625" style="25" customWidth="1"/>
+    <col min="2" max="3" width="11.375" style="25" customWidth="1"/>
+    <col min="4" max="4" width="28.125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.375" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="6.875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="7.875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="10.875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="13.125" style="4" customWidth="1"/>
     <col min="13" max="22" width="19" style="4" customWidth="1"/>
-    <col min="23" max="23" width="8.58203125" style="4" customWidth="1"/>
-    <col min="24" max="24" width="10.1640625" style="4" customWidth="1"/>
+    <col min="23" max="23" width="8.625" style="4" customWidth="1"/>
+    <col min="24" max="24" width="10.125" style="4" customWidth="1"/>
     <col min="25" max="26" width="12.5" style="4" customWidth="1"/>
-    <col min="27" max="27" width="8.58203125" style="4"/>
+    <col min="27" max="27" width="8.625" style="4"/>
     <col min="28" max="28" width="12.25" style="4" customWidth="1"/>
-    <col min="29" max="36" width="8.58203125" style="14"/>
-    <col min="37" max="37" width="11.6640625" style="14" customWidth="1"/>
-    <col min="38" max="38" width="9.1640625" style="14" customWidth="1"/>
+    <col min="29" max="36" width="8.625" style="14"/>
+    <col min="37" max="37" width="11.625" style="14" customWidth="1"/>
+    <col min="38" max="38" width="9.125" style="14" customWidth="1"/>
     <col min="39" max="39" width="12" style="14" customWidth="1"/>
     <col min="40" max="40" width="13" style="14" customWidth="1"/>
-    <col min="41" max="41" width="8.58203125" style="14"/>
+    <col min="41" max="41" width="8.625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" s="46" customFormat="1" ht="15.75" customHeight="1">
@@ -1850,7 +1850,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="84">
+    <row r="6" spans="1:41" ht="85.5">
       <c r="A6" s="15" t="s">
         <v>39</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:41" ht="84">
+    <row r="7" spans="1:41" ht="85.5">
       <c r="A7" s="15" t="s">
         <v>44</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="28">
+    <row r="8" spans="1:41" ht="28.5">
       <c r="A8" s="17" t="s">
         <v>45</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="28">
+    <row r="9" spans="1:41" ht="28.5">
       <c r="A9" s="17" t="s">
         <v>50</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="42">
+    <row r="12" spans="1:41" ht="42.75">
       <c r="A12" s="16" t="s">
         <v>170</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="42">
+    <row r="13" spans="1:41" ht="42.75">
       <c r="A13" s="16" t="s">
         <v>172</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="28">
+    <row r="14" spans="1:41" ht="28.5">
       <c r="A14" s="16" t="s">
         <v>174</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" spans="1:41" ht="42">
+    <row r="15" spans="1:41" ht="42.75">
       <c r="A15" s="16" t="s">
         <v>175</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="17" spans="1:40" ht="28">
+    <row r="17" spans="1:40" ht="28.5">
       <c r="A17" s="16" t="s">
         <v>178</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="18" spans="1:40" ht="28">
+    <row r="18" spans="1:40" ht="28.5">
       <c r="A18" s="16" t="s">
         <v>180</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="19" spans="1:40" ht="42">
+    <row r="19" spans="1:40" ht="42.75">
       <c r="A19" s="16" t="s">
         <v>181</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="20" spans="1:40" ht="126">
+    <row r="20" spans="1:40" ht="128.25">
       <c r="A20" s="26" t="s">
         <v>66</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:40" ht="84">
+    <row r="21" spans="1:40" ht="85.5">
       <c r="A21" s="26" t="s">
         <v>68</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="22" spans="1:40" ht="70">
+    <row r="22" spans="1:40" ht="85.5">
       <c r="A22" s="26" t="s">
         <v>70</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="23" spans="1:40" ht="28">
+    <row r="23" spans="1:40" ht="28.5">
       <c r="A23" s="18" t="s">
         <v>72</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="24" spans="1:40" ht="70">
+    <row r="24" spans="1:40" ht="71.25">
       <c r="A24" s="18" t="s">
         <v>74</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:40" ht="70">
+    <row r="25" spans="1:40" ht="71.25">
       <c r="A25" s="18" t="s">
         <v>76</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="26" spans="1:40" ht="28">
+    <row r="26" spans="1:40" ht="42.75">
       <c r="A26" s="18" t="s">
         <v>78</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="27" spans="1:40" ht="42">
+    <row r="27" spans="1:40" ht="42.75">
       <c r="A27" s="18" t="s">
         <v>80</v>
       </c>
@@ -4305,7 +4305,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="28" spans="1:40" ht="42">
+    <row r="28" spans="1:40" ht="42.75">
       <c r="A28" s="18" t="s">
         <v>82</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="29" spans="1:40" ht="28">
+    <row r="29" spans="1:40" ht="42.75">
       <c r="A29" s="18" t="s">
         <v>84</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="30" spans="1:40" ht="42">
+    <row r="30" spans="1:40" ht="42.75">
       <c r="A30" s="18" t="s">
         <v>86</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="31" spans="1:40" ht="70">
+    <row r="31" spans="1:40" ht="71.25">
       <c r="A31" s="18" t="s">
         <v>88</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="32" spans="1:40" ht="28">
+    <row r="32" spans="1:40" ht="42.75">
       <c r="A32" s="16" t="s">
         <v>182</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="33" spans="1:40" ht="56">
+    <row r="33" spans="1:40" ht="71.25">
       <c r="A33" s="27" t="s">
         <v>92</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="34" spans="1:40" ht="42">
+    <row r="34" spans="1:40" ht="42.75">
       <c r="A34" s="27" t="s">
         <v>94</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="35" spans="1:40" ht="28">
+    <row r="35" spans="1:40" ht="28.5">
       <c r="A35" s="27" t="s">
         <v>96</v>
       </c>
@@ -5306,7 +5306,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="1:40" ht="42">
+    <row r="37" spans="1:40" ht="42.75">
       <c r="A37" s="16" t="s">
         <v>183</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="38" spans="1:40" ht="28">
+    <row r="38" spans="1:40" ht="28.5">
       <c r="A38" s="16" t="s">
         <v>184</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="39" spans="1:40" ht="70">
+    <row r="39" spans="1:40" ht="71.25">
       <c r="A39" s="16" t="s">
         <v>186</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="1:40" ht="42">
+    <row r="40" spans="1:40" ht="42.75">
       <c r="A40" s="16" t="s">
         <v>188</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="42" spans="1:40" ht="70">
+    <row r="42" spans="1:40" ht="71.25">
       <c r="A42" s="16" t="s">
         <v>191</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="43" spans="1:40" ht="42">
+    <row r="43" spans="1:40" ht="42.75">
       <c r="A43" s="16" t="s">
         <v>193</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="45" spans="1:40" ht="28">
+    <row r="45" spans="1:40" ht="28.5">
       <c r="A45" s="17" t="s">
         <v>106</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="47" spans="1:40" ht="28">
+    <row r="47" spans="1:40" ht="28.5">
       <c r="A47" s="17" t="s">
         <v>110</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="48" spans="1:40" ht="28">
+    <row r="48" spans="1:40" ht="28.5">
       <c r="A48" s="17" t="s">
         <v>112</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="49" spans="1:40" ht="98">
+    <row r="49" spans="1:40" ht="99.75">
       <c r="A49" s="16" t="s">
         <v>194</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="50" spans="1:40" ht="98">
+    <row r="50" spans="1:40" ht="99.75">
       <c r="A50" s="16" t="s">
         <v>196</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="51" spans="1:40" ht="56">
+    <row r="51" spans="1:40" ht="57">
       <c r="A51" s="16" t="s">
         <v>197</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="52" spans="1:40" ht="56">
+    <row r="52" spans="1:40" ht="57">
       <c r="A52" s="16" t="s">
         <v>199</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:40" ht="42">
+    <row r="53" spans="1:40" ht="57">
       <c r="A53" s="25" t="s">
         <v>200</v>
       </c>
@@ -7137,8 +7137,8 @@
       <c r="P53" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="Q53" s="13" t="s">
-        <v>24</v>
+      <c r="Q53" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="R53" s="4">
         <v>3600</v>
@@ -7203,7 +7203,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:40" ht="42">
+    <row r="54" spans="1:40" ht="57">
       <c r="A54" s="25" t="s">
         <v>202</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="55" spans="1:40" ht="28">
+    <row r="55" spans="1:40" ht="28.5">
       <c r="A55" s="16" t="s">
         <v>203</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="56" spans="1:40" ht="42">
+    <row r="56" spans="1:40" ht="57">
       <c r="A56" s="16" t="s">
         <v>204</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="57" spans="1:40" ht="56">
+    <row r="57" spans="1:40" ht="57">
       <c r="A57" s="16" t="s">
         <v>205</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="58" spans="1:40" ht="56">
+    <row r="58" spans="1:40" ht="57">
       <c r="A58" s="16" t="s">
         <v>206</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:40" ht="28">
+    <row r="59" spans="1:40" ht="28.5">
       <c r="A59" s="16" t="s">
         <v>207</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="60" spans="1:40" ht="28">
+    <row r="60" spans="1:40" ht="42.75">
       <c r="A60" s="16" t="s">
         <v>208</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="61" spans="1:40" ht="84">
+    <row r="61" spans="1:40" ht="99.75">
       <c r="A61" s="16" t="s">
         <v>209</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="62" spans="1:40" ht="42">
+    <row r="62" spans="1:40" ht="42.75">
       <c r="A62" s="7" t="s">
         <v>130</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="63" spans="1:40" ht="42">
+    <row r="63" spans="1:40" ht="42.75">
       <c r="A63" s="7"/>
       <c r="B63" s="16" t="s">
         <v>212</v>
@@ -8337,7 +8337,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="64" spans="1:40" ht="70">
+    <row r="64" spans="1:40" ht="71.25">
       <c r="A64" s="16" t="s">
         <v>214</v>
       </c>
@@ -8448,7 +8448,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="65" spans="1:40" ht="56">
+    <row r="65" spans="1:40" ht="57">
       <c r="A65" s="27" t="s">
         <v>134</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="67" spans="1:40" ht="56">
+    <row r="67" spans="1:40" ht="57">
       <c r="A67" s="17" t="s">
         <v>138</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="68" spans="1:40" ht="70">
+    <row r="68" spans="1:40" ht="71.25">
       <c r="A68" s="27" t="s">
         <v>140</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="69" spans="1:40" ht="42">
+    <row r="69" spans="1:40" ht="42.75">
       <c r="A69" s="17" t="s">
         <v>142</v>
       </c>
@@ -8945,7 +8945,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="70" spans="1:40" ht="42">
+    <row r="70" spans="1:40" ht="42.75">
       <c r="A70" s="17"/>
       <c r="B70" s="17" t="s">
         <v>142</v>
@@ -9056,7 +9056,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="71" spans="1:40" ht="70">
+    <row r="71" spans="1:40" ht="71.25">
       <c r="A71" s="25" t="s">
         <v>216</v>
       </c>
@@ -9166,7 +9166,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="1:40" ht="42">
+    <row r="72" spans="1:40" ht="42.75">
       <c r="A72" s="16" t="s">
         <v>218</v>
       </c>
@@ -9277,7 +9277,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="73" spans="1:40" ht="42">
+    <row r="73" spans="1:40" ht="42.75">
       <c r="A73" s="16" t="s">
         <v>220</v>
       </c>
@@ -9388,7 +9388,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="74" spans="1:40" ht="56">
+    <row r="74" spans="1:40" ht="57">
       <c r="A74" s="16" t="s">
         <v>222</v>
       </c>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBEB0AA-4686-4B49-9502-FB8C5309F5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0F896C-41F7-43F7-BC3B-C003746AFDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1248,31 +1248,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AO77"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="28.625" style="25" customWidth="1"/>
-    <col min="2" max="3" width="11.375" style="25" customWidth="1"/>
-    <col min="4" max="4" width="28.125" style="25" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10.375" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="6.875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="7.875" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10.875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="13.125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="28.58203125" style="25" customWidth="1"/>
+    <col min="2" max="3" width="11.33203125" style="25" customWidth="1"/>
+    <col min="4" max="4" width="28.08203125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="15.58203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.08203125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="7.83203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="13.08203125" style="4" customWidth="1"/>
     <col min="13" max="22" width="19" style="4" customWidth="1"/>
-    <col min="23" max="23" width="8.625" style="4" customWidth="1"/>
-    <col min="24" max="24" width="10.125" style="4" customWidth="1"/>
+    <col min="23" max="23" width="8.58203125" style="4" customWidth="1"/>
+    <col min="24" max="24" width="10.08203125" style="4" customWidth="1"/>
     <col min="25" max="26" width="12.5" style="4" customWidth="1"/>
-    <col min="27" max="27" width="8.625" style="4"/>
+    <col min="27" max="27" width="8.58203125" style="4"/>
     <col min="28" max="28" width="12.25" style="4" customWidth="1"/>
-    <col min="29" max="36" width="8.625" style="14"/>
-    <col min="37" max="37" width="11.625" style="14" customWidth="1"/>
-    <col min="38" max="38" width="9.125" style="14" customWidth="1"/>
+    <col min="29" max="36" width="8.58203125" style="14"/>
+    <col min="37" max="37" width="11.58203125" style="14" customWidth="1"/>
+    <col min="38" max="38" width="9.08203125" style="14" customWidth="1"/>
     <col min="39" max="39" width="12" style="14" customWidth="1"/>
     <col min="40" max="40" width="13" style="14" customWidth="1"/>
-    <col min="41" max="41" width="8.625" style="14"/>
+    <col min="41" max="41" width="8.58203125" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" s="46" customFormat="1" ht="15.75" customHeight="1">
@@ -1850,7 +1850,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="85.5">
+    <row r="6" spans="1:41" ht="84">
       <c r="A6" s="15" t="s">
         <v>39</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:41" ht="85.5">
+    <row r="7" spans="1:41" ht="84">
       <c r="A7" s="15" t="s">
         <v>44</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="28.5">
+    <row r="8" spans="1:41" ht="28">
       <c r="A8" s="17" t="s">
         <v>45</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="28.5">
+    <row r="9" spans="1:41" ht="28">
       <c r="A9" s="17" t="s">
         <v>50</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>58</v>
       </c>
       <c r="E11" s="24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>23</v>
@@ -2528,7 +2528,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="42.75">
+    <row r="12" spans="1:41" ht="42">
       <c r="A12" s="16" t="s">
         <v>170</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="42.75">
+    <row r="13" spans="1:41" ht="42">
       <c r="A13" s="16" t="s">
         <v>172</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="28.5">
+    <row r="14" spans="1:41" ht="28">
       <c r="A14" s="16" t="s">
         <v>174</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" spans="1:41" ht="42.75">
+    <row r="15" spans="1:41" ht="42">
       <c r="A15" s="16" t="s">
         <v>175</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="17" spans="1:40" ht="28.5">
+    <row r="17" spans="1:40" ht="28">
       <c r="A17" s="16" t="s">
         <v>178</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="18" spans="1:40" ht="28.5">
+    <row r="18" spans="1:40" ht="28">
       <c r="A18" s="16" t="s">
         <v>180</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="19" spans="1:40" ht="42.75">
+    <row r="19" spans="1:40" ht="42">
       <c r="A19" s="16" t="s">
         <v>181</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="20" spans="1:40" ht="128.25">
+    <row r="20" spans="1:40" ht="126">
       <c r="A20" s="26" t="s">
         <v>66</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:40" ht="85.5">
+    <row r="21" spans="1:40" ht="84">
       <c r="A21" s="26" t="s">
         <v>68</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="22" spans="1:40" ht="85.5">
+    <row r="22" spans="1:40" ht="70">
       <c r="A22" s="26" t="s">
         <v>70</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="23" spans="1:40" ht="28.5">
+    <row r="23" spans="1:40" ht="28">
       <c r="A23" s="18" t="s">
         <v>72</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="24" spans="1:40" ht="71.25">
+    <row r="24" spans="1:40" ht="70">
       <c r="A24" s="18" t="s">
         <v>74</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:40" ht="71.25">
+    <row r="25" spans="1:40" ht="70">
       <c r="A25" s="18" t="s">
         <v>76</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="26" spans="1:40" ht="42.75">
+    <row r="26" spans="1:40" ht="28">
       <c r="A26" s="18" t="s">
         <v>78</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="27" spans="1:40" ht="42.75">
+    <row r="27" spans="1:40" ht="42">
       <c r="A27" s="18" t="s">
         <v>80</v>
       </c>
@@ -4305,7 +4305,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="28" spans="1:40" ht="42.75">
+    <row r="28" spans="1:40" ht="42">
       <c r="A28" s="18" t="s">
         <v>82</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="29" spans="1:40" ht="42.75">
+    <row r="29" spans="1:40" ht="28">
       <c r="A29" s="18" t="s">
         <v>84</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="30" spans="1:40" ht="42.75">
+    <row r="30" spans="1:40" ht="42">
       <c r="A30" s="18" t="s">
         <v>86</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="31" spans="1:40" ht="71.25">
+    <row r="31" spans="1:40" ht="70">
       <c r="A31" s="18" t="s">
         <v>88</v>
       </c>
@@ -4751,7 +4751,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="32" spans="1:40" ht="42.75">
+    <row r="32" spans="1:40" ht="28">
       <c r="A32" s="16" t="s">
         <v>182</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="33" spans="1:40" ht="71.25">
+    <row r="33" spans="1:40" ht="56">
       <c r="A33" s="27" t="s">
         <v>92</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="34" spans="1:40" ht="42.75">
+    <row r="34" spans="1:40" ht="42">
       <c r="A34" s="27" t="s">
         <v>94</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="35" spans="1:40" ht="28.5">
+    <row r="35" spans="1:40" ht="28">
       <c r="A35" s="27" t="s">
         <v>96</v>
       </c>
@@ -5306,7 +5306,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="1:40" ht="42.75">
+    <row r="37" spans="1:40" ht="42">
       <c r="A37" s="16" t="s">
         <v>183</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="38" spans="1:40" ht="28.5">
+    <row r="38" spans="1:40" ht="28">
       <c r="A38" s="16" t="s">
         <v>184</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="39" spans="1:40" ht="71.25">
+    <row r="39" spans="1:40" ht="70">
       <c r="A39" s="16" t="s">
         <v>186</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="1:40" ht="42.75">
+    <row r="40" spans="1:40" ht="42">
       <c r="A40" s="16" t="s">
         <v>188</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="42" spans="1:40" ht="71.25">
+    <row r="42" spans="1:40" ht="70">
       <c r="A42" s="16" t="s">
         <v>191</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="43" spans="1:40" ht="42.75">
+    <row r="43" spans="1:40" ht="42">
       <c r="A43" s="16" t="s">
         <v>193</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="45" spans="1:40" ht="28.5">
+    <row r="45" spans="1:40" ht="28">
       <c r="A45" s="17" t="s">
         <v>106</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="47" spans="1:40" ht="28.5">
+    <row r="47" spans="1:40" ht="28">
       <c r="A47" s="17" t="s">
         <v>110</v>
       </c>
@@ -6527,7 +6527,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="48" spans="1:40" ht="28.5">
+    <row r="48" spans="1:40" ht="28">
       <c r="A48" s="17" t="s">
         <v>112</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="49" spans="1:40" ht="99.75">
+    <row r="49" spans="1:40" ht="98">
       <c r="A49" s="16" t="s">
         <v>194</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="50" spans="1:40" ht="99.75">
+    <row r="50" spans="1:40" ht="98">
       <c r="A50" s="16" t="s">
         <v>196</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="51" spans="1:40" ht="57">
+    <row r="51" spans="1:40" ht="56">
       <c r="A51" s="16" t="s">
         <v>197</v>
       </c>
@@ -6977,7 +6977,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="52" spans="1:40" ht="57">
+    <row r="52" spans="1:40" ht="56">
       <c r="A52" s="16" t="s">
         <v>199</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:40" ht="57">
+    <row r="53" spans="1:40" ht="42">
       <c r="A53" s="25" t="s">
         <v>200</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:40" ht="57">
+    <row r="54" spans="1:40" ht="42">
       <c r="A54" s="25" t="s">
         <v>202</v>
       </c>
@@ -7316,7 +7316,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="55" spans="1:40" ht="28.5">
+    <row r="55" spans="1:40" ht="28">
       <c r="A55" s="16" t="s">
         <v>203</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="56" spans="1:40" ht="57">
+    <row r="56" spans="1:40" ht="42">
       <c r="A56" s="16" t="s">
         <v>204</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="57" spans="1:40" ht="57">
+    <row r="57" spans="1:40" ht="56">
       <c r="A57" s="16" t="s">
         <v>205</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="58" spans="1:40" ht="57">
+    <row r="58" spans="1:40" ht="56">
       <c r="A58" s="16" t="s">
         <v>206</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:40" ht="28.5">
+    <row r="59" spans="1:40" ht="28">
       <c r="A59" s="16" t="s">
         <v>207</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="60" spans="1:40" ht="42.75">
+    <row r="60" spans="1:40" ht="28">
       <c r="A60" s="16" t="s">
         <v>208</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="61" spans="1:40" ht="99.75">
+    <row r="61" spans="1:40" ht="84">
       <c r="A61" s="16" t="s">
         <v>209</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="62" spans="1:40" ht="42.75">
+    <row r="62" spans="1:40" ht="42">
       <c r="A62" s="7" t="s">
         <v>130</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="63" spans="1:40" ht="42.75">
+    <row r="63" spans="1:40" ht="42">
       <c r="A63" s="7"/>
       <c r="B63" s="16" t="s">
         <v>212</v>
@@ -8337,7 +8337,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="64" spans="1:40" ht="71.25">
+    <row r="64" spans="1:40" ht="70">
       <c r="A64" s="16" t="s">
         <v>214</v>
       </c>
@@ -8448,7 +8448,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="65" spans="1:40" ht="57">
+    <row r="65" spans="1:40" ht="56">
       <c r="A65" s="27" t="s">
         <v>134</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="67" spans="1:40" ht="57">
+    <row r="67" spans="1:40" ht="56">
       <c r="A67" s="17" t="s">
         <v>138</v>
       </c>
@@ -8718,7 +8718,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="68" spans="1:40" ht="71.25">
+    <row r="68" spans="1:40" ht="70">
       <c r="A68" s="27" t="s">
         <v>140</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="69" spans="1:40" ht="42.75">
+    <row r="69" spans="1:40" ht="42">
       <c r="A69" s="17" t="s">
         <v>142</v>
       </c>
@@ -8945,7 +8945,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="70" spans="1:40" ht="42.75">
+    <row r="70" spans="1:40" ht="42">
       <c r="A70" s="17"/>
       <c r="B70" s="17" t="s">
         <v>142</v>
@@ -9056,7 +9056,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="71" spans="1:40" ht="71.25">
+    <row r="71" spans="1:40" ht="70">
       <c r="A71" s="25" t="s">
         <v>216</v>
       </c>
@@ -9166,7 +9166,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="1:40" ht="42.75">
+    <row r="72" spans="1:40" ht="42">
       <c r="A72" s="16" t="s">
         <v>218</v>
       </c>
@@ -9277,7 +9277,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="73" spans="1:40" ht="42.75">
+    <row r="73" spans="1:40" ht="42">
       <c r="A73" s="16" t="s">
         <v>220</v>
       </c>
@@ -9388,7 +9388,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="74" spans="1:40" ht="57">
+    <row r="74" spans="1:40" ht="56">
       <c r="A74" s="16" t="s">
         <v>222</v>
       </c>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE789DA5-C9BB-480D-98AB-F5C13FBB106B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC7BA84-E67E-4C49-A4AE-053DD43FCBD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4398" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4397" uniqueCount="319">
   <si>
     <t>ExtraInfo</t>
   </si>
@@ -587,18 +587,12 @@
     <t>矿石释氧机</t>
   </si>
   <si>
-    <t>开启</t>
-  </si>
-  <si>
     <t>Construction</t>
   </si>
   <si>
     <t>电池*1+废金属*1+白爆矿*1</t>
   </si>
   <si>
-    <t>关闭</t>
-  </si>
-  <si>
     <t>电池*1+废金属*1+白爆矿*2</t>
   </si>
   <si>
@@ -678,9 +672,6 @@
   </si>
   <si>
     <t>睡眠脉冲仪</t>
-  </si>
-  <si>
-    <t>接电</t>
   </si>
   <si>
     <t>睡眠脉冲仪能通过低频脉冲，刺激大脑释放促进睡眠的神经递质。在安装了睡眠脉冲仪的地点休息能更快地恢复清醒度和健康值并降低做噩梦的概率。
@@ -690,9 +681,6 @@
     <t>精密元件*1+玻璃*1+电池*1</t>
   </si>
   <si>
-    <t>断电</t>
-  </si>
-  <si>
     <t>精密元件*1+玻璃*1+电池*2</t>
   </si>
   <si>
@@ -989,6 +977,22 @@
   </si>
   <si>
     <t>野炊营火</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>已开启</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>已关闭</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>已接电</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>未接电</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -1661,110 +1665,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AZ109"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" style="4" customWidth="1"/>
-    <col min="2" max="3" width="11.33203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.109375" style="27" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10.88671875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="28.625" style="4" customWidth="1"/>
+    <col min="2" max="3" width="11.375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="28.125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.25" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="6.875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="7.875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="10.875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="13.125" style="4" customWidth="1"/>
     <col min="13" max="22" width="19" style="4" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" style="4" customWidth="1"/>
-    <col min="24" max="24" width="10.109375" style="4" customWidth="1"/>
-    <col min="25" max="26" width="12.44140625" style="4" customWidth="1"/>
-    <col min="27" max="27" width="8.6640625" style="4"/>
-    <col min="28" max="28" width="12.21875" style="4" customWidth="1"/>
-    <col min="29" max="36" width="8.6640625" style="15"/>
-    <col min="37" max="37" width="11.6640625" style="15" customWidth="1"/>
-    <col min="38" max="38" width="9.21875" style="15" customWidth="1"/>
+    <col min="23" max="23" width="8.625" style="4" customWidth="1"/>
+    <col min="24" max="24" width="10.125" style="4" customWidth="1"/>
+    <col min="25" max="26" width="12.5" style="4" customWidth="1"/>
+    <col min="27" max="27" width="8.625" style="4"/>
+    <col min="28" max="28" width="12.25" style="4" customWidth="1"/>
+    <col min="29" max="36" width="8.625" style="15"/>
+    <col min="37" max="37" width="11.625" style="15" customWidth="1"/>
+    <col min="38" max="38" width="9.25" style="15" customWidth="1"/>
     <col min="39" max="39" width="12" style="15" customWidth="1"/>
-    <col min="40" max="40" width="11.77734375" style="15" customWidth="1"/>
-    <col min="41" max="41" width="8.6640625" style="15" customWidth="1"/>
-    <col min="42" max="42" width="9.21875" style="15" customWidth="1"/>
-    <col min="43" max="43" width="14.44140625" style="15" customWidth="1"/>
-    <col min="44" max="44" width="12.6640625" style="15" customWidth="1"/>
+    <col min="40" max="40" width="11.75" style="15" customWidth="1"/>
+    <col min="41" max="41" width="8.625" style="15" customWidth="1"/>
+    <col min="42" max="42" width="9.25" style="15" customWidth="1"/>
+    <col min="43" max="43" width="14.5" style="15" customWidth="1"/>
+    <col min="44" max="44" width="12.625" style="15" customWidth="1"/>
     <col min="45" max="45" width="11" style="15" customWidth="1"/>
-    <col min="46" max="46" width="12.33203125" style="15" customWidth="1"/>
-    <col min="47" max="47" width="10.21875" style="15" customWidth="1"/>
-    <col min="48" max="48" width="11.6640625" style="15" customWidth="1"/>
-    <col min="49" max="49" width="10.109375" style="15" customWidth="1"/>
-    <col min="50" max="50" width="16.109375" style="15" customWidth="1"/>
-    <col min="51" max="51" width="14.77734375" style="4" customWidth="1"/>
-    <col min="52" max="52" width="8.6640625" style="15"/>
+    <col min="46" max="46" width="12.375" style="15" customWidth="1"/>
+    <col min="47" max="47" width="10.25" style="15" customWidth="1"/>
+    <col min="48" max="48" width="11.625" style="15" customWidth="1"/>
+    <col min="49" max="49" width="10.125" style="15" customWidth="1"/>
+    <col min="50" max="50" width="16.125" style="15" customWidth="1"/>
+    <col min="51" max="51" width="14.75" style="4" customWidth="1"/>
+    <col min="52" max="52" width="8.625" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="62" customFormat="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="W1" s="4" t="s">
         <v>1</v>
@@ -2439,7 +2443,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:52" ht="82.8">
+    <row r="6" spans="1:52" ht="85.5">
       <c r="A6" s="17" t="s">
         <v>50</v>
       </c>
@@ -2585,18 +2589,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="82.8">
+    <row r="7" spans="1:52" ht="85.5">
       <c r="A7" s="17" t="s">
         <v>55</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E7" s="9">
         <v>3</v>
@@ -2731,7 +2735,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:52" ht="27.6">
+    <row r="8" spans="1:52" ht="28.5">
       <c r="A8" s="19" t="s">
         <v>56</v>
       </c>
@@ -2877,7 +2881,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:52" ht="27.6">
+    <row r="9" spans="1:52" ht="28.5">
       <c r="A9" s="19" t="s">
         <v>61</v>
       </c>
@@ -3315,16 +3319,16 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:52" ht="41.4">
+    <row r="12" spans="1:52" ht="42.75">
       <c r="A12" s="11" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="18" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -3459,16 +3463,16 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:52" ht="41.4">
+    <row r="13" spans="1:52" ht="42.75">
       <c r="A13" s="11" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="18" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E13" s="4">
         <v>1</v>
@@ -3603,12 +3607,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:52" ht="27.6">
+    <row r="14" spans="1:52" ht="28.5">
       <c r="A14" s="11" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="27" t="s">
@@ -3747,16 +3751,16 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:52" ht="41.4">
+    <row r="15" spans="1:52" ht="42.75">
       <c r="A15" s="11" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="18" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E15" s="4">
         <v>3</v>
@@ -3893,10 +3897,10 @@
     </row>
     <row r="16" spans="1:52">
       <c r="A16" s="11" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="27" t="s">
@@ -4037,9 +4041,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:51" ht="27.6">
+    <row r="17" spans="1:51" ht="28.5">
       <c r="A17" s="11" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>77</v>
@@ -4048,7 +4052,7 @@
         <v>78</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E17" s="4">
         <v>5</v>
@@ -4183,16 +4187,16 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:51" ht="27.6">
+    <row r="18" spans="1:51" ht="28.5">
       <c r="A18" s="11" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>77</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="18" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E18" s="4">
         <v>6</v>
@@ -4327,12 +4331,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:51" ht="41.4">
+    <row r="19" spans="1:51" ht="42.75">
       <c r="A19" s="11" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="27" t="s">
@@ -4471,7 +4475,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:51" ht="138">
+    <row r="20" spans="1:51" ht="128.25">
       <c r="A20" s="28" t="s">
         <v>80</v>
       </c>
@@ -4615,7 +4619,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:51" ht="82.8">
+    <row r="21" spans="1:51" ht="85.5">
       <c r="A21" s="28" t="s">
         <v>82</v>
       </c>
@@ -4759,7 +4763,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="82.8">
+    <row r="22" spans="1:51" ht="85.5">
       <c r="A22" s="28" t="s">
         <v>84</v>
       </c>
@@ -4900,7 +4904,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:51" ht="27.6">
+    <row r="23" spans="1:51" ht="28.5">
       <c r="A23" s="5" t="s">
         <v>86</v>
       </c>
@@ -5044,7 +5048,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:51" ht="69">
+    <row r="24" spans="1:51" ht="71.25">
       <c r="A24" s="5" t="s">
         <v>88</v>
       </c>
@@ -5188,7 +5192,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:51" ht="82.8">
+    <row r="25" spans="1:51" ht="71.25">
       <c r="A25" s="5" t="s">
         <v>90</v>
       </c>
@@ -5332,7 +5336,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:51" ht="41.4">
+    <row r="26" spans="1:51" ht="42.75">
       <c r="A26" s="5" t="s">
         <v>92</v>
       </c>
@@ -5476,7 +5480,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:51" ht="41.4">
+    <row r="27" spans="1:51" ht="42.75">
       <c r="A27" s="5" t="s">
         <v>94</v>
       </c>
@@ -5620,7 +5624,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="41.4">
+    <row r="28" spans="1:51" ht="42.75">
       <c r="A28" s="5" t="s">
         <v>96</v>
       </c>
@@ -5764,7 +5768,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:51" ht="41.4">
+    <row r="29" spans="1:51" ht="42.75">
       <c r="A29" s="5" t="s">
         <v>98</v>
       </c>
@@ -5908,7 +5912,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:51" ht="41.4">
+    <row r="30" spans="1:51" ht="42.75">
       <c r="A30" s="5" t="s">
         <v>100</v>
       </c>
@@ -6054,7 +6058,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:51" ht="69">
+    <row r="31" spans="1:51" ht="71.25">
       <c r="A31" s="5" t="s">
         <v>102</v>
       </c>
@@ -6910,7 +6914,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:51" ht="55.2">
+    <row r="37" spans="1:51" ht="57">
       <c r="A37" s="37" t="s">
         <v>76</v>
       </c>
@@ -7196,7 +7200,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:51" ht="27.6">
+    <row r="39" spans="1:51" ht="28.5">
       <c r="A39" s="38" t="s">
         <v>110</v>
       </c>
@@ -7338,7 +7342,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:51" ht="69">
+    <row r="40" spans="1:51" ht="71.25">
       <c r="A40" s="40" t="s">
         <v>112</v>
       </c>
@@ -7479,7 +7483,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:51" ht="55.2">
+    <row r="41" spans="1:51" ht="57">
       <c r="A41" s="40" t="s">
         <v>114</v>
       </c>
@@ -7620,7 +7624,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:51" ht="110.4">
+    <row r="42" spans="1:51" ht="99.75">
       <c r="A42" s="42" t="s">
         <v>116</v>
       </c>
@@ -7762,7 +7766,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:51" ht="69">
+    <row r="43" spans="1:51" ht="71.25">
       <c r="A43" s="43" t="s">
         <v>119</v>
       </c>
@@ -7904,12 +7908,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:51" ht="41.4">
+    <row r="44" spans="1:51" ht="42.75">
       <c r="A44" s="11" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B44" s="44" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="27" t="s">
@@ -8048,7 +8052,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:51" ht="55.2">
+    <row r="45" spans="1:51" ht="57">
       <c r="A45" s="29" t="s">
         <v>124</v>
       </c>
@@ -8192,7 +8196,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:51" ht="41.4">
+    <row r="46" spans="1:51" ht="42.75">
       <c r="A46" s="29" t="s">
         <v>126</v>
       </c>
@@ -8336,7 +8340,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:51" ht="41.4">
+    <row r="47" spans="1:51" ht="28.5">
       <c r="A47" s="29" t="s">
         <v>128</v>
       </c>
@@ -8624,12 +8628,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:51" ht="41.4">
+    <row r="49" spans="1:51" ht="42.75">
       <c r="A49" s="11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="27" t="s">
@@ -8768,16 +8772,16 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:51" ht="27.6">
+    <row r="50" spans="1:51" ht="28.5">
       <c r="A50" s="11" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="18" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E50" s="4">
         <v>2</v>
@@ -8912,16 +8916,16 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:51" ht="82.8">
+    <row r="51" spans="1:51" ht="71.25">
       <c r="A51" s="11" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="18" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E51" s="4">
         <v>3</v>
@@ -9056,16 +9060,16 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:51" ht="41.4">
+    <row r="52" spans="1:51" ht="42.75">
       <c r="A52" s="11" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="18" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E52" s="4">
         <v>4</v>
@@ -9202,10 +9206,10 @@
     </row>
     <row r="53" spans="1:51">
       <c r="A53" s="11" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="27" t="s">
@@ -9344,16 +9348,16 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:51" ht="82.8">
+    <row r="54" spans="1:51" ht="71.25">
       <c r="A54" s="11" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="18" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E54" s="4">
         <v>6</v>
@@ -9488,12 +9492,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:51" ht="41.4">
+    <row r="55" spans="1:51" ht="42.75">
       <c r="A55" s="11" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="27" t="s">
@@ -9632,7 +9636,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:51" ht="27.6">
+    <row r="56" spans="1:51">
       <c r="A56" s="29" t="s">
         <v>136</v>
       </c>
@@ -9776,7 +9780,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:51" ht="27.6">
+    <row r="57" spans="1:51" ht="28.5">
       <c r="A57" s="19" t="s">
         <v>138</v>
       </c>
@@ -10064,7 +10068,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:51" ht="27.6">
+    <row r="59" spans="1:51" ht="28.5">
       <c r="A59" s="19" t="s">
         <v>142</v>
       </c>
@@ -10208,7 +10212,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="1:51" ht="27.6">
+    <row r="60" spans="1:51" ht="28.5">
       <c r="A60" s="19" t="s">
         <v>144</v>
       </c>
@@ -10494,18 +10498,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:51" ht="110.4">
+    <row r="62" spans="1:51" ht="99.75">
       <c r="A62" s="11" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>147</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E62" s="9">
         <v>0</v>
@@ -10640,18 +10644,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:51" ht="110.4">
+    <row r="63" spans="1:51" ht="99.75">
       <c r="A63" s="11" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>78</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E63" s="9">
         <v>1</v>
@@ -10786,18 +10790,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:51" ht="69">
+    <row r="64" spans="1:51" ht="57">
       <c r="A64" s="11" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>147</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E64" s="9">
         <v>2</v>
@@ -10932,18 +10936,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:51" ht="69">
+    <row r="65" spans="1:51" ht="57">
       <c r="A65" s="11" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>78</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E65" s="9">
         <v>3</v>
@@ -11078,18 +11082,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:51" ht="55.2">
+    <row r="66" spans="1:51" ht="57">
       <c r="A66" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>147</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E66" s="9">
         <v>4</v>
@@ -11224,18 +11228,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="1:51" ht="55.2">
+    <row r="67" spans="1:51" ht="57">
       <c r="A67" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>78</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E67" s="9">
         <v>5</v>
@@ -11370,12 +11374,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:51" ht="27.6">
+    <row r="68" spans="1:51" ht="28.5">
       <c r="A68" s="11" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>149</v>
@@ -11518,12 +11522,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:51" ht="55.2">
+    <row r="69" spans="1:51" ht="57">
       <c r="A69" s="11" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="27" t="s">
@@ -11664,12 +11668,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:51" ht="55.2">
+    <row r="70" spans="1:51" ht="57">
       <c r="A70" s="11" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="27" t="s">
@@ -11808,7 +11812,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:51" ht="41.4">
+    <row r="71" spans="1:51" ht="42.75">
       <c r="A71" s="17" t="s">
         <v>156</v>
       </c>
@@ -11952,7 +11956,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:51" ht="41.4">
+    <row r="72" spans="1:51" ht="42.75">
       <c r="A72" s="17" t="s">
         <v>158</v>
       </c>
@@ -12098,7 +12102,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:51" ht="41.4">
+    <row r="73" spans="1:51" ht="42.75">
       <c r="A73" s="19" t="s">
         <v>160</v>
       </c>
@@ -12244,7 +12248,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:51" ht="69">
+    <row r="74" spans="1:51" ht="57">
       <c r="A74" s="19" t="s">
         <v>162</v>
       </c>
@@ -12388,7 +12392,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:51" ht="27.6">
+    <row r="75" spans="1:51" ht="28.5">
       <c r="A75" s="19" t="s">
         <v>164</v>
       </c>
@@ -12532,7 +12536,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:51" ht="69">
+    <row r="76" spans="1:51" ht="71.25">
       <c r="A76" s="19" t="s">
         <v>166</v>
       </c>
@@ -12676,7 +12680,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:51" ht="82.8">
+    <row r="77" spans="1:51" ht="85.5">
       <c r="A77" s="37" t="s">
         <v>168</v>
       </c>
@@ -12817,12 +12821,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="78" spans="1:51" ht="69">
+    <row r="78" spans="1:51" ht="57">
       <c r="A78" s="11" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="8" t="s">
@@ -12963,12 +12967,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:51" ht="27.6">
+    <row r="79" spans="1:51" ht="28.5">
       <c r="A79" s="11" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="27" t="s">
@@ -13109,12 +13113,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:51" ht="41.4">
+    <row r="80" spans="1:51" ht="42.75">
       <c r="A80" s="11" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="27" t="s">
@@ -13255,7 +13259,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="81" spans="1:51" ht="138">
+    <row r="81" spans="1:51" ht="128.25">
       <c r="A81" s="17" t="s">
         <v>176</v>
       </c>
@@ -13401,7 +13405,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:51" ht="27.6">
+    <row r="82" spans="1:51" ht="28.5">
       <c r="A82" s="51" t="s">
         <v>178</v>
       </c>
@@ -13546,7 +13550,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="83" spans="1:51" ht="41.4">
+    <row r="83" spans="1:51" ht="42.75">
       <c r="A83" s="19" t="s">
         <v>181</v>
       </c>
@@ -13691,7 +13695,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:51" ht="55.2">
+    <row r="84" spans="1:51" ht="57">
       <c r="A84" s="19" t="s">
         <v>183</v>
       </c>
@@ -13836,24 +13840,24 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:51" ht="41.4">
+    <row r="85" spans="1:51" ht="42.75">
       <c r="A85" s="7" t="s">
         <v>185</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>186</v>
+        <v>301</v>
+      </c>
+      <c r="C85" s="33" t="s">
+        <v>316</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E85" s="4">
         <v>0</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G85" s="11">
         <v>1</v>
@@ -13982,25 +13986,25 @@
         <v>37</v>
       </c>
       <c r="AY85" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
-    <row r="86" spans="1:51" ht="41.4">
+    <row r="86" spans="1:51" ht="42.75">
       <c r="A86" s="7"/>
       <c r="B86" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>189</v>
+        <v>303</v>
+      </c>
+      <c r="C86" s="33" t="s">
+        <v>315</v>
       </c>
       <c r="D86" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>149</v>
+        <v>304</v>
+      </c>
+      <c r="E86" s="4">
+        <v>1</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G86" s="4">
         <v>1</v>
@@ -14129,25 +14133,25 @@
         <v>37</v>
       </c>
       <c r="AY86" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
-    <row r="87" spans="1:51" ht="69">
+    <row r="87" spans="1:51" ht="71.25">
       <c r="A87" s="11" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="18" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E87" s="4">
         <v>2</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G87" s="11">
         <v>1</v>
@@ -14273,27 +14277,27 @@
         <v>37</v>
       </c>
       <c r="AY87" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="88" spans="1:51" ht="57">
+      <c r="A88" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="B88" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="C88" s="7" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="88" spans="1:51" ht="55.2">
-      <c r="A88" s="29" t="s">
+      <c r="D88" s="8" t="s">
         <v>192</v>
-      </c>
-      <c r="B88" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>194</v>
       </c>
       <c r="E88" s="30">
         <v>3</v>
       </c>
       <c r="F88" s="31" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G88" s="4">
         <v>1</v>
@@ -14422,16 +14426,16 @@
         <v>37</v>
       </c>
       <c r="AY88" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
-    <row r="89" spans="1:51" ht="27.6">
+    <row r="89" spans="1:51">
       <c r="A89" s="29"/>
       <c r="B89" s="29" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="30">
@@ -14495,25 +14499,25 @@
         <v>37</v>
       </c>
       <c r="AY89" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
-    <row r="90" spans="1:51" ht="55.2">
+    <row r="90" spans="1:51" ht="57">
       <c r="A90" s="19" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C90" s="33"/>
       <c r="D90" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E90" s="30">
         <v>5</v>
       </c>
       <c r="F90" s="46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G90" s="4">
         <v>1</v>
@@ -14642,25 +14646,25 @@
         <v>37</v>
       </c>
       <c r="AY90" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
-    <row r="91" spans="1:51" ht="69">
+    <row r="91" spans="1:51" ht="71.25">
       <c r="A91" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B91" s="29" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E91" s="30">
         <v>6</v>
       </c>
       <c r="F91" s="31" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G91" s="4">
         <v>1</v>
@@ -14789,27 +14793,27 @@
         <v>37</v>
       </c>
       <c r="AY91" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="92" spans="1:51" ht="42.75">
+      <c r="A92" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C92" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="D92" s="8" t="s">
         <v>203</v>
-      </c>
-    </row>
-    <row r="92" spans="1:51" ht="41.4">
-      <c r="A92" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="B92" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>205</v>
       </c>
       <c r="E92" s="34">
         <v>7</v>
       </c>
       <c r="F92" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G92" s="4">
         <v>1</v>
@@ -14935,25 +14939,25 @@
         <v>37</v>
       </c>
       <c r="AY92" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="93" spans="1:51" ht="41.4">
+    <row r="93" spans="1:51" ht="42.75">
       <c r="A93" s="19"/>
       <c r="B93" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>189</v>
+        <v>202</v>
+      </c>
+      <c r="C93" s="33" t="s">
+        <v>316</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E93" s="34">
         <v>8</v>
       </c>
       <c r="F93" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G93" s="4">
         <v>1</v>
@@ -15079,27 +15083,27 @@
         <v>37</v>
       </c>
       <c r="AY93" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="94" spans="1:51" ht="57">
+      <c r="A94" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="B94" s="19" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="94" spans="1:51" ht="55.2">
-      <c r="A94" s="37" t="s">
+      <c r="C94" s="55" t="s">
         <v>208</v>
       </c>
-      <c r="B94" s="19" t="s">
+      <c r="D94" s="8" t="s">
         <v>209</v>
-      </c>
-      <c r="C94" s="55" t="s">
-        <v>210</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>211</v>
       </c>
       <c r="E94" s="34">
         <v>9</v>
       </c>
       <c r="F94" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G94" s="4">
         <v>1</v>
@@ -15228,24 +15232,24 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:51" ht="41.4">
+    <row r="95" spans="1:51" ht="42.75">
       <c r="A95" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D95" s="8" t="s">
         <v>212</v>
-      </c>
-      <c r="B95" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>214</v>
       </c>
       <c r="E95" s="34">
         <v>10</v>
       </c>
       <c r="F95" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G95" s="4">
         <v>1</v>
@@ -15374,27 +15378,27 @@
         <v>37</v>
       </c>
       <c r="AY95" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="96" spans="1:51" ht="85.5">
+      <c r="A96" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="C96" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="D96" s="8" t="s">
         <v>215</v>
-      </c>
-    </row>
-    <row r="96" spans="1:51" ht="110.4">
-      <c r="A96" s="37" t="s">
-        <v>216</v>
-      </c>
-      <c r="B96" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>218</v>
       </c>
       <c r="E96" s="34">
         <v>11</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G96" s="4">
         <v>1</v>
@@ -15520,23 +15524,23 @@
         <v>37</v>
       </c>
       <c r="AY96" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="97" spans="1:51" ht="27.6">
+    <row r="97" spans="1:51" ht="28.5">
       <c r="A97" s="56"/>
       <c r="B97" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="C97" s="28" t="s">
-        <v>220</v>
+        <v>214</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>318</v>
       </c>
       <c r="D97" s="57"/>
       <c r="E97" s="34">
         <v>12</v>
       </c>
       <c r="F97" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G97" s="4">
         <v>1</v>
@@ -15662,25 +15666,25 @@
         <v>37</v>
       </c>
       <c r="AY97" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
-    <row r="98" spans="1:51" ht="41.4">
+    <row r="98" spans="1:51" ht="42.75">
       <c r="A98" s="56" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C98" s="28"/>
       <c r="D98" s="57" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E98" s="34">
         <v>13</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G98" s="4">
         <v>1</v>
@@ -15809,25 +15813,25 @@
         <v>37</v>
       </c>
       <c r="AY98" s="4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="99" spans="1:51">
       <c r="A99" s="56" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B99" s="19" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C99" s="28" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D99" s="57"/>
       <c r="E99" s="34">
         <v>14</v>
       </c>
       <c r="F99" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G99" s="4">
         <v>1</v>
@@ -15953,15 +15957,15 @@
         <v>37</v>
       </c>
       <c r="AY99" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
-    <row r="100" spans="1:51" ht="27.6">
+    <row r="100" spans="1:51" ht="28.5">
       <c r="A100" s="56" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C100" s="58"/>
       <c r="D100" s="57"/>
@@ -15969,7 +15973,7 @@
         <v>15</v>
       </c>
       <c r="F100" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G100" s="4">
         <v>1</v>
@@ -16095,25 +16099,25 @@
         <v>37</v>
       </c>
       <c r="AY100" s="59" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="101" spans="1:51" ht="55.2">
+    <row r="101" spans="1:51" ht="57">
       <c r="A101" s="56" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B101" s="22" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C101" s="58"/>
       <c r="D101" s="57" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E101" s="34">
         <v>16</v>
       </c>
       <c r="F101" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G101" s="4">
         <v>1</v>
@@ -16242,25 +16246,25 @@
         <v>37</v>
       </c>
       <c r="AY101" s="4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
-    <row r="102" spans="1:51" ht="124.2">
+    <row r="102" spans="1:51" ht="114">
       <c r="A102" s="56" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B102" s="22" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C102" s="58"/>
       <c r="D102" s="57" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E102" s="34">
         <v>17</v>
       </c>
       <c r="F102" s="35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G102" s="4">
         <v>1</v>
@@ -16386,25 +16390,25 @@
         <v>37</v>
       </c>
       <c r="AY102" s="4" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
-    <row r="103" spans="1:51" ht="41.4">
+    <row r="103" spans="1:51" ht="42.75">
       <c r="A103" s="11" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C103" s="11"/>
       <c r="D103" s="18" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E103" s="9">
         <v>0</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G103" s="11">
         <v>1</v>
@@ -16533,21 +16537,21 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:51" ht="69">
+    <row r="104" spans="1:51" ht="71.25">
       <c r="A104" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D104" s="27" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E104" s="9">
         <v>1</v>
       </c>
       <c r="F104" s="50" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G104" s="4">
         <v>10</v>
@@ -16676,22 +16680,22 @@
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="1:51" ht="69">
+    <row r="105" spans="1:51" ht="71.25">
       <c r="A105" s="11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C105" s="11"/>
       <c r="D105" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E105" s="9">
         <v>2</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G105" s="4">
         <v>5</v>
@@ -16820,24 +16824,24 @@
         <v>36</v>
       </c>
     </row>
-    <row r="106" spans="1:51" ht="55.2">
+    <row r="106" spans="1:51" ht="57">
       <c r="A106" s="11" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D106" s="18" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E106" s="9">
         <v>3</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G106" s="4">
         <v>1</v>
@@ -16966,20 +16970,20 @@
         <v>36</v>
       </c>
     </row>
-    <row r="107" spans="1:51" ht="55.2">
+    <row r="107" spans="1:51" ht="57">
       <c r="A107" s="17"/>
       <c r="B107" s="60" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C107" s="7"/>
       <c r="D107" s="27" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E107" s="9">
         <v>4</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G107" s="4">
         <v>1</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC7BA84-E67E-4C49-A4AE-053DD43FCBD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3878242-BDA9-46F2-93CD-D3763D975C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3810" yWindow="3810" windowWidth="28800" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4397" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4395" uniqueCount="319">
   <si>
     <t>ExtraInfo</t>
   </si>
@@ -577,13 +577,6 @@
 （减重率50%）</t>
   </si>
   <si>
-    <t>鱼获袋</t>
-  </si>
-  <si>
-    <t>纤维编织的鱼获袋，适合在水中携带物品。
-（减重率60%，在水域环境中额外+15%减重率）</t>
-  </si>
-  <si>
     <t>矿石释氧机</t>
   </si>
   <si>
@@ -993,6 +986,15 @@
   </si>
   <si>
     <t>未接电</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>渔获袋</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>纤维编织的渔获袋，适合在水中携带物品。
+（减重率60%）</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -1705,70 +1707,70 @@
   <sheetData>
     <row r="1" spans="1:52" s="62" customFormat="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="W1" s="4" t="s">
         <v>1</v>
@@ -2594,13 +2596,13 @@
         <v>55</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>32</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E7" s="9">
         <v>3</v>
@@ -3321,14 +3323,14 @@
     </row>
     <row r="12" spans="1:52" ht="42.75">
       <c r="A12" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="18" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -3465,14 +3467,14 @@
     </row>
     <row r="13" spans="1:52" ht="42.75">
       <c r="A13" s="11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="18" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E13" s="4">
         <v>1</v>
@@ -3609,10 +3611,10 @@
     </row>
     <row r="14" spans="1:52" ht="28.5">
       <c r="A14" s="11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="27" t="s">
@@ -3753,14 +3755,14 @@
     </row>
     <row r="15" spans="1:52" ht="42.75">
       <c r="A15" s="11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="18" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E15" s="4">
         <v>3</v>
@@ -3897,10 +3899,10 @@
     </row>
     <row r="16" spans="1:52">
       <c r="A16" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="27" t="s">
@@ -4043,7 +4045,7 @@
     </row>
     <row r="17" spans="1:51" ht="28.5">
       <c r="A17" s="11" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>77</v>
@@ -4052,7 +4054,7 @@
         <v>78</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E17" s="4">
         <v>5</v>
@@ -4189,14 +4191,14 @@
     </row>
     <row r="18" spans="1:51" ht="28.5">
       <c r="A18" s="11" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>77</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="18" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E18" s="4">
         <v>6</v>
@@ -4333,10 +4335,10 @@
     </row>
     <row r="19" spans="1:51" ht="42.75">
       <c r="A19" s="11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="27" t="s">
@@ -7910,10 +7912,10 @@
     </row>
     <row r="44" spans="1:51" ht="42.75">
       <c r="A44" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B44" s="44" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="27" t="s">
@@ -8630,10 +8632,10 @@
     </row>
     <row r="49" spans="1:51" ht="42.75">
       <c r="A49" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="27" t="s">
@@ -8774,14 +8776,14 @@
     </row>
     <row r="50" spans="1:51" ht="28.5">
       <c r="A50" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E50" s="4">
         <v>2</v>
@@ -8918,14 +8920,14 @@
     </row>
     <row r="51" spans="1:51" ht="71.25">
       <c r="A51" s="11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="18" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E51" s="4">
         <v>3</v>
@@ -9062,14 +9064,14 @@
     </row>
     <row r="52" spans="1:51" ht="42.75">
       <c r="A52" s="11" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="18" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E52" s="4">
         <v>4</v>
@@ -9206,10 +9208,10 @@
     </row>
     <row r="53" spans="1:51">
       <c r="A53" s="11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="27" t="s">
@@ -9350,14 +9352,14 @@
     </row>
     <row r="54" spans="1:51" ht="71.25">
       <c r="A54" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="18" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E54" s="4">
         <v>6</v>
@@ -9494,10 +9496,10 @@
     </row>
     <row r="55" spans="1:51" ht="42.75">
       <c r="A55" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="27" t="s">
@@ -10500,16 +10502,16 @@
     </row>
     <row r="62" spans="1:51" ht="99.75">
       <c r="A62" s="11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>147</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E62" s="9">
         <v>0</v>
@@ -10646,16 +10648,16 @@
     </row>
     <row r="63" spans="1:51" ht="99.75">
       <c r="A63" s="11" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>78</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E63" s="9">
         <v>1</v>
@@ -10792,16 +10794,16 @@
     </row>
     <row r="64" spans="1:51" ht="57">
       <c r="A64" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>147</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E64" s="9">
         <v>2</v>
@@ -10938,16 +10940,16 @@
     </row>
     <row r="65" spans="1:51" ht="57">
       <c r="A65" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>78</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E65" s="9">
         <v>3</v>
@@ -11084,16 +11086,16 @@
     </row>
     <row r="66" spans="1:51" ht="57">
       <c r="A66" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>147</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E66" s="9">
         <v>4</v>
@@ -11230,16 +11232,16 @@
     </row>
     <row r="67" spans="1:51" ht="57">
       <c r="A67" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>78</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E67" s="9">
         <v>5</v>
@@ -11376,10 +11378,10 @@
     </row>
     <row r="68" spans="1:51" ht="28.5">
       <c r="A68" s="11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>149</v>
@@ -11524,10 +11526,10 @@
     </row>
     <row r="69" spans="1:51" ht="57">
       <c r="A69" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="27" t="s">
@@ -11670,10 +11672,10 @@
     </row>
     <row r="70" spans="1:51" ht="57">
       <c r="A70" s="11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="27" t="s">
@@ -12691,6 +12693,9 @@
       <c r="D77" s="27" t="s">
         <v>169</v>
       </c>
+      <c r="E77" s="4">
+        <v>9</v>
+      </c>
       <c r="F77" s="12" t="s">
         <v>151</v>
       </c>
@@ -12823,10 +12828,10 @@
     </row>
     <row r="78" spans="1:51" ht="57">
       <c r="A78" s="11" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="8" t="s">
@@ -12969,10 +12974,10 @@
     </row>
     <row r="79" spans="1:51" ht="28.5">
       <c r="A79" s="11" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="27" t="s">
@@ -13115,10 +13120,10 @@
     </row>
     <row r="80" spans="1:51" ht="42.75">
       <c r="A80" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="27" t="s">
@@ -13613,8 +13618,11 @@
       <c r="W83" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="X83" s="24" t="s">
-        <v>35</v>
+      <c r="X83" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y83" s="4">
+        <v>3</v>
       </c>
       <c r="Z83" s="24" t="s">
         <v>35</v>
@@ -13695,15 +13703,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:51" ht="57">
+    <row r="84" spans="1:51" ht="42.75">
       <c r="A84" s="19" t="s">
-        <v>183</v>
+        <v>317</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>183</v>
+        <v>317</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>184</v>
+        <v>318</v>
       </c>
       <c r="E84" s="26">
         <v>6</v>
@@ -13758,8 +13766,11 @@
       <c r="W84" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="X84" s="24" t="s">
-        <v>35</v>
+      <c r="X84" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y84" s="4">
+        <v>4</v>
       </c>
       <c r="Z84" s="24" t="s">
         <v>35</v>
@@ -13842,22 +13853,22 @@
     </row>
     <row r="85" spans="1:51" ht="42.75">
       <c r="A85" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E85" s="4">
         <v>0</v>
       </c>
       <c r="F85" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G85" s="11">
         <v>1</v>
@@ -13986,25 +13997,25 @@
         <v>37</v>
       </c>
       <c r="AY85" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:51" ht="42.75">
       <c r="A86" s="7"/>
       <c r="B86" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C86" s="33" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D86" s="18" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E86" s="4">
         <v>1</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G86" s="4">
         <v>1</v>
@@ -14133,25 +14144,25 @@
         <v>37</v>
       </c>
       <c r="AY86" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:51" ht="71.25">
       <c r="A87" s="11" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="18" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E87" s="4">
         <v>2</v>
       </c>
       <c r="F87" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G87" s="11">
         <v>1</v>
@@ -14277,27 +14288,27 @@
         <v>37</v>
       </c>
       <c r="AY87" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" spans="1:51" ht="57">
       <c r="A88" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="B88" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D88" s="8" t="s">
         <v>190</v>
-      </c>
-      <c r="B88" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>192</v>
       </c>
       <c r="E88" s="30">
         <v>3</v>
       </c>
       <c r="F88" s="31" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G88" s="4">
         <v>1</v>
@@ -14426,16 +14437,16 @@
         <v>37</v>
       </c>
       <c r="AY88" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="89" spans="1:51">
       <c r="A89" s="29"/>
       <c r="B89" s="29" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D89" s="8"/>
       <c r="E89" s="30">
@@ -14499,25 +14510,25 @@
         <v>37</v>
       </c>
       <c r="AY89" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="90" spans="1:51" ht="57">
       <c r="A90" s="19" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C90" s="33"/>
       <c r="D90" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E90" s="30">
         <v>5</v>
       </c>
       <c r="F90" s="46" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G90" s="4">
         <v>1</v>
@@ -14646,25 +14657,25 @@
         <v>37</v>
       </c>
       <c r="AY90" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="91" spans="1:51" ht="71.25">
       <c r="A91" s="29" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B91" s="29" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C91" s="7"/>
       <c r="D91" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E91" s="30">
         <v>6</v>
       </c>
       <c r="F91" s="31" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G91" s="4">
         <v>1</v>
@@ -14793,27 +14804,27 @@
         <v>37</v>
       </c>
       <c r="AY91" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="92" spans="1:51" ht="42.75">
       <c r="A92" s="19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E92" s="34">
         <v>7</v>
       </c>
       <c r="F92" s="35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G92" s="4">
         <v>1</v>
@@ -14939,25 +14950,25 @@
         <v>37</v>
       </c>
       <c r="AY92" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="93" spans="1:51" ht="42.75">
       <c r="A93" s="19"/>
       <c r="B93" s="19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C93" s="33" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E93" s="34">
         <v>8</v>
       </c>
       <c r="F93" s="35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G93" s="4">
         <v>1</v>
@@ -15083,27 +15094,27 @@
         <v>37</v>
       </c>
       <c r="AY93" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="94" spans="1:51" ht="57">
       <c r="A94" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C94" s="55" t="s">
         <v>206</v>
       </c>
-      <c r="B94" s="19" t="s">
+      <c r="D94" s="8" t="s">
         <v>207</v>
-      </c>
-      <c r="C94" s="55" t="s">
-        <v>208</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>209</v>
       </c>
       <c r="E94" s="34">
         <v>9</v>
       </c>
       <c r="F94" s="35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G94" s="4">
         <v>1</v>
@@ -15234,22 +15245,22 @@
     </row>
     <row r="95" spans="1:51" ht="42.75">
       <c r="A95" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D95" s="8" t="s">
         <v>210</v>
-      </c>
-      <c r="B95" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>212</v>
       </c>
       <c r="E95" s="34">
         <v>10</v>
       </c>
       <c r="F95" s="35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G95" s="4">
         <v>1</v>
@@ -15378,27 +15389,27 @@
         <v>37</v>
       </c>
       <c r="AY95" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:51" ht="85.5">
       <c r="A96" s="37" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C96" s="33" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E96" s="34">
         <v>11</v>
       </c>
       <c r="F96" s="35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G96" s="4">
         <v>1</v>
@@ -15524,23 +15535,23 @@
         <v>37</v>
       </c>
       <c r="AY96" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:51" ht="28.5">
       <c r="A97" s="56"/>
       <c r="B97" s="19" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D97" s="57"/>
       <c r="E97" s="34">
         <v>12</v>
       </c>
       <c r="F97" s="35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G97" s="4">
         <v>1</v>
@@ -15666,25 +15677,25 @@
         <v>37</v>
       </c>
       <c r="AY97" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="98" spans="1:51" ht="42.75">
       <c r="A98" s="56" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B98" s="19" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C98" s="28"/>
       <c r="D98" s="57" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E98" s="34">
         <v>13</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G98" s="4">
         <v>1</v>
@@ -15813,25 +15824,25 @@
         <v>37</v>
       </c>
       <c r="AY98" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="99" spans="1:51">
       <c r="A99" s="56" t="s">
+        <v>219</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="C99" s="28" t="s">
         <v>221</v>
-      </c>
-      <c r="B99" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="C99" s="28" t="s">
-        <v>223</v>
       </c>
       <c r="D99" s="57"/>
       <c r="E99" s="34">
         <v>14</v>
       </c>
       <c r="F99" s="35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G99" s="4">
         <v>1</v>
@@ -15957,15 +15968,15 @@
         <v>37</v>
       </c>
       <c r="AY99" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="100" spans="1:51" ht="28.5">
       <c r="A100" s="56" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B100" s="19" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C100" s="58"/>
       <c r="D100" s="57"/>
@@ -15973,7 +15984,7 @@
         <v>15</v>
       </c>
       <c r="F100" s="35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G100" s="4">
         <v>1</v>
@@ -16099,25 +16110,25 @@
         <v>37</v>
       </c>
       <c r="AY100" s="59" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="101" spans="1:51" ht="57">
       <c r="A101" s="56" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B101" s="22" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C101" s="58"/>
       <c r="D101" s="57" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E101" s="34">
         <v>16</v>
       </c>
       <c r="F101" s="35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G101" s="4">
         <v>1</v>
@@ -16246,25 +16257,25 @@
         <v>37</v>
       </c>
       <c r="AY101" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="102" spans="1:51" ht="114">
       <c r="A102" s="56" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B102" s="22" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C102" s="58"/>
       <c r="D102" s="57" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E102" s="34">
         <v>17</v>
       </c>
       <c r="F102" s="35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G102" s="4">
         <v>1</v>
@@ -16390,25 +16401,25 @@
         <v>37</v>
       </c>
       <c r="AY102" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="103" spans="1:51" ht="42.75">
       <c r="A103" s="11" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C103" s="11"/>
       <c r="D103" s="18" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E103" s="9">
         <v>0</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G103" s="11">
         <v>1</v>
@@ -16539,19 +16550,19 @@
     </row>
     <row r="104" spans="1:51" ht="71.25">
       <c r="A104" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D104" s="27" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E104" s="9">
         <v>1</v>
       </c>
       <c r="F104" s="50" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G104" s="4">
         <v>10</v>
@@ -16682,20 +16693,20 @@
     </row>
     <row r="105" spans="1:51" ht="71.25">
       <c r="A105" s="11" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C105" s="11"/>
       <c r="D105" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E105" s="9">
         <v>2</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G105" s="4">
         <v>5</v>
@@ -16826,22 +16837,22 @@
     </row>
     <row r="106" spans="1:51" ht="57">
       <c r="A106" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D106" s="18" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E106" s="9">
         <v>3</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G106" s="4">
         <v>1</v>
@@ -16973,17 +16984,17 @@
     <row r="107" spans="1:51" ht="57">
       <c r="A107" s="17"/>
       <c r="B107" s="60" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C107" s="7"/>
       <c r="D107" s="27" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E107" s="9">
         <v>4</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G107" s="4">
         <v>1</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3878242-BDA9-46F2-93CD-D3763D975C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33D519D-1E02-4FA2-975C-AFCE2A991463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3810" yWindow="3810" windowWidth="28800" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4395" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4394" uniqueCount="319">
   <si>
     <t>ExtraInfo</t>
   </si>
@@ -15161,8 +15161,11 @@
       <c r="W94" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="X94" s="14" t="s">
-        <v>35</v>
+      <c r="X94" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y94" s="4">
+        <v>4</v>
       </c>
       <c r="Z94" s="14" t="s">
         <v>35</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33D519D-1E02-4FA2-975C-AFCE2A991463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319947B9-F6C4-49E9-ADE9-5A258D4D69B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="3810" windowWidth="28800" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4394" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4392" uniqueCount="320">
   <si>
     <t>ExtraInfo</t>
   </si>
@@ -995,6 +995,10 @@
   <si>
     <t>纤维编织的渔获袋，适合在水中携带物品。
 （减重率60%）</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>熟触手</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -1667,42 +1671,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AZ109"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="28.625" style="4" customWidth="1"/>
-    <col min="2" max="3" width="11.375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.125" style="27" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10.25" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="6.875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="7.875" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10.875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="13.125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" style="4" customWidth="1"/>
+    <col min="2" max="3" width="11.33203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="28.109375" style="27" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.109375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="13.109375" style="4" customWidth="1"/>
     <col min="13" max="22" width="19" style="4" customWidth="1"/>
-    <col min="23" max="23" width="8.625" style="4" customWidth="1"/>
-    <col min="24" max="24" width="10.125" style="4" customWidth="1"/>
-    <col min="25" max="26" width="12.5" style="4" customWidth="1"/>
-    <col min="27" max="27" width="8.625" style="4"/>
-    <col min="28" max="28" width="12.25" style="4" customWidth="1"/>
-    <col min="29" max="36" width="8.625" style="15"/>
-    <col min="37" max="37" width="11.625" style="15" customWidth="1"/>
-    <col min="38" max="38" width="9.25" style="15" customWidth="1"/>
+    <col min="23" max="23" width="8.6640625" style="4" customWidth="1"/>
+    <col min="24" max="24" width="10.109375" style="4" customWidth="1"/>
+    <col min="25" max="26" width="12.44140625" style="4" customWidth="1"/>
+    <col min="27" max="27" width="8.6640625" style="4"/>
+    <col min="28" max="28" width="12.21875" style="4" customWidth="1"/>
+    <col min="29" max="36" width="8.6640625" style="15"/>
+    <col min="37" max="37" width="11.6640625" style="15" customWidth="1"/>
+    <col min="38" max="38" width="9.21875" style="15" customWidth="1"/>
     <col min="39" max="39" width="12" style="15" customWidth="1"/>
-    <col min="40" max="40" width="11.75" style="15" customWidth="1"/>
-    <col min="41" max="41" width="8.625" style="15" customWidth="1"/>
-    <col min="42" max="42" width="9.25" style="15" customWidth="1"/>
-    <col min="43" max="43" width="14.5" style="15" customWidth="1"/>
-    <col min="44" max="44" width="12.625" style="15" customWidth="1"/>
+    <col min="40" max="40" width="11.77734375" style="15" customWidth="1"/>
+    <col min="41" max="41" width="8.6640625" style="15" customWidth="1"/>
+    <col min="42" max="42" width="9.21875" style="15" customWidth="1"/>
+    <col min="43" max="43" width="14.44140625" style="15" customWidth="1"/>
+    <col min="44" max="44" width="12.6640625" style="15" customWidth="1"/>
     <col min="45" max="45" width="11" style="15" customWidth="1"/>
-    <col min="46" max="46" width="12.375" style="15" customWidth="1"/>
-    <col min="47" max="47" width="10.25" style="15" customWidth="1"/>
-    <col min="48" max="48" width="11.625" style="15" customWidth="1"/>
-    <col min="49" max="49" width="10.125" style="15" customWidth="1"/>
-    <col min="50" max="50" width="16.125" style="15" customWidth="1"/>
-    <col min="51" max="51" width="14.75" style="4" customWidth="1"/>
-    <col min="52" max="52" width="8.625" style="15"/>
+    <col min="46" max="46" width="12.33203125" style="15" customWidth="1"/>
+    <col min="47" max="47" width="10.21875" style="15" customWidth="1"/>
+    <col min="48" max="48" width="11.6640625" style="15" customWidth="1"/>
+    <col min="49" max="49" width="10.109375" style="15" customWidth="1"/>
+    <col min="50" max="50" width="16.109375" style="15" customWidth="1"/>
+    <col min="51" max="51" width="14.77734375" style="4" customWidth="1"/>
+    <col min="52" max="52" width="8.6640625" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="62" customFormat="1" ht="15.75" customHeight="1">
@@ -2445,7 +2449,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:52" ht="85.5">
+    <row r="6" spans="1:52" ht="82.8">
       <c r="A6" s="17" t="s">
         <v>50</v>
       </c>
@@ -2591,7 +2595,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="85.5">
+    <row r="7" spans="1:52" ht="82.8">
       <c r="A7" s="17" t="s">
         <v>55</v>
       </c>
@@ -2737,7 +2741,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:52" ht="28.5">
+    <row r="8" spans="1:52" ht="27.6">
       <c r="A8" s="19" t="s">
         <v>56</v>
       </c>
@@ -2883,7 +2887,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:52" ht="28.5">
+    <row r="9" spans="1:52" ht="27.6">
       <c r="A9" s="19" t="s">
         <v>61</v>
       </c>
@@ -3321,7 +3325,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:52" ht="42.75">
+    <row r="12" spans="1:52" ht="41.4">
       <c r="A12" s="11" t="s">
         <v>260</v>
       </c>
@@ -3465,7 +3469,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:52" ht="42.75">
+    <row r="13" spans="1:52" ht="41.4">
       <c r="A13" s="11" t="s">
         <v>262</v>
       </c>
@@ -3609,7 +3613,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:52" ht="28.5">
+    <row r="14" spans="1:52" ht="27.6">
       <c r="A14" s="11" t="s">
         <v>264</v>
       </c>
@@ -3753,7 +3757,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:52" ht="42.75">
+    <row r="15" spans="1:52" ht="41.4">
       <c r="A15" s="11" t="s">
         <v>265</v>
       </c>
@@ -4043,7 +4047,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:51" ht="28.5">
+    <row r="17" spans="1:51" ht="27.6">
       <c r="A17" s="11" t="s">
         <v>268</v>
       </c>
@@ -4189,7 +4193,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:51" ht="28.5">
+    <row r="18" spans="1:51" ht="27.6">
       <c r="A18" s="11" t="s">
         <v>270</v>
       </c>
@@ -4333,7 +4337,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:51" ht="42.75">
+    <row r="19" spans="1:51" ht="41.4">
       <c r="A19" s="11" t="s">
         <v>271</v>
       </c>
@@ -4477,7 +4481,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:51" ht="128.25">
+    <row r="20" spans="1:51" ht="138">
       <c r="A20" s="28" t="s">
         <v>80</v>
       </c>
@@ -4621,7 +4625,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:51" ht="85.5">
+    <row r="21" spans="1:51" ht="82.8">
       <c r="A21" s="28" t="s">
         <v>82</v>
       </c>
@@ -4765,7 +4769,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="85.5">
+    <row r="22" spans="1:51" ht="82.8">
       <c r="A22" s="28" t="s">
         <v>84</v>
       </c>
@@ -4906,7 +4910,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:51" ht="28.5">
+    <row r="23" spans="1:51" ht="27.6">
       <c r="A23" s="5" t="s">
         <v>86</v>
       </c>
@@ -5050,7 +5054,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:51" ht="71.25">
+    <row r="24" spans="1:51" ht="69">
       <c r="A24" s="5" t="s">
         <v>88</v>
       </c>
@@ -5194,7 +5198,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:51" ht="71.25">
+    <row r="25" spans="1:51" ht="82.8">
       <c r="A25" s="5" t="s">
         <v>90</v>
       </c>
@@ -5338,7 +5342,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:51" ht="42.75">
+    <row r="26" spans="1:51" ht="41.4">
       <c r="A26" s="5" t="s">
         <v>92</v>
       </c>
@@ -5482,7 +5486,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:51" ht="42.75">
+    <row r="27" spans="1:51" ht="41.4">
       <c r="A27" s="5" t="s">
         <v>94</v>
       </c>
@@ -5626,7 +5630,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="42.75">
+    <row r="28" spans="1:51" ht="41.4">
       <c r="A28" s="5" t="s">
         <v>96</v>
       </c>
@@ -5770,7 +5774,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:51" ht="42.75">
+    <row r="29" spans="1:51" ht="41.4">
       <c r="A29" s="5" t="s">
         <v>98</v>
       </c>
@@ -5914,7 +5918,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:51" ht="42.75">
+    <row r="30" spans="1:51" ht="41.4">
       <c r="A30" s="5" t="s">
         <v>100</v>
       </c>
@@ -6060,7 +6064,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:51" ht="71.25">
+    <row r="31" spans="1:51" ht="69">
       <c r="A31" s="5" t="s">
         <v>102</v>
       </c>
@@ -6886,7 +6890,7 @@
         <v>37</v>
       </c>
       <c r="AP36" s="15">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="AQ36" s="15" t="s">
         <v>76</v>
@@ -6916,7 +6920,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:51" ht="57">
+    <row r="37" spans="1:51" ht="55.2">
       <c r="A37" s="37" t="s">
         <v>76</v>
       </c>
@@ -7202,7 +7206,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:51" ht="28.5">
+    <row r="39" spans="1:51" ht="27.6">
       <c r="A39" s="38" t="s">
         <v>110</v>
       </c>
@@ -7344,7 +7348,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:51" ht="71.25">
+    <row r="40" spans="1:51" ht="69">
       <c r="A40" s="40" t="s">
         <v>112</v>
       </c>
@@ -7485,7 +7489,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:51" ht="57">
+    <row r="41" spans="1:51" ht="55.2">
       <c r="A41" s="40" t="s">
         <v>114</v>
       </c>
@@ -7626,7 +7630,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:51" ht="99.75">
+    <row r="42" spans="1:51" ht="110.4">
       <c r="A42" s="42" t="s">
         <v>116</v>
       </c>
@@ -7768,7 +7772,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:51" ht="71.25">
+    <row r="43" spans="1:51" ht="69">
       <c r="A43" s="43" t="s">
         <v>119</v>
       </c>
@@ -7910,7 +7914,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:51" ht="42.75">
+    <row r="44" spans="1:51" ht="41.4">
       <c r="A44" s="11" t="s">
         <v>272</v>
       </c>
@@ -8054,7 +8058,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:51" ht="57">
+    <row r="45" spans="1:51" ht="55.2">
       <c r="A45" s="29" t="s">
         <v>124</v>
       </c>
@@ -8198,7 +8202,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:51" ht="42.75">
+    <row r="46" spans="1:51" ht="41.4">
       <c r="A46" s="29" t="s">
         <v>126</v>
       </c>
@@ -8342,7 +8346,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:51" ht="28.5">
+    <row r="47" spans="1:51" ht="41.4">
       <c r="A47" s="29" t="s">
         <v>128</v>
       </c>
@@ -8630,7 +8634,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:51" ht="42.75">
+    <row r="49" spans="1:51" ht="41.4">
       <c r="A49" s="11" t="s">
         <v>273</v>
       </c>
@@ -8774,7 +8778,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:51" ht="28.5">
+    <row r="50" spans="1:51" ht="27.6">
       <c r="A50" s="11" t="s">
         <v>274</v>
       </c>
@@ -8918,7 +8922,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:51" ht="71.25">
+    <row r="51" spans="1:51" ht="82.8">
       <c r="A51" s="11" t="s">
         <v>276</v>
       </c>
@@ -9062,7 +9066,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:51" ht="42.75">
+    <row r="52" spans="1:51" ht="41.4">
       <c r="A52" s="11" t="s">
         <v>278</v>
       </c>
@@ -9350,7 +9354,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:51" ht="71.25">
+    <row r="54" spans="1:51" ht="82.8">
       <c r="A54" s="11" t="s">
         <v>281</v>
       </c>
@@ -9460,14 +9464,14 @@
       <c r="AN54" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="AO54" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="AP54" s="15" t="s">
-        <v>36</v>
+      <c r="AO54" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP54" s="15">
+        <v>45</v>
       </c>
       <c r="AQ54" s="15" t="s">
-        <v>36</v>
+        <v>319</v>
       </c>
       <c r="AR54" s="16" t="s">
         <v>35</v>
@@ -9494,7 +9498,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:51" ht="42.75">
+    <row r="55" spans="1:51" ht="41.4">
       <c r="A55" s="11" t="s">
         <v>283</v>
       </c>
@@ -9638,7 +9642,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:51">
+    <row r="56" spans="1:51" ht="27.6">
       <c r="A56" s="29" t="s">
         <v>136</v>
       </c>
@@ -9782,7 +9786,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:51" ht="28.5">
+    <row r="57" spans="1:51" ht="27.6">
       <c r="A57" s="19" t="s">
         <v>138</v>
       </c>
@@ -10070,7 +10074,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:51" ht="28.5">
+    <row r="59" spans="1:51" ht="27.6">
       <c r="A59" s="19" t="s">
         <v>142</v>
       </c>
@@ -10214,7 +10218,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="1:51" ht="28.5">
+    <row r="60" spans="1:51" ht="27.6">
       <c r="A60" s="19" t="s">
         <v>144</v>
       </c>
@@ -10500,7 +10504,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:51" ht="99.75">
+    <row r="62" spans="1:51" ht="110.4">
       <c r="A62" s="11" t="s">
         <v>284</v>
       </c>
@@ -10646,7 +10650,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:51" ht="99.75">
+    <row r="63" spans="1:51" ht="110.4">
       <c r="A63" s="11" t="s">
         <v>286</v>
       </c>
@@ -10792,7 +10796,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:51" ht="57">
+    <row r="64" spans="1:51" ht="69">
       <c r="A64" s="11" t="s">
         <v>287</v>
       </c>
@@ -10938,7 +10942,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:51" ht="57">
+    <row r="65" spans="1:51" ht="69">
       <c r="A65" s="11" t="s">
         <v>289</v>
       </c>
@@ -11084,7 +11088,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:51" ht="57">
+    <row r="66" spans="1:51" ht="55.2">
       <c r="A66" s="4" t="s">
         <v>290</v>
       </c>
@@ -11230,7 +11234,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="1:51" ht="57">
+    <row r="67" spans="1:51" ht="55.2">
       <c r="A67" s="4" t="s">
         <v>292</v>
       </c>
@@ -11376,7 +11380,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:51" ht="28.5">
+    <row r="68" spans="1:51" ht="27.6">
       <c r="A68" s="11" t="s">
         <v>293</v>
       </c>
@@ -11524,7 +11528,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:51" ht="57">
+    <row r="69" spans="1:51" ht="55.2">
       <c r="A69" s="11" t="s">
         <v>294</v>
       </c>
@@ -11670,7 +11674,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:51" ht="57">
+    <row r="70" spans="1:51" ht="55.2">
       <c r="A70" s="11" t="s">
         <v>295</v>
       </c>
@@ -11814,7 +11818,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:51" ht="42.75">
+    <row r="71" spans="1:51" ht="41.4">
       <c r="A71" s="17" t="s">
         <v>156</v>
       </c>
@@ -11958,7 +11962,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:51" ht="42.75">
+    <row r="72" spans="1:51" ht="41.4">
       <c r="A72" s="17" t="s">
         <v>158</v>
       </c>
@@ -12104,7 +12108,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:51" ht="42.75">
+    <row r="73" spans="1:51" ht="41.4">
       <c r="A73" s="19" t="s">
         <v>160</v>
       </c>
@@ -12250,7 +12254,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:51" ht="57">
+    <row r="74" spans="1:51" ht="69">
       <c r="A74" s="19" t="s">
         <v>162</v>
       </c>
@@ -12394,7 +12398,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:51" ht="28.5">
+    <row r="75" spans="1:51" ht="27.6">
       <c r="A75" s="19" t="s">
         <v>164</v>
       </c>
@@ -12538,7 +12542,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:51" ht="71.25">
+    <row r="76" spans="1:51" ht="69">
       <c r="A76" s="19" t="s">
         <v>166</v>
       </c>
@@ -12682,7 +12686,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:51" ht="85.5">
+    <row r="77" spans="1:51" ht="82.8">
       <c r="A77" s="37" t="s">
         <v>168</v>
       </c>
@@ -12826,7 +12830,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="78" spans="1:51" ht="57">
+    <row r="78" spans="1:51" ht="69">
       <c r="A78" s="11" t="s">
         <v>296</v>
       </c>
@@ -12972,7 +12976,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:51" ht="28.5">
+    <row r="79" spans="1:51" ht="27.6">
       <c r="A79" s="11" t="s">
         <v>297</v>
       </c>
@@ -13118,7 +13122,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:51" ht="42.75">
+    <row r="80" spans="1:51" ht="41.4">
       <c r="A80" s="11" t="s">
         <v>298</v>
       </c>
@@ -13264,7 +13268,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="81" spans="1:51" ht="128.25">
+    <row r="81" spans="1:51" ht="138">
       <c r="A81" s="17" t="s">
         <v>176</v>
       </c>
@@ -13410,7 +13414,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:51" ht="28.5">
+    <row r="82" spans="1:51" ht="27.6">
       <c r="A82" s="51" t="s">
         <v>178</v>
       </c>
@@ -13555,7 +13559,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="83" spans="1:51" ht="42.75">
+    <row r="83" spans="1:51" ht="41.4">
       <c r="A83" s="19" t="s">
         <v>181</v>
       </c>
@@ -13703,7 +13707,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:51" ht="42.75">
+    <row r="84" spans="1:51" ht="41.4">
       <c r="A84" s="19" t="s">
         <v>317</v>
       </c>
@@ -13851,7 +13855,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:51" ht="42.75">
+    <row r="85" spans="1:51" ht="41.4">
       <c r="A85" s="7" t="s">
         <v>183</v>
       </c>
@@ -14000,7 +14004,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="86" spans="1:51" ht="42.75">
+    <row r="86" spans="1:51" ht="41.4">
       <c r="A86" s="7"/>
       <c r="B86" s="11" t="s">
         <v>301</v>
@@ -14147,7 +14151,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="87" spans="1:51" ht="71.25">
+    <row r="87" spans="1:51" ht="69">
       <c r="A87" s="11" t="s">
         <v>303</v>
       </c>
@@ -14291,7 +14295,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="88" spans="1:51" ht="57">
+    <row r="88" spans="1:51" ht="55.2">
       <c r="A88" s="29" t="s">
         <v>188</v>
       </c>
@@ -14440,7 +14444,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="89" spans="1:51">
+    <row r="89" spans="1:51" ht="27.6">
       <c r="A89" s="29"/>
       <c r="B89" s="29" t="s">
         <v>188</v>
@@ -14513,7 +14517,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="90" spans="1:51" ht="57">
+    <row r="90" spans="1:51" ht="55.2">
       <c r="A90" s="19" t="s">
         <v>194</v>
       </c>
@@ -14660,7 +14664,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="91" spans="1:51" ht="71.25">
+    <row r="91" spans="1:51" ht="69">
       <c r="A91" s="29" t="s">
         <v>197</v>
       </c>
@@ -14807,7 +14811,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="92" spans="1:51" ht="42.75">
+    <row r="92" spans="1:51" ht="41.4">
       <c r="A92" s="19" t="s">
         <v>200</v>
       </c>
@@ -14953,7 +14957,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="93" spans="1:51" ht="42.75">
+    <row r="93" spans="1:51" ht="41.4">
       <c r="A93" s="19"/>
       <c r="B93" s="19" t="s">
         <v>200</v>
@@ -15097,7 +15101,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="94" spans="1:51" ht="57">
+    <row r="94" spans="1:51" ht="55.2">
       <c r="A94" s="37" t="s">
         <v>204</v>
       </c>
@@ -15246,7 +15250,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:51" ht="42.75">
+    <row r="95" spans="1:51" ht="41.4">
       <c r="A95" s="37" t="s">
         <v>208</v>
       </c>
@@ -15395,7 +15399,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="96" spans="1:51" ht="85.5">
+    <row r="96" spans="1:51" ht="110.4">
       <c r="A96" s="37" t="s">
         <v>212</v>
       </c>
@@ -15541,7 +15545,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="97" spans="1:51" ht="28.5">
+    <row r="97" spans="1:51" ht="27.6">
       <c r="A97" s="56"/>
       <c r="B97" s="19" t="s">
         <v>212</v>
@@ -15683,7 +15687,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="98" spans="1:51" ht="42.75">
+    <row r="98" spans="1:51" ht="41.4">
       <c r="A98" s="56" t="s">
         <v>216</v>
       </c>
@@ -15974,7 +15978,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="100" spans="1:51" ht="28.5">
+    <row r="100" spans="1:51" ht="27.6">
       <c r="A100" s="56" t="s">
         <v>223</v>
       </c>
@@ -16116,7 +16120,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="101" spans="1:51" ht="57">
+    <row r="101" spans="1:51" ht="55.2">
       <c r="A101" s="56" t="s">
         <v>225</v>
       </c>
@@ -16263,7 +16267,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="102" spans="1:51" ht="114">
+    <row r="102" spans="1:51" ht="124.2">
       <c r="A102" s="56" t="s">
         <v>228</v>
       </c>
@@ -16407,7 +16411,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="103" spans="1:51" ht="42.75">
+    <row r="103" spans="1:51" ht="41.4">
       <c r="A103" s="11" t="s">
         <v>305</v>
       </c>
@@ -16551,7 +16555,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:51" ht="71.25">
+    <row r="104" spans="1:51" ht="69">
       <c r="A104" s="4" t="s">
         <v>307</v>
       </c>
@@ -16694,7 +16698,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="1:51" ht="71.25">
+    <row r="105" spans="1:51" ht="69">
       <c r="A105" s="11" t="s">
         <v>309</v>
       </c>
@@ -16838,7 +16842,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="106" spans="1:51" ht="57">
+    <row r="106" spans="1:51" ht="55.2">
       <c r="A106" s="11" t="s">
         <v>310</v>
       </c>
@@ -16984,7 +16988,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="107" spans="1:51" ht="57">
+    <row r="107" spans="1:51" ht="55.2">
       <c r="A107" s="17"/>
       <c r="B107" s="60" t="s">
         <v>235</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{319947B9-F6C4-49E9-ADE9-5A258D4D69B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF1CEFE-2688-4B97-ADCC-505E54391E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3810" yWindow="3810" windowWidth="28800" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4392" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4391" uniqueCount="320">
   <si>
     <t>ExtraInfo</t>
   </si>
@@ -1671,42 +1671,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AZ109"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" style="4" customWidth="1"/>
-    <col min="2" max="3" width="11.33203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.109375" style="27" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10.88671875" style="4" customWidth="1"/>
-    <col min="12" max="12" width="13.109375" style="4" customWidth="1"/>
+    <col min="1" max="1" width="28.625" style="4" customWidth="1"/>
+    <col min="2" max="3" width="11.375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="28.125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="10.25" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="6.875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="7.875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="10.875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="13.125" style="4" customWidth="1"/>
     <col min="13" max="22" width="19" style="4" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" style="4" customWidth="1"/>
-    <col min="24" max="24" width="10.109375" style="4" customWidth="1"/>
-    <col min="25" max="26" width="12.44140625" style="4" customWidth="1"/>
-    <col min="27" max="27" width="8.6640625" style="4"/>
-    <col min="28" max="28" width="12.21875" style="4" customWidth="1"/>
-    <col min="29" max="36" width="8.6640625" style="15"/>
-    <col min="37" max="37" width="11.6640625" style="15" customWidth="1"/>
-    <col min="38" max="38" width="9.21875" style="15" customWidth="1"/>
+    <col min="23" max="23" width="8.625" style="4" customWidth="1"/>
+    <col min="24" max="24" width="10.125" style="4" customWidth="1"/>
+    <col min="25" max="26" width="12.5" style="4" customWidth="1"/>
+    <col min="27" max="27" width="8.625" style="4"/>
+    <col min="28" max="28" width="12.25" style="4" customWidth="1"/>
+    <col min="29" max="36" width="8.625" style="15"/>
+    <col min="37" max="37" width="11.625" style="15" customWidth="1"/>
+    <col min="38" max="38" width="9.25" style="15" customWidth="1"/>
     <col min="39" max="39" width="12" style="15" customWidth="1"/>
-    <col min="40" max="40" width="11.77734375" style="15" customWidth="1"/>
-    <col min="41" max="41" width="8.6640625" style="15" customWidth="1"/>
-    <col min="42" max="42" width="9.21875" style="15" customWidth="1"/>
-    <col min="43" max="43" width="14.44140625" style="15" customWidth="1"/>
-    <col min="44" max="44" width="12.6640625" style="15" customWidth="1"/>
+    <col min="40" max="40" width="11.75" style="15" customWidth="1"/>
+    <col min="41" max="41" width="8.625" style="15" customWidth="1"/>
+    <col min="42" max="42" width="9.25" style="15" customWidth="1"/>
+    <col min="43" max="43" width="14.5" style="15" customWidth="1"/>
+    <col min="44" max="44" width="12.625" style="15" customWidth="1"/>
     <col min="45" max="45" width="11" style="15" customWidth="1"/>
-    <col min="46" max="46" width="12.33203125" style="15" customWidth="1"/>
-    <col min="47" max="47" width="10.21875" style="15" customWidth="1"/>
-    <col min="48" max="48" width="11.6640625" style="15" customWidth="1"/>
-    <col min="49" max="49" width="10.109375" style="15" customWidth="1"/>
-    <col min="50" max="50" width="16.109375" style="15" customWidth="1"/>
-    <col min="51" max="51" width="14.77734375" style="4" customWidth="1"/>
-    <col min="52" max="52" width="8.6640625" style="15"/>
+    <col min="46" max="46" width="12.375" style="15" customWidth="1"/>
+    <col min="47" max="47" width="10.25" style="15" customWidth="1"/>
+    <col min="48" max="48" width="11.625" style="15" customWidth="1"/>
+    <col min="49" max="49" width="10.125" style="15" customWidth="1"/>
+    <col min="50" max="50" width="16.125" style="15" customWidth="1"/>
+    <col min="51" max="51" width="14.75" style="4" customWidth="1"/>
+    <col min="52" max="52" width="8.625" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:52" s="62" customFormat="1" ht="15.75" customHeight="1">
@@ -2449,7 +2449,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:52" ht="82.8">
+    <row r="6" spans="1:52" ht="85.5">
       <c r="A6" s="17" t="s">
         <v>50</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="82.8">
+    <row r="7" spans="1:52" ht="85.5">
       <c r="A7" s="17" t="s">
         <v>55</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:52" ht="27.6">
+    <row r="8" spans="1:52" ht="28.5">
       <c r="A8" s="19" t="s">
         <v>56</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:52" ht="27.6">
+    <row r="9" spans="1:52" ht="28.5">
       <c r="A9" s="19" t="s">
         <v>61</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:52" ht="41.4">
+    <row r="12" spans="1:52" ht="42.75">
       <c r="A12" s="11" t="s">
         <v>260</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:52" ht="41.4">
+    <row r="13" spans="1:52" ht="42.75">
       <c r="A13" s="11" t="s">
         <v>262</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:52" ht="27.6">
+    <row r="14" spans="1:52" ht="28.5">
       <c r="A14" s="11" t="s">
         <v>264</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:52" ht="41.4">
+    <row r="15" spans="1:52" ht="42.75">
       <c r="A15" s="11" t="s">
         <v>265</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:51" ht="27.6">
+    <row r="17" spans="1:51" ht="28.5">
       <c r="A17" s="11" t="s">
         <v>268</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:51" ht="27.6">
+    <row r="18" spans="1:51" ht="28.5">
       <c r="A18" s="11" t="s">
         <v>270</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:51" ht="41.4">
+    <row r="19" spans="1:51" ht="42.75">
       <c r="A19" s="11" t="s">
         <v>271</v>
       </c>
@@ -4481,7 +4481,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:51" ht="138">
+    <row r="20" spans="1:51" ht="128.25">
       <c r="A20" s="28" t="s">
         <v>80</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:51" ht="82.8">
+    <row r="21" spans="1:51" ht="85.5">
       <c r="A21" s="28" t="s">
         <v>82</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="82.8">
+    <row r="22" spans="1:51" ht="85.5">
       <c r="A22" s="28" t="s">
         <v>84</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="23" spans="1:51" ht="27.6">
+    <row r="23" spans="1:51" ht="28.5">
       <c r="A23" s="5" t="s">
         <v>86</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:51" ht="69">
+    <row r="24" spans="1:51" ht="71.25">
       <c r="A24" s="5" t="s">
         <v>88</v>
       </c>
@@ -5198,7 +5198,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:51" ht="82.8">
+    <row r="25" spans="1:51" ht="71.25">
       <c r="A25" s="5" t="s">
         <v>90</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:51" ht="41.4">
+    <row r="26" spans="1:51" ht="42.75">
       <c r="A26" s="5" t="s">
         <v>92</v>
       </c>
@@ -5486,7 +5486,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:51" ht="41.4">
+    <row r="27" spans="1:51" ht="42.75">
       <c r="A27" s="5" t="s">
         <v>94</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:51" ht="41.4">
+    <row r="28" spans="1:51" ht="42.75">
       <c r="A28" s="5" t="s">
         <v>96</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:51" ht="41.4">
+    <row r="29" spans="1:51" ht="42.75">
       <c r="A29" s="5" t="s">
         <v>98</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:51" ht="41.4">
+    <row r="30" spans="1:51" ht="42.75">
       <c r="A30" s="5" t="s">
         <v>100</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:51" ht="69">
+    <row r="31" spans="1:51" ht="71.25">
       <c r="A31" s="5" t="s">
         <v>102</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:51" ht="55.2">
+    <row r="37" spans="1:51" ht="57">
       <c r="A37" s="37" t="s">
         <v>76</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:51" ht="27.6">
+    <row r="39" spans="1:51" ht="28.5">
       <c r="A39" s="38" t="s">
         <v>110</v>
       </c>
@@ -7348,7 +7348,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:51" ht="69">
+    <row r="40" spans="1:51" ht="71.25">
       <c r="A40" s="40" t="s">
         <v>112</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:51" ht="55.2">
+    <row r="41" spans="1:51" ht="57">
       <c r="A41" s="40" t="s">
         <v>114</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:51" ht="110.4">
+    <row r="42" spans="1:51" ht="99.75">
       <c r="A42" s="42" t="s">
         <v>116</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:51" ht="69">
+    <row r="43" spans="1:51" ht="71.25">
       <c r="A43" s="43" t="s">
         <v>119</v>
       </c>
@@ -7914,7 +7914,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:51" ht="41.4">
+    <row r="44" spans="1:51" ht="42.75">
       <c r="A44" s="11" t="s">
         <v>272</v>
       </c>
@@ -8058,7 +8058,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:51" ht="55.2">
+    <row r="45" spans="1:51" ht="57">
       <c r="A45" s="29" t="s">
         <v>124</v>
       </c>
@@ -8202,7 +8202,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:51" ht="41.4">
+    <row r="46" spans="1:51" ht="42.75">
       <c r="A46" s="29" t="s">
         <v>126</v>
       </c>
@@ -8346,7 +8346,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:51" ht="41.4">
+    <row r="47" spans="1:51" ht="28.5">
       <c r="A47" s="29" t="s">
         <v>128</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:51" ht="41.4">
+    <row r="49" spans="1:51" ht="42.75">
       <c r="A49" s="11" t="s">
         <v>273</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="50" spans="1:51" ht="27.6">
+    <row r="50" spans="1:51" ht="28.5">
       <c r="A50" s="11" t="s">
         <v>274</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="51" spans="1:51" ht="82.8">
+    <row r="51" spans="1:51" ht="71.25">
       <c r="A51" s="11" t="s">
         <v>276</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:51" ht="41.4">
+    <row r="52" spans="1:51" ht="42.75">
       <c r="A52" s="11" t="s">
         <v>278</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="1:51" ht="82.8">
+    <row r="54" spans="1:51" ht="71.25">
       <c r="A54" s="11" t="s">
         <v>281</v>
       </c>
@@ -9498,7 +9498,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="55" spans="1:51" ht="41.4">
+    <row r="55" spans="1:51" ht="42.75">
       <c r="A55" s="11" t="s">
         <v>283</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="56" spans="1:51" ht="27.6">
+    <row r="56" spans="1:51">
       <c r="A56" s="29" t="s">
         <v>136</v>
       </c>
@@ -9786,7 +9786,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="1:51" ht="27.6">
+    <row r="57" spans="1:51" ht="28.5">
       <c r="A57" s="19" t="s">
         <v>138</v>
       </c>
@@ -10074,7 +10074,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="59" spans="1:51" ht="27.6">
+    <row r="59" spans="1:51" ht="28.5">
       <c r="A59" s="19" t="s">
         <v>142</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="1:51" ht="27.6">
+    <row r="60" spans="1:51" ht="28.5">
       <c r="A60" s="19" t="s">
         <v>144</v>
       </c>
@@ -10504,7 +10504,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:51" ht="110.4">
+    <row r="62" spans="1:51" ht="99.75">
       <c r="A62" s="11" t="s">
         <v>284</v>
       </c>
@@ -10650,7 +10650,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:51" ht="110.4">
+    <row r="63" spans="1:51" ht="99.75">
       <c r="A63" s="11" t="s">
         <v>286</v>
       </c>
@@ -10796,7 +10796,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:51" ht="69">
+    <row r="64" spans="1:51" ht="57">
       <c r="A64" s="11" t="s">
         <v>287</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:51" ht="69">
+    <row r="65" spans="1:51" ht="57">
       <c r="A65" s="11" t="s">
         <v>289</v>
       </c>
@@ -11088,7 +11088,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:51" ht="55.2">
+    <row r="66" spans="1:51" ht="57">
       <c r="A66" s="4" t="s">
         <v>290</v>
       </c>
@@ -11234,7 +11234,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="1:51" ht="55.2">
+    <row r="67" spans="1:51" ht="57">
       <c r="A67" s="4" t="s">
         <v>292</v>
       </c>
@@ -11380,7 +11380,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:51" ht="27.6">
+    <row r="68" spans="1:51" ht="28.5">
       <c r="A68" s="11" t="s">
         <v>293</v>
       </c>
@@ -11528,7 +11528,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:51" ht="55.2">
+    <row r="69" spans="1:51" ht="57">
       <c r="A69" s="11" t="s">
         <v>294</v>
       </c>
@@ -11674,7 +11674,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:51" ht="55.2">
+    <row r="70" spans="1:51" ht="57">
       <c r="A70" s="11" t="s">
         <v>295</v>
       </c>
@@ -11818,7 +11818,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:51" ht="41.4">
+    <row r="71" spans="1:51" ht="42.75">
       <c r="A71" s="17" t="s">
         <v>156</v>
       </c>
@@ -11962,7 +11962,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:51" ht="41.4">
+    <row r="72" spans="1:51" ht="42.75">
       <c r="A72" s="17" t="s">
         <v>158</v>
       </c>
@@ -12108,7 +12108,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="73" spans="1:51" ht="41.4">
+    <row r="73" spans="1:51" ht="42.75">
       <c r="A73" s="19" t="s">
         <v>160</v>
       </c>
@@ -12254,7 +12254,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:51" ht="69">
+    <row r="74" spans="1:51" ht="57">
       <c r="A74" s="19" t="s">
         <v>162</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="75" spans="1:51" ht="27.6">
+    <row r="75" spans="1:51" ht="28.5">
       <c r="A75" s="19" t="s">
         <v>164</v>
       </c>
@@ -12542,7 +12542,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="76" spans="1:51" ht="69">
+    <row r="76" spans="1:51" ht="71.25">
       <c r="A76" s="19" t="s">
         <v>166</v>
       </c>
@@ -12686,7 +12686,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="77" spans="1:51" ht="82.8">
+    <row r="77" spans="1:51" ht="85.5">
       <c r="A77" s="37" t="s">
         <v>168</v>
       </c>
@@ -12830,7 +12830,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="78" spans="1:51" ht="69">
+    <row r="78" spans="1:51" ht="57">
       <c r="A78" s="11" t="s">
         <v>296</v>
       </c>
@@ -12976,7 +12976,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" spans="1:51" ht="27.6">
+    <row r="79" spans="1:51" ht="28.5">
       <c r="A79" s="11" t="s">
         <v>297</v>
       </c>
@@ -13122,7 +13122,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:51" ht="41.4">
+    <row r="80" spans="1:51" ht="42.75">
       <c r="A80" s="11" t="s">
         <v>298</v>
       </c>
@@ -13268,7 +13268,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="81" spans="1:51" ht="138">
+    <row r="81" spans="1:51" ht="128.25">
       <c r="A81" s="17" t="s">
         <v>176</v>
       </c>
@@ -13414,7 +13414,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:51" ht="27.6">
+    <row r="82" spans="1:51" ht="28.5">
       <c r="A82" s="51" t="s">
         <v>178</v>
       </c>
@@ -13559,7 +13559,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="83" spans="1:51" ht="41.4">
+    <row r="83" spans="1:51" ht="42.75">
       <c r="A83" s="19" t="s">
         <v>181</v>
       </c>
@@ -13707,7 +13707,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="84" spans="1:51" ht="41.4">
+    <row r="84" spans="1:51" ht="42.75">
       <c r="A84" s="19" t="s">
         <v>317</v>
       </c>
@@ -13855,7 +13855,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="85" spans="1:51" ht="41.4">
+    <row r="85" spans="1:51" ht="42.75">
       <c r="A85" s="7" t="s">
         <v>183</v>
       </c>
@@ -14004,7 +14004,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="86" spans="1:51" ht="41.4">
+    <row r="86" spans="1:51" ht="42.75">
       <c r="A86" s="7"/>
       <c r="B86" s="11" t="s">
         <v>301</v>
@@ -14151,7 +14151,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="87" spans="1:51" ht="69">
+    <row r="87" spans="1:51" ht="71.25">
       <c r="A87" s="11" t="s">
         <v>303</v>
       </c>
@@ -14295,7 +14295,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="88" spans="1:51" ht="55.2">
+    <row r="88" spans="1:51" ht="57">
       <c r="A88" s="29" t="s">
         <v>188</v>
       </c>
@@ -14444,7 +14444,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="89" spans="1:51" ht="27.6">
+    <row r="89" spans="1:51">
       <c r="A89" s="29"/>
       <c r="B89" s="29" t="s">
         <v>188</v>
@@ -14517,7 +14517,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="90" spans="1:51" ht="55.2">
+    <row r="90" spans="1:51" ht="57">
       <c r="A90" s="19" t="s">
         <v>194</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="91" spans="1:51" ht="69">
+    <row r="91" spans="1:51" ht="71.25">
       <c r="A91" s="29" t="s">
         <v>197</v>
       </c>
@@ -14811,7 +14811,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="92" spans="1:51" ht="41.4">
+    <row r="92" spans="1:51" ht="42.75">
       <c r="A92" s="19" t="s">
         <v>200</v>
       </c>
@@ -14957,7 +14957,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="93" spans="1:51" ht="41.4">
+    <row r="93" spans="1:51" ht="42.75">
       <c r="A93" s="19"/>
       <c r="B93" s="19" t="s">
         <v>200</v>
@@ -15101,7 +15101,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="94" spans="1:51" ht="55.2">
+    <row r="94" spans="1:51" ht="57">
       <c r="A94" s="37" t="s">
         <v>204</v>
       </c>
@@ -15250,7 +15250,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:51" ht="41.4">
+    <row r="95" spans="1:51" ht="42.75">
       <c r="A95" s="37" t="s">
         <v>208</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="96" spans="1:51" ht="110.4">
+    <row r="96" spans="1:51" ht="85.5">
       <c r="A96" s="37" t="s">
         <v>212</v>
       </c>
@@ -15545,7 +15545,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="97" spans="1:51" ht="27.6">
+    <row r="97" spans="1:51" ht="28.5">
       <c r="A97" s="56"/>
       <c r="B97" s="19" t="s">
         <v>212</v>
@@ -15687,7 +15687,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="98" spans="1:51" ht="41.4">
+    <row r="98" spans="1:51" ht="42.75">
       <c r="A98" s="56" t="s">
         <v>216</v>
       </c>
@@ -15978,7 +15978,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="100" spans="1:51" ht="27.6">
+    <row r="100" spans="1:51" ht="28.5">
       <c r="A100" s="56" t="s">
         <v>223</v>
       </c>
@@ -16038,8 +16038,11 @@
       <c r="W100" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="X100" s="14" t="s">
-        <v>35</v>
+      <c r="X100" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y100" s="4">
+        <v>6</v>
       </c>
       <c r="Z100" s="14" t="s">
         <v>35</v>
@@ -16120,7 +16123,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="101" spans="1:51" ht="55.2">
+    <row r="101" spans="1:51" ht="57">
       <c r="A101" s="56" t="s">
         <v>225</v>
       </c>
@@ -16267,7 +16270,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="102" spans="1:51" ht="124.2">
+    <row r="102" spans="1:51" ht="114">
       <c r="A102" s="56" t="s">
         <v>228</v>
       </c>
@@ -16411,7 +16414,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="103" spans="1:51" ht="41.4">
+    <row r="103" spans="1:51" ht="42.75">
       <c r="A103" s="11" t="s">
         <v>305</v>
       </c>
@@ -16555,7 +16558,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="104" spans="1:51" ht="69">
+    <row r="104" spans="1:51" ht="71.25">
       <c r="A104" s="4" t="s">
         <v>307</v>
       </c>
@@ -16698,7 +16701,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="1:51" ht="69">
+    <row r="105" spans="1:51" ht="71.25">
       <c r="A105" s="11" t="s">
         <v>309</v>
       </c>
@@ -16842,7 +16845,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="106" spans="1:51" ht="55.2">
+    <row r="106" spans="1:51" ht="57">
       <c r="A106" s="11" t="s">
         <v>310</v>
       </c>
@@ -16988,7 +16991,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="107" spans="1:51" ht="55.2">
+    <row r="107" spans="1:51" ht="57">
       <c r="A107" s="17"/>
       <c r="B107" s="60" t="s">
         <v>235</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE3CB81-65E4-4125-B43A-61F5F7FFDAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F155AF5-8690-4B5D-A67A-C0AF5F050EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -774,9 +774,6 @@
     <t>已点燃</t>
   </si>
   <si>
-    <t xml:space="preserve"> 数据传输台</t>
-  </si>
-  <si>
     <t>数据传输台</t>
   </si>
   <si>
@@ -1039,6 +1036,10 @@
   </si>
   <si>
     <t>DemolitionDebris</t>
+    <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据传输台</t>
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
@@ -1781,70 +1782,70 @@
   <sheetData>
     <row r="1" spans="1:56" s="68" customFormat="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="W1" s="4" t="s">
         <v>1</v>
@@ -1931,7 +1932,7 @@
         <v>28</v>
       </c>
       <c r="AY1" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AZ1" s="5" t="s">
         <v>29</v>
@@ -2759,13 +2760,13 @@
         <v>59</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E7" s="9">
         <v>3</v>
@@ -3561,14 +3562,14 @@
     </row>
     <row r="12" spans="1:56" ht="42.75">
       <c r="A12" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="18" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -3720,10 +3721,10 @@
     </row>
     <row r="13" spans="1:56" ht="28.5">
       <c r="A13" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="29" t="s">
@@ -3879,14 +3880,14 @@
     </row>
     <row r="14" spans="1:56" ht="42.75">
       <c r="A14" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E14" s="4">
         <v>3</v>
@@ -4038,10 +4039,10 @@
     </row>
     <row r="15" spans="1:56">
       <c r="A15" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="29" t="s">
@@ -4199,7 +4200,7 @@
     </row>
     <row r="16" spans="1:56" ht="28.5">
       <c r="A16" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>81</v>
@@ -4208,7 +4209,7 @@
         <v>82</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E16" s="4">
         <v>5</v>
@@ -4360,14 +4361,14 @@
     </row>
     <row r="17" spans="1:56" ht="28.5">
       <c r="A17" s="11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>81</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="18" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E17" s="4">
         <v>6</v>
@@ -4519,10 +4520,10 @@
     </row>
     <row r="18" spans="1:56" ht="42.75">
       <c r="A18" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="29" t="s">
@@ -7380,14 +7381,14 @@
     </row>
     <row r="36" spans="1:56" ht="42.75">
       <c r="A36" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E36" s="4">
         <v>1</v>
@@ -8334,10 +8335,10 @@
     </row>
     <row r="42" spans="1:56" ht="42.75">
       <c r="A42" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B42" s="47" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="29" t="s">
@@ -9129,10 +9130,10 @@
     </row>
     <row r="47" spans="1:56" ht="42.75">
       <c r="A47" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="29" t="s">
@@ -9288,14 +9289,14 @@
     </row>
     <row r="48" spans="1:56" ht="28.5">
       <c r="A48" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E48" s="4">
         <v>2</v>
@@ -9447,14 +9448,14 @@
     </row>
     <row r="49" spans="1:56" ht="71.25">
       <c r="A49" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E49" s="4">
         <v>3</v>
@@ -9606,14 +9607,14 @@
     </row>
     <row r="50" spans="1:56" ht="42.75">
       <c r="A50" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="18" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E50" s="4">
         <v>4</v>
@@ -9765,10 +9766,10 @@
     </row>
     <row r="51" spans="1:56" ht="42.75">
       <c r="A51" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="29" t="s">
@@ -9924,14 +9925,14 @@
     </row>
     <row r="52" spans="1:56" ht="71.25">
       <c r="A52" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="18" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E52" s="4">
         <v>6</v>
@@ -10083,10 +10084,10 @@
     </row>
     <row r="53" spans="1:56" ht="42.75">
       <c r="A53" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="29" t="s">
@@ -11196,16 +11197,16 @@
     </row>
     <row r="60" spans="1:56" ht="99.75">
       <c r="A60" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>157</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E60" s="9">
         <v>0</v>
@@ -11357,16 +11358,16 @@
     </row>
     <row r="61" spans="1:56" ht="99.75">
       <c r="A61" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>82</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E61" s="9">
         <v>1</v>
@@ -11518,16 +11519,16 @@
     </row>
     <row r="62" spans="1:56" ht="57">
       <c r="A62" s="11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>157</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E62" s="9">
         <v>2</v>
@@ -11679,16 +11680,16 @@
     </row>
     <row r="63" spans="1:56" ht="57">
       <c r="A63" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>82</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E63" s="9">
         <v>3</v>
@@ -11840,16 +11841,16 @@
     </row>
     <row r="64" spans="1:56" ht="57">
       <c r="A64" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>157</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E64" s="9">
         <v>4</v>
@@ -12001,16 +12002,16 @@
     </row>
     <row r="65" spans="1:56" ht="57">
       <c r="A65" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>82</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E65" s="9">
         <v>5</v>
@@ -12162,10 +12163,10 @@
     </row>
     <row r="66" spans="1:56" ht="28.5">
       <c r="A66" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>159</v>
@@ -12325,10 +12326,10 @@
     </row>
     <row r="67" spans="1:56" ht="57">
       <c r="A67" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="29" t="s">
@@ -12486,10 +12487,10 @@
     </row>
     <row r="68" spans="1:56" ht="57">
       <c r="A68" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="29" t="s">
@@ -13762,10 +13763,10 @@
     </row>
     <row r="76" spans="1:56" ht="71.25">
       <c r="A76" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="8" t="s">
@@ -13923,10 +13924,10 @@
     </row>
     <row r="77" spans="1:56" ht="28.5">
       <c r="A77" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="29" t="s">
@@ -14084,10 +14085,10 @@
     </row>
     <row r="78" spans="1:56" ht="42.75">
       <c r="A78" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="29" t="s">
@@ -14895,13 +14896,13 @@
         <v>195</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>196</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E83" s="4">
         <v>0</v>
@@ -15057,13 +15058,13 @@
     <row r="84" spans="1:56" ht="42.75">
       <c r="A84" s="7"/>
       <c r="B84" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>199</v>
       </c>
       <c r="D84" s="18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E84" s="4">
         <v>1</v>
@@ -15218,14 +15219,14 @@
     </row>
     <row r="85" spans="1:56" ht="71.25">
       <c r="A85" s="11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E85" s="4">
         <v>2</v>
@@ -17731,16 +17732,16 @@
     </row>
     <row r="103" spans="1:56" ht="114">
       <c r="A103" s="65" t="s">
+        <v>333</v>
+      </c>
+      <c r="B103" s="22" t="s">
         <v>246</v>
-      </c>
-      <c r="B103" s="22" t="s">
-        <v>247</v>
       </c>
       <c r="C103" s="62" t="s">
         <v>196</v>
       </c>
       <c r="D103" s="60" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E103" s="36">
         <v>20</v>
@@ -17872,7 +17873,7 @@
         <v>41</v>
       </c>
       <c r="AY103" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AZ103" s="13" t="s">
         <v>39</v>
@@ -17893,7 +17894,7 @@
     <row r="104" spans="1:56">
       <c r="A104" s="22"/>
       <c r="B104" s="22" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C104" s="62" t="s">
         <v>199</v>
@@ -17946,14 +17947,14 @@
     </row>
     <row r="105" spans="1:56" ht="99.75">
       <c r="A105" s="22" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B105" s="22" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C105" s="64"/>
       <c r="D105" s="60" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E105" s="36">
         <v>22</v>
@@ -18088,7 +18089,7 @@
         <v>41</v>
       </c>
       <c r="AY105" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AZ105" s="13" t="s">
         <v>39</v>
@@ -18109,7 +18110,7 @@
     <row r="106" spans="1:56">
       <c r="A106" s="22"/>
       <c r="B106" s="22" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C106" s="64" t="s">
         <v>245</v>
@@ -18162,20 +18163,20 @@
     </row>
     <row r="107" spans="1:56" ht="42.75">
       <c r="A107" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C107" s="11"/>
       <c r="D107" s="18" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E107" s="9">
         <v>0</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G107" s="11">
         <v>1</v>
@@ -18321,19 +18322,19 @@
     </row>
     <row r="108" spans="1:56" ht="71.25">
       <c r="A108" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D108" s="29" t="s">
         <v>328</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="D108" s="29" t="s">
-        <v>329</v>
       </c>
       <c r="E108" s="9">
         <v>1</v>
       </c>
       <c r="F108" s="53" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G108" s="4">
         <v>10</v>
@@ -18479,20 +18480,20 @@
     </row>
     <row r="109" spans="1:56" ht="71.25">
       <c r="A109" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C109" s="11"/>
       <c r="D109" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E109" s="9">
         <v>2</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G109" s="4">
         <v>5</v>
@@ -18638,22 +18639,22 @@
     </row>
     <row r="110" spans="1:56" ht="57">
       <c r="A110" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C110" s="7" t="s">
         <v>245</v>
       </c>
       <c r="D110" s="18" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E110" s="9">
         <v>3</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G110" s="4">
         <v>1</v>
@@ -18800,17 +18801,17 @@
     <row r="111" spans="1:56" ht="57">
       <c r="A111" s="66"/>
       <c r="B111" s="17" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C111" s="7"/>
       <c r="D111" s="29" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E111" s="9">
         <v>4</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G111" s="4">
         <v>1</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCFE1F9-7AF3-49CF-8378-E0AF85E8B6FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE03921-F9D7-41E2-BFD2-84D4CC775516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1515" yWindow="1515" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4977" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4975" uniqueCount="343">
   <si>
     <t>ExtraInfo</t>
   </si>
@@ -14903,11 +14903,11 @@
       <c r="Y86" s="4">
         <v>3</v>
       </c>
-      <c r="Z86" s="24" t="s">
-        <v>42</v>
+      <c r="Z86" s="24" t="b">
+        <v>0</v>
       </c>
       <c r="AA86" s="4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AB86" s="24" t="s">
         <v>40</v>
@@ -15066,11 +15066,11 @@
       <c r="Y87" s="4">
         <v>4</v>
       </c>
-      <c r="Z87" s="24" t="s">
-        <v>42</v>
+      <c r="Z87" s="24" t="b">
+        <v>0</v>
       </c>
       <c r="AA87" s="4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AB87" s="24" t="s">
         <v>40</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DFF460-B125-490F-BFC1-E4DDA5D7C099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B9ACC3-FE0B-4F35-9512-EC50D5E153D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2580" yWindow="2580" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6129" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6128" uniqueCount="403">
   <si>
     <t>ExtraInfo</t>
   </si>
@@ -22318,8 +22318,8 @@
       <c r="AQ132" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AR132" s="15" t="s">
-        <v>53</v>
+      <c r="AR132" s="15" t="b">
+        <v>1</v>
       </c>
       <c r="AS132" s="80" t="s">
         <v>54</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DB7F8E-FF78-4667-BC10-6F3C6B409A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E694F0E4-B28A-4E03-8DF6-833FB8B7821B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="4245" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4590" yWindow="4590" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -337,7 +337,7 @@
     <t>Food</t>
   </si>
   <si>
-    <t>Plants,Food</t>
+    <t>Vege,Food</t>
   </si>
   <si>
     <t>一小块生肉，如果你不怕生病的话，可以直接生吃。</t>
@@ -507,7 +507,7 @@
     <t>一种充满淀粉的植物果实，有着一个坚硬的钙质外壳。</t>
   </si>
   <si>
-    <t>Plants</t>
+    <t>Vege</t>
   </si>
   <si>
     <t>菱果肉</t>
@@ -1086,7 +1086,7 @@
     <t>吸盘蠕虫</t>
   </si>
   <si>
-    <t>Hunter</t>
+    <t>Predator</t>
   </si>
   <si>
     <t>Hostile</t>
@@ -28012,7 +28012,7 @@
       <formula1>"false,true,"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576" xr:uid="{00000000-0002-0000-0000-00000C000000}">
-      <formula1>"Rubbish,Plants,Meat,Hunter,Food,FruitCrop,"</formula1>
+      <formula1>"Rubbish,Vege,Meat,Predator,Food,FruitCrop,"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{00000000-0002-0000-0000-00000E000000}">
       <formula1>"Place,Food,ResourcePoint,Resource,Creature,Tool,Equipment,Other,Construction,Crop,Seed,Liquids,Medicine,LiveEntities,Weapon,"</formula1>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E694F0E4-B28A-4E03-8DF6-833FB8B7821B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CA6069-5F68-487B-8DF9-5A13BE99F4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4590" yWindow="4590" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4935" yWindow="4935" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -556,7 +556,7 @@
     <t>鱼皮</t>
   </si>
   <si>
-    <t>Liquids</t>
+    <t>Liquid</t>
   </si>
   <si>
     <t>盐水</t>
@@ -1074,7 +1074,7 @@
     <t>看着有些呆傻的大肥鱼，喜欢食用各类果实，有着能咬开菱果壳的大门牙，但性格胆小，没什么攻击性。</t>
   </si>
   <si>
-    <t>LiveEntities</t>
+    <t>Entity</t>
   </si>
   <si>
     <t>Friendly</t>
@@ -28015,7 +28015,7 @@
       <formula1>"Rubbish,Vege,Meat,Predator,Food,FruitCrop,"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576" xr:uid="{00000000-0002-0000-0000-00000E000000}">
-      <formula1>"Place,Food,ResourcePoint,Resource,Creature,Tool,Equipment,Other,Construction,Crop,Seed,Liquids,Medicine,LiveEntities,Weapon,"</formula1>
+      <formula1>"Place,Food,ResourcePoint,Resource,Creature,Tool,Equipment,Other,Construction,Crop,Seed,Liquid,Medicine,Entity,Weapon,"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576" xr:uid="{00000000-0002-0000-0000-000015000000}">
       <formula1>"Head,Back,Body,Leg,"</formula1>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CA6069-5F68-487B-8DF9-5A13BE99F4E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AAC63A-FCB4-48C3-A115-B663C1F8BC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4935" yWindow="4935" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7264" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7280" uniqueCount="438">
   <si>
     <t>ExtraInfo</t>
   </si>
@@ -13567,8 +13567,21 @@
       <c r="AL68" s="16"/>
       <c r="AP68" s="16"/>
       <c r="AS68" s="16"/>
-      <c r="BA68" s="16"/>
-      <c r="BB68" s="4"/>
+      <c r="BA68" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="BB68" s="90">
+        <v>0.5</v>
+      </c>
+      <c r="BC68" s="90" t="s">
+        <v>189</v>
+      </c>
+      <c r="BD68" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="BE68" s="90" t="s">
+        <v>191</v>
+      </c>
       <c r="BF68" s="15" t="s">
         <v>55</v>
       </c>
@@ -13643,7 +13656,18 @@
       <c r="AP69" s="16"/>
       <c r="AS69" s="16"/>
       <c r="BA69" s="16"/>
-      <c r="BB69" s="4"/>
+      <c r="BB69" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="BC69" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="BD69" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE69" s="90" t="s">
+        <v>56</v>
+      </c>
       <c r="BF69" s="16" t="s">
         <v>55</v>
       </c>
@@ -13718,7 +13742,18 @@
       <c r="AP70" s="16"/>
       <c r="AS70" s="16"/>
       <c r="BA70" s="16"/>
-      <c r="BB70" s="4"/>
+      <c r="BB70" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="BC70" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="BD70" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE70" s="90" t="s">
+        <v>56</v>
+      </c>
       <c r="BF70" s="16" t="s">
         <v>55</v>
       </c>
@@ -13793,7 +13828,18 @@
       <c r="AP71" s="16"/>
       <c r="AS71" s="16"/>
       <c r="BA71" s="16"/>
-      <c r="BB71" s="4"/>
+      <c r="BB71" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="BC71" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="BD71" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE71" s="90" t="s">
+        <v>56</v>
+      </c>
       <c r="BF71" s="16" t="s">
         <v>55</v>
       </c>
@@ -28005,7 +28051,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL2:BL1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Single,AOE,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BA2:BA1048576 BN2:BN154 Z2:Z1048576 BF2:BF1048576 W2:X1048576 BH2:BH1048576 AB2:AB1048576 BM2:BM1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM2:BM1048576 BN2:BN154 Z2:Z1048576 BF2:BF1048576 W2:X1048576 BH2:BH1048576 AB2:AB1048576 BA2:BA1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"true,false,"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY1048576 AX117:AX144 AS2:AS154 AL2:AL1048576 U2:U1048576 S2:S1048576 Q2:Q1048576 H2:H1048576 O2:O1048576 M2:M1048576 K2:K1048576 AP2:AP1048576 AT2:AW1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C16F8B-06C9-4BC2-92EA-78DBC311E2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6997A4C-3164-4B2C-BEC8-74634EEA4310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1035,10 +1035,6 @@
     <t>数据传输台</t>
   </si>
   <si>
-    <t>有了数据传输台后，麦麦就能将自己在这颗星球上记录的样本数据详细地传输出去，这将对科技研究有很大帮助。
-（在拥有数据传输台后将解锁中级科技的研究。数据传输台会每15分钟消耗0.5电力，电力不足将无法进行中级科技研究）</t>
-  </si>
-  <si>
     <t xml:space="preserve">石砖*1+钢材*1+韧性胶管*1
 </t>
   </si>
@@ -1379,6 +1375,11 @@
   </si>
   <si>
     <t>燃烧期间的氧烛会不断产生氧气,可以作为探索时的氧气来源,当氧烛快要燃烧殆尽时,记得及时返回。</t>
+  </si>
+  <si>
+    <t>有了数据传输台后，麦麦就能将自己在这颗星球上记录的样本数据详细地传输出去，这将对科技研究有很大帮助。
+（在建造数据传输台后将解锁中级科技的研究。研究中级科技时每15分钟消耗0.5单位电力，电力不足将无法进行中级科技研究）</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2208,70 +2209,70 @@
   <sheetData>
     <row r="1" spans="1:72" s="88" customFormat="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>390</v>
       </c>
       <c r="W1" s="4" t="s">
         <v>1</v>
@@ -3324,13 +3325,13 @@
         <v>75</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E7" s="10">
         <v>3</v>
@@ -5266,14 +5267,14 @@
     </row>
     <row r="18" spans="1:70" ht="42.75">
       <c r="A18" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="21" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E18" s="4">
         <v>0</v>
@@ -5442,10 +5443,10 @@
     </row>
     <row r="19" spans="1:70" ht="28.5">
       <c r="A19" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="38" t="s">
@@ -5618,14 +5619,14 @@
     </row>
     <row r="20" spans="1:70" ht="42.75">
       <c r="A20" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="21" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E20" s="4">
         <v>2</v>
@@ -5794,10 +5795,10 @@
     </row>
     <row r="21" spans="1:70">
       <c r="A21" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="38" t="s">
@@ -5970,7 +5971,7 @@
     </row>
     <row r="22" spans="1:70" ht="28.5">
       <c r="A22" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>113</v>
@@ -5979,7 +5980,7 @@
         <v>114</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E22" s="4">
         <v>4</v>
@@ -6148,14 +6149,14 @@
     </row>
     <row r="23" spans="1:70" ht="28.5">
       <c r="A23" s="12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>113</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="21" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E23" s="4">
         <v>5</v>
@@ -6324,10 +6325,10 @@
     </row>
     <row r="24" spans="1:70" ht="42.75">
       <c r="A24" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="38" t="s">
@@ -12572,14 +12573,14 @@
     </row>
     <row r="60" spans="1:70" ht="42.75">
       <c r="A60" s="56" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C60" s="12"/>
       <c r="D60" s="21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E60" s="10">
         <v>0</v>
@@ -15184,10 +15185,10 @@
     </row>
     <row r="75" spans="1:70" ht="42.75">
       <c r="A75" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B75" s="56" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C75" s="12"/>
       <c r="D75" s="38" t="s">
@@ -16226,10 +16227,10 @@
     </row>
     <row r="81" spans="1:70" ht="42.75">
       <c r="A81" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C81" s="12"/>
       <c r="D81" s="38" t="s">
@@ -16400,14 +16401,14 @@
     </row>
     <row r="82" spans="1:70" ht="28.5">
       <c r="A82" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C82" s="12"/>
       <c r="D82" s="21" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E82" s="4">
         <v>2</v>
@@ -16574,14 +16575,14 @@
     </row>
     <row r="83" spans="1:70" ht="71.25">
       <c r="A83" s="12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C83" s="12"/>
       <c r="D83" s="21" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E83" s="4">
         <v>3</v>
@@ -16748,14 +16749,14 @@
     </row>
     <row r="84" spans="1:70" ht="42.75">
       <c r="A84" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C84" s="12"/>
       <c r="D84" s="21" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E84" s="4">
         <v>4</v>
@@ -16922,10 +16923,10 @@
     </row>
     <row r="85" spans="1:70" ht="42.75">
       <c r="A85" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="38" t="s">
@@ -17096,14 +17097,14 @@
     </row>
     <row r="86" spans="1:70" ht="71.25">
       <c r="A86" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C86" s="12"/>
       <c r="D86" s="21" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E86" s="4">
         <v>6</v>
@@ -17272,10 +17273,10 @@
     </row>
     <row r="87" spans="1:70" ht="42.75">
       <c r="A87" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C87" s="12"/>
       <c r="D87" s="38" t="s">
@@ -18662,16 +18663,16 @@
     </row>
     <row r="95" spans="1:70" ht="99.75">
       <c r="A95" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>237</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E95" s="10">
         <v>0</v>
@@ -18838,16 +18839,16 @@
     </row>
     <row r="96" spans="1:70" ht="99.75">
       <c r="A96" s="12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E96" s="10">
         <v>1</v>
@@ -19014,16 +19015,16 @@
     </row>
     <row r="97" spans="1:70" ht="57">
       <c r="A97" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>237</v>
       </c>
       <c r="D97" s="21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E97" s="10">
         <v>2</v>
@@ -19190,16 +19191,16 @@
     </row>
     <row r="98" spans="1:70" ht="57">
       <c r="A98" s="12" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E98" s="10">
         <v>3</v>
@@ -19366,16 +19367,16 @@
     </row>
     <row r="99" spans="1:70" ht="57">
       <c r="A99" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>237</v>
       </c>
       <c r="D99" s="38" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E99" s="10">
         <v>4</v>
@@ -19542,16 +19543,16 @@
     </row>
     <row r="100" spans="1:70" ht="57">
       <c r="A100" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>114</v>
       </c>
       <c r="D100" s="38" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E100" s="10">
         <v>5</v>
@@ -19718,10 +19719,10 @@
     </row>
     <row r="101" spans="1:70" ht="28.5">
       <c r="A101" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>239</v>
@@ -19910,10 +19911,10 @@
     </row>
     <row r="102" spans="1:70" ht="57">
       <c r="A102" s="12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C102" s="12"/>
       <c r="D102" s="38" t="s">
@@ -20100,10 +20101,10 @@
     </row>
     <row r="103" spans="1:70" ht="57">
       <c r="A103" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C103" s="12"/>
       <c r="D103" s="38" t="s">
@@ -21936,10 +21937,10 @@
     </row>
     <row r="113" spans="1:70" ht="71.25">
       <c r="A113" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C113" s="12"/>
       <c r="D113" s="9" t="s">
@@ -22112,10 +22113,10 @@
     </row>
     <row r="114" spans="1:70" ht="28.5">
       <c r="A114" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C114" s="12"/>
       <c r="D114" s="38" t="s">
@@ -22288,10 +22289,10 @@
     </row>
     <row r="115" spans="1:70" ht="42.75">
       <c r="A115" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C115" s="12"/>
       <c r="D115" s="38" t="s">
@@ -23174,13 +23175,13 @@
         <v>279</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>280</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E120" s="4">
         <v>0</v>
@@ -23351,13 +23352,13 @@
     <row r="121" spans="1:70" ht="42.75">
       <c r="A121" s="8"/>
       <c r="B121" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>283</v>
       </c>
       <c r="D121" s="21" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E121" s="4">
         <v>1</v>
@@ -23527,14 +23528,14 @@
     </row>
     <row r="122" spans="1:70" ht="71.25">
       <c r="A122" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C122" s="12"/>
       <c r="D122" s="21" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E122" s="4">
         <v>2</v>
@@ -26306,8 +26307,8 @@
       <c r="C140" s="79" t="s">
         <v>280</v>
       </c>
-      <c r="D140" s="78" t="s">
-        <v>331</v>
+      <c r="D140" s="30" t="s">
+        <v>444</v>
       </c>
       <c r="E140" s="45">
         <v>20</v>
@@ -26442,7 +26443,7 @@
         <v>57</v>
       </c>
       <c r="AZ140" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="BA140" s="15" t="s">
         <v>55</v>
@@ -26540,14 +26541,14 @@
     </row>
     <row r="142" spans="1:70" ht="99.75">
       <c r="A142" s="26" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B142" s="26" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C142" s="81"/>
       <c r="D142" s="78" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E142" s="45">
         <v>22</v>
@@ -26685,7 +26686,7 @@
         <v>57</v>
       </c>
       <c r="AZ142" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BA142" s="15" t="s">
         <v>55</v>
@@ -26718,7 +26719,7 @@
     <row r="143" spans="1:70">
       <c r="A143" s="26"/>
       <c r="B143" s="26" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C143" s="81" t="s">
         <v>329</v>
@@ -26813,14 +26814,14 @@
     </row>
     <row r="144" spans="1:70" ht="28.5">
       <c r="A144" s="26" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B144" s="26" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C144" s="81"/>
       <c r="D144" s="78" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E144" s="45">
         <v>24</v>
@@ -26955,7 +26956,7 @@
         <v>57</v>
       </c>
       <c r="AZ144" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="BA144" s="15" t="s">
         <v>55</v>
@@ -26987,14 +26988,14 @@
     </row>
     <row r="145" spans="1:72" ht="71.25">
       <c r="A145" s="26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B145" s="26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C145" s="81"/>
       <c r="D145" s="78" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E145" s="45">
         <v>25</v>
@@ -27132,7 +27133,7 @@
         <v>57</v>
       </c>
       <c r="AZ145" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="BA145" s="15" t="s">
         <v>55</v>
@@ -27164,14 +27165,14 @@
     </row>
     <row r="146" spans="1:72" ht="28.5">
       <c r="A146" s="26" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B146" s="26" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C146" s="81"/>
       <c r="D146" s="78" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E146" s="45">
         <v>26</v>
@@ -27306,7 +27307,7 @@
         <v>57</v>
       </c>
       <c r="AZ146" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="BA146" s="15" t="s">
         <v>55</v>
@@ -27339,7 +27340,7 @@
     <row r="147" spans="1:72">
       <c r="A147" s="26"/>
       <c r="B147" s="26" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C147" s="26" t="s">
         <v>329</v>
@@ -27491,20 +27492,20 @@
     </row>
     <row r="148" spans="1:72" ht="57">
       <c r="A148" s="26" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B148" s="26" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C148" s="26"/>
       <c r="D148" s="30" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E148" s="31">
         <v>0</v>
       </c>
       <c r="F148" s="27" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G148" s="4">
         <v>1</v>
@@ -27670,31 +27671,31 @@
         <v>1.5</v>
       </c>
       <c r="BR148" s="25" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BS148" s="82">
         <v>5</v>
       </c>
       <c r="BT148" s="82" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="149" spans="1:72" ht="99.75">
       <c r="A149" s="34" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B149" s="26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C149" s="26"/>
       <c r="D149" s="30" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E149" s="31">
         <v>1</v>
       </c>
       <c r="F149" s="33" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G149" s="4">
         <v>1</v>
@@ -27706,7 +27707,7 @@
         <v>1.6</v>
       </c>
       <c r="J149" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K149" s="24" t="s">
         <v>55</v>
@@ -27862,31 +27863,31 @@
         <v>0.6</v>
       </c>
       <c r="BR149" s="25" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="BS149" s="82">
         <v>5</v>
       </c>
       <c r="BT149" s="82" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="150" spans="1:72" ht="57">
       <c r="A150" s="34" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B150" s="26" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C150" s="26"/>
       <c r="D150" s="30" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E150" s="31">
         <v>2</v>
       </c>
       <c r="F150" s="33" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G150" s="4">
         <v>1</v>
@@ -28052,31 +28053,31 @@
         <v>0.5</v>
       </c>
       <c r="BR150" s="25" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BS150" s="82">
         <v>5</v>
       </c>
       <c r="BT150" s="82" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="151" spans="1:72" ht="42.75">
       <c r="A151" s="34" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B151" s="26" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C151" s="26"/>
       <c r="D151" s="30" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E151" s="31">
         <v>3</v>
       </c>
       <c r="F151" s="33" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G151" s="4">
         <v>1</v>
@@ -28088,7 +28089,7 @@
         <v>4</v>
       </c>
       <c r="J151" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K151" s="24" t="s">
         <v>55</v>
@@ -28244,31 +28245,31 @@
         <v>0.4</v>
       </c>
       <c r="BR151" s="25" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="BS151" s="82">
         <v>5</v>
       </c>
       <c r="BT151" s="82" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="152" spans="1:72" ht="28.5">
       <c r="A152" s="26" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B152" s="26" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C152" s="26"/>
       <c r="D152" s="30" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E152" s="31">
         <v>4</v>
       </c>
       <c r="F152" s="33" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G152" s="4">
         <v>1</v>
@@ -28434,31 +28435,31 @@
         <v>1</v>
       </c>
       <c r="BR152" s="25" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BS152" s="82">
         <v>5</v>
       </c>
       <c r="BT152" s="82" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="153" spans="1:72" ht="42.75">
       <c r="A153" s="12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C153" s="12"/>
       <c r="D153" s="21" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E153" s="69">
         <v>0</v>
       </c>
       <c r="F153" s="83" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G153" s="12">
         <v>1</v>
@@ -28619,19 +28620,19 @@
     </row>
     <row r="154" spans="1:72" ht="71.25">
       <c r="A154" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D154" s="38" t="s">
         <v>440</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="D154" s="38" t="s">
-        <v>441</v>
       </c>
       <c r="E154" s="69">
         <v>1</v>
       </c>
       <c r="F154" s="59" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G154" s="4">
         <v>10</v>
@@ -28792,20 +28793,20 @@
     </row>
     <row r="155" spans="1:72" ht="71.25">
       <c r="A155" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C155" s="12"/>
       <c r="D155" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E155" s="69">
         <v>2</v>
       </c>
       <c r="F155" s="83" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G155" s="4">
         <v>5</v>
@@ -28966,22 +28967,22 @@
     </row>
     <row r="156" spans="1:72" ht="57">
       <c r="A156" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>329</v>
       </c>
       <c r="D156" s="21" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E156" s="69">
         <v>3</v>
       </c>
       <c r="F156" s="83" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G156" s="4">
         <v>1</v>
@@ -29143,17 +29144,17 @@
     <row r="157" spans="1:72" ht="57">
       <c r="A157" s="84"/>
       <c r="B157" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C157" s="8"/>
       <c r="D157" s="38" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E157" s="69">
         <v>4</v>
       </c>
       <c r="F157" s="83" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G157" s="4">
         <v>1</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6997A4C-3164-4B2C-BEC8-74634EEA4310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864F910F-0A48-418D-8A45-C39F495B3277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1239,9 +1239,6 @@
     <t>腐烂物</t>
   </si>
   <si>
-    <t>有产物的被捉住的水瓶鱼</t>
-  </si>
-  <si>
     <t>一只水瓶鱼,其怀孕时体内的育卵液是重要的淡水来源。</t>
   </si>
   <si>
@@ -1318,9 +1315,6 @@
   </si>
   <si>
     <t>有产物的虹吸海葵</t>
-  </si>
-  <si>
-    <t>废铁铲</t>
   </si>
   <si>
     <t>废铁刀</t>
@@ -1379,6 +1373,14 @@
   <si>
     <t>有了数据传输台后，麦麦就能将自己在这颗星球上记录的样本数据详细地传输出去，这将对科技研究有很大帮助。
 （在建造数据传输台后将解锁中级科技的研究。研究中级科技时每15分钟消耗0.5单位电力，电力不足将无法进行中级科技研究）</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>被捉住的有产物的水瓶鱼</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>废铁铲</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
@@ -5971,7 +5973,7 @@
     </row>
     <row r="22" spans="1:70" ht="28.5">
       <c r="A22" s="12" t="s">
-        <v>398</v>
+        <v>443</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>113</v>
@@ -5980,7 +5982,7 @@
         <v>114</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E22" s="4">
         <v>4</v>
@@ -6149,14 +6151,14 @@
     </row>
     <row r="23" spans="1:70" ht="28.5">
       <c r="A23" s="12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>113</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="21" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E23" s="4">
         <v>5</v>
@@ -6325,10 +6327,10 @@
     </row>
     <row r="24" spans="1:70" ht="42.75">
       <c r="A24" s="12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="38" t="s">
@@ -12573,14 +12575,14 @@
     </row>
     <row r="60" spans="1:70" ht="42.75">
       <c r="A60" s="56" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C60" s="12"/>
       <c r="D60" s="21" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E60" s="10">
         <v>0</v>
@@ -15185,10 +15187,10 @@
     </row>
     <row r="75" spans="1:70" ht="42.75">
       <c r="A75" s="12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B75" s="56" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C75" s="12"/>
       <c r="D75" s="38" t="s">
@@ -16227,10 +16229,10 @@
     </row>
     <row r="81" spans="1:70" ht="42.75">
       <c r="A81" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C81" s="12"/>
       <c r="D81" s="38" t="s">
@@ -16401,14 +16403,14 @@
     </row>
     <row r="82" spans="1:70" ht="28.5">
       <c r="A82" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C82" s="12"/>
       <c r="D82" s="21" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E82" s="4">
         <v>2</v>
@@ -16575,14 +16577,14 @@
     </row>
     <row r="83" spans="1:70" ht="71.25">
       <c r="A83" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C83" s="12"/>
       <c r="D83" s="21" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E83" s="4">
         <v>3</v>
@@ -16749,14 +16751,14 @@
     </row>
     <row r="84" spans="1:70" ht="42.75">
       <c r="A84" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C84" s="12"/>
       <c r="D84" s="21" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E84" s="4">
         <v>4</v>
@@ -16923,10 +16925,10 @@
     </row>
     <row r="85" spans="1:70" ht="42.75">
       <c r="A85" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="38" t="s">
@@ -17097,14 +17099,14 @@
     </row>
     <row r="86" spans="1:70" ht="71.25">
       <c r="A86" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C86" s="12"/>
       <c r="D86" s="21" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E86" s="4">
         <v>6</v>
@@ -17273,10 +17275,10 @@
     </row>
     <row r="87" spans="1:70" ht="42.75">
       <c r="A87" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C87" s="12"/>
       <c r="D87" s="38" t="s">
@@ -18663,16 +18665,16 @@
     </row>
     <row r="95" spans="1:70" ht="99.75">
       <c r="A95" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>237</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E95" s="10">
         <v>0</v>
@@ -18839,16 +18841,16 @@
     </row>
     <row r="96" spans="1:70" ht="99.75">
       <c r="A96" s="12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E96" s="10">
         <v>1</v>
@@ -19015,16 +19017,16 @@
     </row>
     <row r="97" spans="1:70" ht="57">
       <c r="A97" s="12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>237</v>
       </c>
       <c r="D97" s="21" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E97" s="10">
         <v>2</v>
@@ -19191,16 +19193,16 @@
     </row>
     <row r="98" spans="1:70" ht="57">
       <c r="A98" s="12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E98" s="10">
         <v>3</v>
@@ -19367,16 +19369,16 @@
     </row>
     <row r="99" spans="1:70" ht="57">
       <c r="A99" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>237</v>
       </c>
       <c r="D99" s="38" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E99" s="10">
         <v>4</v>
@@ -19543,16 +19545,16 @@
     </row>
     <row r="100" spans="1:70" ht="57">
       <c r="A100" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>114</v>
       </c>
       <c r="D100" s="38" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E100" s="10">
         <v>5</v>
@@ -19719,10 +19721,10 @@
     </row>
     <row r="101" spans="1:70" ht="28.5">
       <c r="A101" s="12" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>239</v>
@@ -19911,10 +19913,10 @@
     </row>
     <row r="102" spans="1:70" ht="57">
       <c r="A102" s="12" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C102" s="12"/>
       <c r="D102" s="38" t="s">
@@ -20101,10 +20103,10 @@
     </row>
     <row r="103" spans="1:70" ht="57">
       <c r="A103" s="12" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C103" s="12"/>
       <c r="D103" s="38" t="s">
@@ -21937,10 +21939,10 @@
     </row>
     <row r="113" spans="1:70" ht="71.25">
       <c r="A113" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C113" s="12"/>
       <c r="D113" s="9" t="s">
@@ -22113,10 +22115,10 @@
     </row>
     <row r="114" spans="1:70" ht="28.5">
       <c r="A114" s="12" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C114" s="12"/>
       <c r="D114" s="38" t="s">
@@ -22289,10 +22291,10 @@
     </row>
     <row r="115" spans="1:70" ht="42.75">
       <c r="A115" s="12" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C115" s="12"/>
       <c r="D115" s="38" t="s">
@@ -23175,13 +23177,13 @@
         <v>279</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>280</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E120" s="4">
         <v>0</v>
@@ -23352,13 +23354,13 @@
     <row r="121" spans="1:70" ht="42.75">
       <c r="A121" s="8"/>
       <c r="B121" s="12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>283</v>
       </c>
       <c r="D121" s="21" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E121" s="4">
         <v>1</v>
@@ -23528,14 +23530,14 @@
     </row>
     <row r="122" spans="1:70" ht="71.25">
       <c r="A122" s="12" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C122" s="12"/>
       <c r="D122" s="21" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E122" s="4">
         <v>2</v>
@@ -26308,7 +26310,7 @@
         <v>280</v>
       </c>
       <c r="D140" s="30" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E140" s="45">
         <v>20</v>
@@ -28446,14 +28448,14 @@
     </row>
     <row r="153" spans="1:72" ht="42.75">
       <c r="A153" s="12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C153" s="12"/>
       <c r="D153" s="21" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E153" s="69">
         <v>0</v>
@@ -28620,13 +28622,13 @@
     </row>
     <row r="154" spans="1:72" ht="71.25">
       <c r="A154" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D154" s="38" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E154" s="69">
         <v>1</v>
@@ -28793,10 +28795,10 @@
     </row>
     <row r="155" spans="1:72" ht="71.25">
       <c r="A155" s="12" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C155" s="12"/>
       <c r="D155" s="9" t="s">
@@ -28967,7 +28969,7 @@
     </row>
     <row r="156" spans="1:72" ht="57">
       <c r="A156" s="12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B156" s="8" t="s">
         <v>366</v>
@@ -28976,7 +28978,7 @@
         <v>329</v>
       </c>
       <c r="D156" s="21" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E156" s="69">
         <v>3</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F531E8B-688F-4472-84C5-791D54A9E254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86BA152-89B0-4558-A277-5CE7DE1B4B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1205,9 +1205,6 @@
     <t>食果豚</t>
   </si>
   <si>
-    <t>食果鲀</t>
-  </si>
-  <si>
     <t>看着有些呆傻的大肥鱼，喜欢食用各类果实，有着能咬开菱果壳的大门牙，但性格胆小，没什么攻击性。</t>
   </si>
   <si>
@@ -1504,6 +1501,10 @@
   </si>
   <si>
     <t>燃烧期间的氧烛会不断产生氧气,可以作为探索时的氧气来源,当氧烛快要燃烧殆尽时,记得及时返回。</t>
+  </si>
+  <si>
+    <t>食果豚</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2224,138 +2225,138 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BY160"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="28.58203125" style="58" customWidth="1"/>
-    <col min="2" max="3" width="11.4140625" style="58" customWidth="1"/>
-    <col min="4" max="4" width="28.08203125" style="65" customWidth="1"/>
+    <col min="1" max="1" width="28.625" style="58" customWidth="1"/>
+    <col min="2" max="3" width="11.375" style="58" customWidth="1"/>
+    <col min="4" max="4" width="28.125" style="65" customWidth="1"/>
     <col min="5" max="5" width="18.75" style="66" customWidth="1"/>
-    <col min="6" max="6" width="15.58203125" style="58" customWidth="1"/>
-    <col min="7" max="7" width="8.58203125" style="58" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" style="58" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" style="58" customWidth="1"/>
-    <col min="10" max="10" width="10.1640625" style="58" customWidth="1"/>
-    <col min="11" max="11" width="6.83203125" style="58" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="58" customWidth="1"/>
+    <col min="7" max="7" width="8.625" style="58" customWidth="1"/>
+    <col min="8" max="8" width="15.375" style="58" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="58" customWidth="1"/>
+    <col min="10" max="10" width="10.125" style="58" customWidth="1"/>
+    <col min="11" max="11" width="6.875" style="58" customWidth="1"/>
     <col min="12" max="12" width="13" style="58" customWidth="1"/>
     <col min="13" max="13" width="18.75" style="66" customWidth="1"/>
-    <col min="14" max="14" width="12.1640625" style="58" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" style="58" customWidth="1"/>
+    <col min="14" max="14" width="12.125" style="58" customWidth="1"/>
+    <col min="15" max="15" width="13.125" style="58" customWidth="1"/>
     <col min="16" max="25" width="19" style="58" customWidth="1"/>
-    <col min="26" max="26" width="10.1640625" style="58" customWidth="1"/>
+    <col min="26" max="26" width="10.125" style="58" customWidth="1"/>
     <col min="27" max="29" width="12.5" style="58" customWidth="1"/>
-    <col min="30" max="32" width="11.1640625" style="58" customWidth="1"/>
+    <col min="30" max="32" width="11.125" style="58" customWidth="1"/>
     <col min="33" max="33" width="12.25" style="58" customWidth="1"/>
-    <col min="34" max="42" width="8.58203125" style="58"/>
-    <col min="43" max="43" width="11.6640625" style="58" customWidth="1"/>
-    <col min="44" max="44" width="9.1640625" style="58" customWidth="1"/>
+    <col min="34" max="42" width="8.625" style="58"/>
+    <col min="43" max="43" width="11.625" style="58" customWidth="1"/>
+    <col min="44" max="44" width="9.125" style="58" customWidth="1"/>
     <col min="45" max="45" width="12" style="58" customWidth="1"/>
-    <col min="46" max="46" width="11.6640625" style="58" customWidth="1"/>
-    <col min="47" max="47" width="8.58203125" style="58" customWidth="1"/>
+    <col min="46" max="46" width="11.625" style="58" customWidth="1"/>
+    <col min="47" max="47" width="8.625" style="58" customWidth="1"/>
     <col min="48" max="48" width="9.25" style="58" customWidth="1"/>
     <col min="49" max="49" width="14.5" style="58" customWidth="1"/>
-    <col min="50" max="50" width="12.58203125" style="58" customWidth="1"/>
+    <col min="50" max="50" width="12.625" style="58" customWidth="1"/>
     <col min="51" max="51" width="11" style="58" customWidth="1"/>
-    <col min="52" max="52" width="12.4140625" style="58" customWidth="1"/>
-    <col min="53" max="53" width="10.1640625" style="58" customWidth="1"/>
-    <col min="54" max="54" width="11.58203125" style="58" customWidth="1"/>
-    <col min="55" max="55" width="10.08203125" style="58" customWidth="1"/>
-    <col min="56" max="56" width="16.08203125" style="58" customWidth="1"/>
+    <col min="52" max="52" width="12.375" style="58" customWidth="1"/>
+    <col min="53" max="53" width="10.125" style="58" customWidth="1"/>
+    <col min="54" max="54" width="11.625" style="58" customWidth="1"/>
+    <col min="55" max="55" width="10.125" style="58" customWidth="1"/>
+    <col min="56" max="56" width="16.125" style="58" customWidth="1"/>
     <col min="57" max="57" width="14" style="58" customWidth="1"/>
     <col min="58" max="58" width="12" style="58" customWidth="1"/>
     <col min="59" max="59" width="13.75" style="67" customWidth="1"/>
     <col min="60" max="60" width="18.75" style="58" customWidth="1"/>
-    <col min="61" max="61" width="12.4140625" style="58" customWidth="1"/>
-    <col min="62" max="62" width="22.58203125" style="58" customWidth="1"/>
-    <col min="63" max="63" width="15.08203125" style="58" customWidth="1"/>
-    <col min="64" max="64" width="9.9140625" style="58" customWidth="1"/>
-    <col min="65" max="65" width="11.4140625" style="58" customWidth="1"/>
+    <col min="61" max="61" width="12.375" style="58" customWidth="1"/>
+    <col min="62" max="62" width="22.625" style="58" customWidth="1"/>
+    <col min="63" max="63" width="15.125" style="58" customWidth="1"/>
+    <col min="64" max="64" width="9.875" style="58" customWidth="1"/>
+    <col min="65" max="65" width="11.375" style="58" customWidth="1"/>
     <col min="66" max="66" width="7.25" style="58" customWidth="1"/>
-    <col min="67" max="67" width="12.1640625" style="58" customWidth="1"/>
+    <col min="67" max="67" width="12.125" style="58" customWidth="1"/>
     <col min="68" max="68" width="12.75" style="58" customWidth="1"/>
-    <col min="69" max="69" width="14.58203125" style="58" customWidth="1"/>
+    <col min="69" max="69" width="14.625" style="58" customWidth="1"/>
     <col min="70" max="70" width="14.5" style="58" customWidth="1"/>
-    <col min="71" max="71" width="17.9140625" style="58" customWidth="1"/>
+    <col min="71" max="71" width="17.875" style="58" customWidth="1"/>
     <col min="72" max="72" width="13.5" style="58" customWidth="1"/>
     <col min="73" max="73" width="20.25" style="58" customWidth="1"/>
-    <col min="74" max="74" width="20.33203125" style="58" customWidth="1"/>
+    <col min="74" max="74" width="20.375" style="58" customWidth="1"/>
     <col min="75" max="77" width="18.75" style="68" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:77" s="64" customFormat="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>413</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="Z1" s="4" t="s">
         <v>4</v>
@@ -2908,7 +2909,7 @@
       <c r="BX3" s="49"/>
       <c r="BY3" s="49"/>
     </row>
-    <row r="4" spans="1:77" ht="28">
+    <row r="4" spans="1:77" ht="28.5">
       <c r="A4" s="5" t="s">
         <v>70</v>
       </c>
@@ -3302,7 +3303,7 @@
       <c r="BX5" s="49"/>
       <c r="BY5" s="49"/>
     </row>
-    <row r="6" spans="1:77" ht="84">
+    <row r="6" spans="1:77" ht="85.5">
       <c r="A6" s="12" t="s">
         <v>76</v>
       </c>
@@ -3499,18 +3500,18 @@
       <c r="BX6" s="49"/>
       <c r="BY6" s="49"/>
     </row>
-    <row r="7" spans="1:77" ht="84">
+    <row r="7" spans="1:77" ht="85.5">
       <c r="A7" s="12" t="s">
         <v>81</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="11">
@@ -3696,7 +3697,7 @@
       <c r="BX7" s="49"/>
       <c r="BY7" s="49"/>
     </row>
-    <row r="8" spans="1:77" ht="28">
+    <row r="8" spans="1:77" ht="28.5">
       <c r="A8" s="37" t="s">
         <v>82</v>
       </c>
@@ -3893,7 +3894,7 @@
       <c r="BX8" s="49"/>
       <c r="BY8" s="49"/>
     </row>
-    <row r="9" spans="1:77" ht="28">
+    <row r="9" spans="1:77" ht="28.5">
       <c r="A9" s="37" t="s">
         <v>87</v>
       </c>
@@ -5666,16 +5667,16 @@
       <c r="BX17" s="49"/>
       <c r="BY17" s="49"/>
     </row>
-    <row r="18" spans="1:77" ht="42">
+    <row r="18" spans="1:77" ht="42.75">
       <c r="A18" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4">
@@ -5861,12 +5862,12 @@
       <c r="BX18" s="49"/>
       <c r="BY18" s="49"/>
     </row>
-    <row r="19" spans="1:77" ht="28">
+    <row r="19" spans="1:77" ht="28.5">
       <c r="A19" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="4" t="s">
@@ -6056,16 +6057,16 @@
       <c r="BX19" s="49"/>
       <c r="BY19" s="49"/>
     </row>
-    <row r="20" spans="1:77" ht="42">
+    <row r="20" spans="1:77" ht="42.75">
       <c r="A20" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4">
@@ -6253,10 +6254,10 @@
     </row>
     <row r="21" spans="1:77">
       <c r="A21" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="4" t="s">
@@ -6446,7 +6447,7 @@
       <c r="BX21" s="49"/>
       <c r="BY21" s="49"/>
     </row>
-    <row r="22" spans="1:77" ht="28">
+    <row r="22" spans="1:77" ht="28.5">
       <c r="A22" s="5" t="s">
         <v>126</v>
       </c>
@@ -6457,7 +6458,7 @@
         <v>128</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4">
@@ -6643,16 +6644,16 @@
       <c r="BX22" s="49"/>
       <c r="BY22" s="49"/>
     </row>
-    <row r="23" spans="1:77" ht="28">
+    <row r="23" spans="1:77" ht="28.5">
       <c r="A23" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>127</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4">
@@ -6838,12 +6839,12 @@
       <c r="BX23" s="49"/>
       <c r="BY23" s="49"/>
     </row>
-    <row r="24" spans="1:77" ht="42">
+    <row r="24" spans="1:77" ht="42.75">
       <c r="A24" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="4" t="s">
@@ -7033,7 +7034,7 @@
       <c r="BX24" s="49"/>
       <c r="BY24" s="49"/>
     </row>
-    <row r="25" spans="1:77" ht="126">
+    <row r="25" spans="1:77" ht="128.25">
       <c r="A25" s="20" t="s">
         <v>132</v>
       </c>
@@ -7228,7 +7229,7 @@
       <c r="BX25" s="49"/>
       <c r="BY25" s="49"/>
     </row>
-    <row r="26" spans="1:77" ht="84">
+    <row r="26" spans="1:77" ht="85.5">
       <c r="A26" s="20" t="s">
         <v>134</v>
       </c>
@@ -7423,7 +7424,7 @@
       <c r="BX26" s="49"/>
       <c r="BY26" s="49"/>
     </row>
-    <row r="27" spans="1:77" ht="70">
+    <row r="27" spans="1:77" ht="85.5">
       <c r="A27" s="20" t="s">
         <v>136</v>
       </c>
@@ -7616,7 +7617,7 @@
       <c r="BX27" s="49"/>
       <c r="BY27" s="49"/>
     </row>
-    <row r="28" spans="1:77" ht="28">
+    <row r="28" spans="1:77" ht="28.5">
       <c r="A28" s="4" t="s">
         <v>138</v>
       </c>
@@ -7811,7 +7812,7 @@
       <c r="BX28" s="49"/>
       <c r="BY28" s="49"/>
     </row>
-    <row r="29" spans="1:77" ht="70">
+    <row r="29" spans="1:77" ht="71.25">
       <c r="A29" s="4" t="s">
         <v>140</v>
       </c>
@@ -8004,7 +8005,7 @@
       <c r="BX29" s="49"/>
       <c r="BY29" s="49"/>
     </row>
-    <row r="30" spans="1:77" ht="70">
+    <row r="30" spans="1:77" ht="71.25">
       <c r="A30" s="4" t="s">
         <v>142</v>
       </c>
@@ -8199,7 +8200,7 @@
       <c r="BX30" s="49"/>
       <c r="BY30" s="49"/>
     </row>
-    <row r="31" spans="1:77" ht="28">
+    <row r="31" spans="1:77" ht="42.75">
       <c r="A31" s="4" t="s">
         <v>144</v>
       </c>
@@ -8394,7 +8395,7 @@
       <c r="BX31" s="49"/>
       <c r="BY31" s="49"/>
     </row>
-    <row r="32" spans="1:77" ht="42">
+    <row r="32" spans="1:77" ht="42.75">
       <c r="A32" s="4" t="s">
         <v>146</v>
       </c>
@@ -8589,7 +8590,7 @@
       <c r="BX32" s="49"/>
       <c r="BY32" s="49"/>
     </row>
-    <row r="33" spans="1:77" ht="42">
+    <row r="33" spans="1:77" ht="42.75">
       <c r="A33" s="4" t="s">
         <v>148</v>
       </c>
@@ -8784,7 +8785,7 @@
       <c r="BX33" s="49"/>
       <c r="BY33" s="49"/>
     </row>
-    <row r="34" spans="1:77" ht="28">
+    <row r="34" spans="1:77" ht="42.75">
       <c r="A34" s="4" t="s">
         <v>150</v>
       </c>
@@ -8979,7 +8980,7 @@
       <c r="BX34" s="49"/>
       <c r="BY34" s="49"/>
     </row>
-    <row r="35" spans="1:77" ht="42">
+    <row r="35" spans="1:77" ht="42.75">
       <c r="A35" s="4" t="s">
         <v>152</v>
       </c>
@@ -9174,7 +9175,7 @@
       <c r="BX35" s="49"/>
       <c r="BY35" s="49"/>
     </row>
-    <row r="36" spans="1:77" ht="70">
+    <row r="36" spans="1:77" ht="71.25">
       <c r="A36" s="4" t="s">
         <v>154</v>
       </c>
@@ -9369,7 +9370,7 @@
       <c r="BX36" s="49"/>
       <c r="BY36" s="49"/>
     </row>
-    <row r="37" spans="1:77" ht="28">
+    <row r="37" spans="1:77" ht="28.5">
       <c r="A37" s="37" t="s">
         <v>121</v>
       </c>
@@ -9564,7 +9565,7 @@
       <c r="BX37" s="49"/>
       <c r="BY37" s="49"/>
     </row>
-    <row r="38" spans="1:77" ht="28">
+    <row r="38" spans="1:77" ht="28.5">
       <c r="A38" s="37" t="s">
         <v>122</v>
       </c>
@@ -9759,7 +9760,7 @@
       <c r="BX38" s="49"/>
       <c r="BY38" s="49"/>
     </row>
-    <row r="39" spans="1:77" ht="28">
+    <row r="39" spans="1:77" ht="28.5">
       <c r="A39" s="37" t="s">
         <v>158</v>
       </c>
@@ -9954,7 +9955,7 @@
       <c r="BX39" s="49"/>
       <c r="BY39" s="49"/>
     </row>
-    <row r="40" spans="1:77" ht="56">
+    <row r="40" spans="1:77" ht="57">
       <c r="A40" s="37" t="s">
         <v>125</v>
       </c>
@@ -10149,7 +10150,7 @@
       <c r="BX40" s="49"/>
       <c r="BY40" s="49"/>
     </row>
-    <row r="41" spans="1:77" ht="28">
+    <row r="41" spans="1:77" ht="28.5">
       <c r="A41" s="28" t="s">
         <v>161</v>
       </c>
@@ -10344,7 +10345,7 @@
       <c r="BX41" s="49"/>
       <c r="BY41" s="49"/>
     </row>
-    <row r="42" spans="1:77" ht="28">
+    <row r="42" spans="1:77" ht="28.5">
       <c r="A42" s="28" t="s">
         <v>163</v>
       </c>
@@ -10539,7 +10540,7 @@
       <c r="BX42" s="49"/>
       <c r="BY42" s="49"/>
     </row>
-    <row r="43" spans="1:77" ht="56">
+    <row r="43" spans="1:77" ht="57">
       <c r="A43" s="30" t="s">
         <v>165</v>
       </c>
@@ -10734,7 +10735,7 @@
       <c r="BX43" s="49"/>
       <c r="BY43" s="49"/>
     </row>
-    <row r="44" spans="1:77" ht="28">
+    <row r="44" spans="1:77" ht="28.5">
       <c r="A44" s="31" t="s">
         <v>167</v>
       </c>
@@ -10927,7 +10928,7 @@
       <c r="BX44" s="49"/>
       <c r="BY44" s="49"/>
     </row>
-    <row r="45" spans="1:77" ht="28">
+    <row r="45" spans="1:77" ht="42.75">
       <c r="A45" s="33" t="s">
         <v>171</v>
       </c>
@@ -11309,7 +11310,7 @@
       <c r="BX46" s="49"/>
       <c r="BY46" s="49"/>
     </row>
-    <row r="47" spans="1:77" ht="28">
+    <row r="47" spans="1:77" ht="28.5">
       <c r="A47" s="30" t="s">
         <v>176</v>
       </c>
@@ -11500,7 +11501,7 @@
       <c r="BX47" s="49"/>
       <c r="BY47" s="49"/>
     </row>
-    <row r="48" spans="1:77" ht="28">
+    <row r="48" spans="1:77" ht="28.5">
       <c r="A48" s="30" t="s">
         <v>179</v>
       </c>
@@ -11890,7 +11891,7 @@
       <c r="BX49" s="49"/>
       <c r="BY49" s="49"/>
     </row>
-    <row r="50" spans="1:77" ht="28">
+    <row r="50" spans="1:77" ht="28.5">
       <c r="A50" s="30" t="s">
         <v>183</v>
       </c>
@@ -12081,7 +12082,7 @@
       <c r="BX50" s="49"/>
       <c r="BY50" s="49"/>
     </row>
-    <row r="51" spans="1:77" ht="70">
+    <row r="51" spans="1:77" ht="71.25">
       <c r="A51" s="30" t="s">
         <v>186</v>
       </c>
@@ -12272,7 +12273,7 @@
       <c r="BX51" s="49"/>
       <c r="BY51" s="49"/>
     </row>
-    <row r="52" spans="1:77" ht="42">
+    <row r="52" spans="1:77" ht="42.75">
       <c r="A52" s="33" t="s">
         <v>188</v>
       </c>
@@ -12463,7 +12464,7 @@
       <c r="BX52" s="49"/>
       <c r="BY52" s="49"/>
     </row>
-    <row r="53" spans="1:77" ht="42">
+    <row r="53" spans="1:77" ht="42.75">
       <c r="A53" s="30" t="s">
         <v>190</v>
       </c>
@@ -12654,7 +12655,7 @@
       <c r="BX53" s="49"/>
       <c r="BY53" s="49"/>
     </row>
-    <row r="54" spans="1:77" ht="42">
+    <row r="54" spans="1:77" ht="42.75">
       <c r="A54" s="30" t="s">
         <v>192</v>
       </c>
@@ -12845,7 +12846,7 @@
       <c r="BX54" s="49"/>
       <c r="BY54" s="49"/>
     </row>
-    <row r="55" spans="1:77" ht="70">
+    <row r="55" spans="1:77" ht="71.25">
       <c r="A55" s="30" t="s">
         <v>194</v>
       </c>
@@ -13036,7 +13037,7 @@
       <c r="BX55" s="49"/>
       <c r="BY55" s="49"/>
     </row>
-    <row r="56" spans="1:77" ht="56">
+    <row r="56" spans="1:77" ht="57">
       <c r="A56" s="30" t="s">
         <v>196</v>
       </c>
@@ -13231,7 +13232,7 @@
       <c r="BX56" s="49"/>
       <c r="BY56" s="49"/>
     </row>
-    <row r="57" spans="1:77" ht="42">
+    <row r="57" spans="1:77" ht="42.75">
       <c r="A57" s="30" t="s">
         <v>198</v>
       </c>
@@ -13426,7 +13427,7 @@
       <c r="BX57" s="49"/>
       <c r="BY57" s="49"/>
     </row>
-    <row r="58" spans="1:77" ht="34" customHeight="1">
+    <row r="58" spans="1:77" ht="33.950000000000003" customHeight="1">
       <c r="A58" s="37" t="s">
         <v>200</v>
       </c>
@@ -13621,7 +13622,7 @@
       <c r="BX58" s="49"/>
       <c r="BY58" s="49"/>
     </row>
-    <row r="59" spans="1:77" ht="34" customHeight="1">
+    <row r="59" spans="1:77" ht="33.950000000000003" customHeight="1">
       <c r="A59" s="37" t="s">
         <v>202</v>
       </c>
@@ -13816,16 +13817,16 @@
       <c r="BX59" s="49"/>
       <c r="BY59" s="49"/>
     </row>
-    <row r="60" spans="1:77" ht="42">
+    <row r="60" spans="1:77" ht="42.75">
       <c r="A60" s="35" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C60" s="8"/>
       <c r="D60" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="11">
@@ -14009,7 +14010,7 @@
       <c r="BX60" s="49"/>
       <c r="BY60" s="49"/>
     </row>
-    <row r="61" spans="1:77" ht="70">
+    <row r="61" spans="1:77" ht="71.25">
       <c r="A61" s="36" t="s">
         <v>205</v>
       </c>
@@ -14202,7 +14203,7 @@
       <c r="BX61" s="49"/>
       <c r="BY61" s="49"/>
     </row>
-    <row r="62" spans="1:77" ht="56">
+    <row r="62" spans="1:77" ht="57">
       <c r="A62" s="36" t="s">
         <v>207</v>
       </c>
@@ -14397,7 +14398,7 @@
       <c r="BX62" s="49"/>
       <c r="BY62" s="49"/>
     </row>
-    <row r="63" spans="1:77">
+    <row r="63" spans="1:77" ht="28.5">
       <c r="A63" s="28" t="s">
         <v>209</v>
       </c>
@@ -14590,7 +14591,7 @@
       <c r="BX63" s="49"/>
       <c r="BY63" s="49"/>
     </row>
-    <row r="64" spans="1:77" ht="140">
+    <row r="64" spans="1:77" ht="142.5">
       <c r="A64" s="38" t="s">
         <v>212</v>
       </c>
@@ -15762,7 +15763,7 @@
       <c r="BX69" s="49"/>
       <c r="BY69" s="49"/>
     </row>
-    <row r="70" spans="1:77" ht="70">
+    <row r="70" spans="1:77" ht="85.5">
       <c r="A70" s="29" t="s">
         <v>231</v>
       </c>
@@ -16546,7 +16547,7 @@
       <c r="BX73" s="49"/>
       <c r="BY73" s="49"/>
     </row>
-    <row r="74" spans="1:77" ht="70">
+    <row r="74" spans="1:77" ht="71.25">
       <c r="A74" s="39" t="s">
         <v>217</v>
       </c>
@@ -16741,12 +16742,12 @@
       <c r="BX74" s="49"/>
       <c r="BY74" s="49"/>
     </row>
-    <row r="75" spans="1:77" ht="28">
+    <row r="75" spans="1:77" ht="42.75">
       <c r="A75" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B75" s="35" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C75" s="8"/>
       <c r="D75" s="4" t="s">
@@ -16934,7 +16935,7 @@
       <c r="BX75" s="49"/>
       <c r="BY75" s="49"/>
     </row>
-    <row r="76" spans="1:77" ht="42">
+    <row r="76" spans="1:77" ht="57">
       <c r="A76" s="21" t="s">
         <v>241</v>
       </c>
@@ -17127,7 +17128,7 @@
       <c r="BX76" s="49"/>
       <c r="BY76" s="49"/>
     </row>
-    <row r="77" spans="1:77" ht="28">
+    <row r="77" spans="1:77" ht="28.5">
       <c r="A77" s="21" t="s">
         <v>243</v>
       </c>
@@ -17320,7 +17321,7 @@
       <c r="BX77" s="49"/>
       <c r="BY77" s="49"/>
     </row>
-    <row r="78" spans="1:77" ht="28">
+    <row r="78" spans="1:77" ht="28.5">
       <c r="A78" s="21" t="s">
         <v>245</v>
       </c>
@@ -17513,7 +17514,7 @@
       <c r="BX78" s="49"/>
       <c r="BY78" s="49"/>
     </row>
-    <row r="79" spans="1:77" ht="42">
+    <row r="79" spans="1:77" ht="42.75">
       <c r="A79" s="21" t="s">
         <v>247</v>
       </c>
@@ -17706,7 +17707,7 @@
       <c r="BX79" s="49"/>
       <c r="BY79" s="49"/>
     </row>
-    <row r="80" spans="1:77" ht="42">
+    <row r="80" spans="1:77" ht="42.75">
       <c r="A80" s="21" t="s">
         <v>249</v>
       </c>
@@ -18092,12 +18093,12 @@
       <c r="BX81" s="49"/>
       <c r="BY81" s="49"/>
     </row>
-    <row r="82" spans="1:77" ht="42">
+    <row r="82" spans="1:77" ht="42.75">
       <c r="A82" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="4" t="s">
@@ -18285,16 +18286,16 @@
       <c r="BX82" s="49"/>
       <c r="BY82" s="49"/>
     </row>
-    <row r="83" spans="1:77" ht="28">
+    <row r="83" spans="1:77" ht="28.5">
       <c r="A83" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C83" s="8"/>
       <c r="D83" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4">
@@ -18478,16 +18479,16 @@
       <c r="BX83" s="49"/>
       <c r="BY83" s="49"/>
     </row>
-    <row r="84" spans="1:77" ht="70">
+    <row r="84" spans="1:77" ht="71.25">
       <c r="A84" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C84" s="8"/>
       <c r="D84" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E84" s="4"/>
       <c r="F84" s="4">
@@ -18671,16 +18672,16 @@
       <c r="BX84" s="49"/>
       <c r="BY84" s="49"/>
     </row>
-    <row r="85" spans="1:77" ht="42">
+    <row r="85" spans="1:77" ht="42.75">
       <c r="A85" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4">
@@ -18864,12 +18865,12 @@
       <c r="BX85" s="49"/>
       <c r="BY85" s="49"/>
     </row>
-    <row r="86" spans="1:77" ht="42">
+    <row r="86" spans="1:77" ht="42.75">
       <c r="A86" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="4" t="s">
@@ -19057,16 +19058,16 @@
       <c r="BX86" s="49"/>
       <c r="BY86" s="49"/>
     </row>
-    <row r="87" spans="1:77" ht="70">
+    <row r="87" spans="1:77" ht="71.25">
       <c r="A87" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C87" s="8"/>
       <c r="D87" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="4">
@@ -19252,12 +19253,12 @@
       <c r="BX87" s="49"/>
       <c r="BY87" s="49"/>
     </row>
-    <row r="88" spans="1:77" ht="42">
+    <row r="88" spans="1:77" ht="42.75">
       <c r="A88" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="4" t="s">
@@ -19445,7 +19446,7 @@
       <c r="BX88" s="49"/>
       <c r="BY88" s="49"/>
     </row>
-    <row r="89" spans="1:77" ht="42">
+    <row r="89" spans="1:77" ht="42.75">
       <c r="A89" s="21" t="s">
         <v>258</v>
       </c>
@@ -19638,7 +19639,7 @@
       <c r="BX89" s="49"/>
       <c r="BY89" s="49"/>
     </row>
-    <row r="90" spans="1:77" ht="28">
+    <row r="90" spans="1:77" ht="28.5">
       <c r="A90" s="37" t="s">
         <v>260</v>
       </c>
@@ -20024,7 +20025,7 @@
       <c r="BX91" s="49"/>
       <c r="BY91" s="49"/>
     </row>
-    <row r="92" spans="1:77" ht="28">
+    <row r="92" spans="1:77" ht="28.5">
       <c r="A92" s="37" t="s">
         <v>264</v>
       </c>
@@ -20217,7 +20218,7 @@
       <c r="BX92" s="49"/>
       <c r="BY92" s="49"/>
     </row>
-    <row r="93" spans="1:77" ht="56">
+    <row r="93" spans="1:77" ht="57">
       <c r="A93" s="37" t="s">
         <v>266</v>
       </c>
@@ -20410,7 +20411,7 @@
       <c r="BX93" s="49"/>
       <c r="BY93" s="49"/>
     </row>
-    <row r="94" spans="1:77" ht="28">
+    <row r="94" spans="1:77" ht="28.5">
       <c r="A94" s="37" t="s">
         <v>268</v>
       </c>
@@ -20603,7 +20604,7 @@
       <c r="BX94" s="49"/>
       <c r="BY94" s="49"/>
     </row>
-    <row r="95" spans="1:77" ht="34" customHeight="1">
+    <row r="95" spans="1:77" ht="33.950000000000003" customHeight="1">
       <c r="A95" s="37" t="s">
         <v>270</v>
       </c>
@@ -20794,18 +20795,18 @@
       <c r="BX95" s="49"/>
       <c r="BY95" s="49"/>
     </row>
-    <row r="96" spans="1:77" ht="98">
+    <row r="96" spans="1:77" ht="99.75">
       <c r="A96" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>271</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="11">
@@ -20989,18 +20990,18 @@
       <c r="BX96" s="49"/>
       <c r="BY96" s="49"/>
     </row>
-    <row r="97" spans="1:77" ht="98">
+    <row r="97" spans="1:77" ht="99.75">
       <c r="A97" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>128</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="11">
@@ -21184,18 +21185,18 @@
       <c r="BX97" s="49"/>
       <c r="BY97" s="49"/>
     </row>
-    <row r="98" spans="1:77" ht="56">
+    <row r="98" spans="1:77" ht="57">
       <c r="A98" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>271</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="11">
@@ -21379,18 +21380,18 @@
       <c r="BX98" s="49"/>
       <c r="BY98" s="49"/>
     </row>
-    <row r="99" spans="1:77" ht="56">
+    <row r="99" spans="1:77" ht="57">
       <c r="A99" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>128</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="11">
@@ -21574,18 +21575,18 @@
       <c r="BX99" s="49"/>
       <c r="BY99" s="49"/>
     </row>
-    <row r="100" spans="1:77" ht="42">
+    <row r="100" spans="1:77" ht="57">
       <c r="A100" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>271</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="11">
@@ -21769,18 +21770,18 @@
       <c r="BX100" s="49"/>
       <c r="BY100" s="49"/>
     </row>
-    <row r="101" spans="1:77" ht="42">
+    <row r="101" spans="1:77" ht="57">
       <c r="A101" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>128</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="11">
@@ -21964,12 +21965,12 @@
       <c r="BX101" s="49"/>
       <c r="BY101" s="49"/>
     </row>
-    <row r="102" spans="1:77" ht="28">
+    <row r="102" spans="1:77" ht="28.5">
       <c r="A102" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>273</v>
@@ -22171,12 +22172,12 @@
       <c r="BX102" s="49"/>
       <c r="BY102" s="49"/>
     </row>
-    <row r="103" spans="1:77" ht="42">
+    <row r="103" spans="1:77" ht="57">
       <c r="A103" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="4" t="s">
@@ -22376,12 +22377,12 @@
       <c r="BX103" s="49"/>
       <c r="BY103" s="49"/>
     </row>
-    <row r="104" spans="1:77" ht="56">
+    <row r="104" spans="1:77" ht="57">
       <c r="A104" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C104" s="8"/>
       <c r="D104" s="4" t="s">
@@ -22579,7 +22580,7 @@
       <c r="BX104" s="49"/>
       <c r="BY104" s="49"/>
     </row>
-    <row r="105" spans="1:77" ht="42">
+    <row r="105" spans="1:77" ht="42.75">
       <c r="A105" s="12" t="s">
         <v>281</v>
       </c>
@@ -22782,7 +22783,7 @@
       <c r="BX105" s="49"/>
       <c r="BY105" s="49"/>
     </row>
-    <row r="106" spans="1:77" ht="42">
+    <row r="106" spans="1:77" ht="42.75">
       <c r="A106" s="12" t="s">
         <v>283</v>
       </c>
@@ -22987,7 +22988,7 @@
       <c r="BX106" s="49"/>
       <c r="BY106" s="49"/>
     </row>
-    <row r="107" spans="1:77" ht="42">
+    <row r="107" spans="1:77" ht="42.75">
       <c r="A107" s="37" t="s">
         <v>285</v>
       </c>
@@ -23192,7 +23193,7 @@
       <c r="BX107" s="49"/>
       <c r="BY107" s="49"/>
     </row>
-    <row r="108" spans="1:77" ht="56">
+    <row r="108" spans="1:77" ht="57">
       <c r="A108" s="37" t="s">
         <v>287</v>
       </c>
@@ -23395,7 +23396,7 @@
       <c r="BX108" s="49"/>
       <c r="BY108" s="49"/>
     </row>
-    <row r="109" spans="1:77" ht="28">
+    <row r="109" spans="1:77" ht="28.5">
       <c r="A109" s="37" t="s">
         <v>289</v>
       </c>
@@ -23588,7 +23589,7 @@
       <c r="BX109" s="49"/>
       <c r="BY109" s="49"/>
     </row>
-    <row r="110" spans="1:77" ht="98">
+    <row r="110" spans="1:77" ht="99.75">
       <c r="A110" s="37" t="s">
         <v>291</v>
       </c>
@@ -23781,7 +23782,7 @@
       <c r="BX110" s="49"/>
       <c r="BY110" s="49"/>
     </row>
-    <row r="111" spans="1:77" ht="70">
+    <row r="111" spans="1:77" ht="71.25">
       <c r="A111" s="37" t="s">
         <v>293</v>
       </c>
@@ -24177,7 +24178,7 @@
       <c r="BX112" s="49"/>
       <c r="BY112" s="49"/>
     </row>
-    <row r="113" spans="1:77" ht="28">
+    <row r="113" spans="1:77" ht="28.5">
       <c r="A113" s="29" t="s">
         <v>298</v>
       </c>
@@ -24380,12 +24381,12 @@
       <c r="BX113" s="49"/>
       <c r="BY113" s="49"/>
     </row>
-    <row r="114" spans="1:77" ht="70">
+    <row r="114" spans="1:77" ht="71.25">
       <c r="A114" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="5" t="s">
@@ -24575,12 +24576,12 @@
       <c r="BX114" s="49"/>
       <c r="BY114" s="49"/>
     </row>
-    <row r="115" spans="1:77" ht="28">
+    <row r="115" spans="1:77" ht="28.5">
       <c r="A115" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="4" t="s">
@@ -24770,12 +24771,12 @@
       <c r="BX115" s="49"/>
       <c r="BY115" s="49"/>
     </row>
-    <row r="116" spans="1:77" ht="28">
+    <row r="116" spans="1:77" ht="42.75">
       <c r="A116" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C116" s="8"/>
       <c r="D116" s="4" t="s">
@@ -24965,7 +24966,7 @@
       <c r="BX116" s="49"/>
       <c r="BY116" s="49"/>
     </row>
-    <row r="117" spans="1:77" ht="98">
+    <row r="117" spans="1:77" ht="114">
       <c r="A117" s="12" t="s">
         <v>306</v>
       </c>
@@ -25160,7 +25161,7 @@
       <c r="BX117" s="49"/>
       <c r="BY117" s="49"/>
     </row>
-    <row r="118" spans="1:77" ht="56">
+    <row r="118" spans="1:77" ht="71.25">
       <c r="A118" s="44" t="s">
         <v>308</v>
       </c>
@@ -25355,7 +25356,7 @@
       <c r="BX118" s="49"/>
       <c r="BY118" s="49"/>
     </row>
-    <row r="119" spans="1:77" ht="42">
+    <row r="119" spans="1:77" ht="42.75">
       <c r="A119" s="37" t="s">
         <v>311</v>
       </c>
@@ -25554,7 +25555,7 @@
       <c r="BX119" s="49"/>
       <c r="BY119" s="49"/>
     </row>
-    <row r="120" spans="1:77" ht="42">
+    <row r="120" spans="1:77" ht="42.75">
       <c r="A120" s="37" t="s">
         <v>313</v>
       </c>
@@ -25753,16 +25754,16 @@
       <c r="BX120" s="49"/>
       <c r="BY120" s="49"/>
     </row>
-    <row r="121" spans="1:77" ht="42">
+    <row r="121" spans="1:77" ht="42.75">
       <c r="A121" s="5" t="s">
         <v>315</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C121" s="5"/>
       <c r="D121" s="8" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>316</v>
@@ -25950,14 +25951,14 @@
       <c r="BX121" s="49"/>
       <c r="BY121" s="49"/>
     </row>
-    <row r="122" spans="1:77" ht="42">
+    <row r="122" spans="1:77" ht="42.75">
       <c r="A122" s="5"/>
       <c r="B122" s="8" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C122" s="5"/>
       <c r="D122" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>319</v>
@@ -26145,16 +26146,16 @@
       <c r="BX122" s="49"/>
       <c r="BY122" s="49"/>
     </row>
-    <row r="123" spans="1:77" ht="70">
+    <row r="123" spans="1:77" ht="71.25">
       <c r="A123" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B123" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C123" s="8"/>
       <c r="D123" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="4">
@@ -26338,7 +26339,7 @@
       <c r="BX123" s="49"/>
       <c r="BY123" s="49"/>
     </row>
-    <row r="124" spans="1:77" ht="84">
+    <row r="124" spans="1:77" ht="99.75">
       <c r="A124" s="21" t="s">
         <v>322</v>
       </c>
@@ -26535,7 +26536,7 @@
       <c r="BX124" s="49"/>
       <c r="BY124" s="49"/>
     </row>
-    <row r="125" spans="1:77" ht="28">
+    <row r="125" spans="1:77" ht="28.5">
       <c r="A125" s="21"/>
       <c r="B125" s="21" t="s">
         <v>322</v>
@@ -26672,7 +26673,7 @@
       <c r="BX125" s="49"/>
       <c r="BY125" s="49"/>
     </row>
-    <row r="126" spans="1:77" ht="56">
+    <row r="126" spans="1:77" ht="57">
       <c r="A126" s="37" t="s">
         <v>328</v>
       </c>
@@ -26980,7 +26981,7 @@
       <c r="BX127" s="49"/>
       <c r="BY127" s="49"/>
     </row>
-    <row r="128" spans="1:77" ht="70">
+    <row r="128" spans="1:77" ht="71.25">
       <c r="A128" s="21" t="s">
         <v>333</v>
       </c>
@@ -27177,7 +27178,7 @@
       <c r="BX128" s="49"/>
       <c r="BY128" s="49"/>
     </row>
-    <row r="129" spans="1:77" ht="42">
+    <row r="129" spans="1:77" ht="42.75">
       <c r="A129" s="37" t="s">
         <v>336</v>
       </c>
@@ -27372,7 +27373,7 @@
       <c r="BX129" s="49"/>
       <c r="BY129" s="49"/>
     </row>
-    <row r="130" spans="1:77" ht="42">
+    <row r="130" spans="1:77" ht="42.75">
       <c r="A130" s="37"/>
       <c r="B130" s="37" t="s">
         <v>336</v>
@@ -27565,7 +27566,7 @@
       <c r="BX130" s="49"/>
       <c r="BY130" s="49"/>
     </row>
-    <row r="131" spans="1:77" ht="56">
+    <row r="131" spans="1:77" ht="57">
       <c r="A131" s="37" t="s">
         <v>340</v>
       </c>
@@ -27762,7 +27763,7 @@
       <c r="BX131" s="49"/>
       <c r="BY131" s="49"/>
     </row>
-    <row r="132" spans="1:77" ht="28">
+    <row r="132" spans="1:77" ht="42.75">
       <c r="A132" s="37" t="s">
         <v>344</v>
       </c>
@@ -27961,7 +27962,7 @@
       <c r="BX132" s="49"/>
       <c r="BY132" s="49"/>
     </row>
-    <row r="133" spans="1:77" ht="98">
+    <row r="133" spans="1:77" ht="114">
       <c r="A133" s="37" t="s">
         <v>348</v>
       </c>
@@ -28156,7 +28157,7 @@
       <c r="BX133" s="49"/>
       <c r="BY133" s="49"/>
     </row>
-    <row r="134" spans="1:77" ht="28">
+    <row r="134" spans="1:77" ht="28.5">
       <c r="A134" s="29"/>
       <c r="B134" s="37" t="s">
         <v>348</v>
@@ -28347,7 +28348,7 @@
       <c r="BX134" s="49"/>
       <c r="BY134" s="49"/>
     </row>
-    <row r="135" spans="1:77" ht="42">
+    <row r="135" spans="1:77" ht="42.75">
       <c r="A135" s="30" t="s">
         <v>352</v>
       </c>
@@ -28542,7 +28543,7 @@
       <c r="BX135" s="49"/>
       <c r="BY135" s="49"/>
     </row>
-    <row r="136" spans="1:77" ht="56">
+    <row r="136" spans="1:77" ht="57">
       <c r="A136" s="29" t="s">
         <v>355</v>
       </c>
@@ -28737,7 +28738,7 @@
       <c r="BX136" s="49"/>
       <c r="BY136" s="49"/>
     </row>
-    <row r="137" spans="1:77" ht="42">
+    <row r="137" spans="1:77" ht="42.75">
       <c r="A137" s="29" t="s">
         <v>360</v>
       </c>
@@ -29041,7 +29042,7 @@
       <c r="BX138" s="49"/>
       <c r="BY138" s="49"/>
     </row>
-    <row r="139" spans="1:77" ht="56">
+    <row r="139" spans="1:77" ht="57">
       <c r="A139" s="29" t="s">
         <v>363</v>
       </c>
@@ -29347,7 +29348,7 @@
       <c r="BX140" s="49"/>
       <c r="BY140" s="49"/>
     </row>
-    <row r="141" spans="1:77" ht="112">
+    <row r="141" spans="1:77" ht="114">
       <c r="A141" s="32" t="s">
         <v>368</v>
       </c>
@@ -29649,7 +29650,7 @@
       <c r="BX142" s="49"/>
       <c r="BY142" s="49"/>
     </row>
-    <row r="143" spans="1:77" ht="84">
+    <row r="143" spans="1:77" ht="99.75">
       <c r="A143" s="29" t="s">
         <v>373</v>
       </c>
@@ -29981,7 +29982,7 @@
       <c r="BX144" s="49"/>
       <c r="BY144" s="49"/>
     </row>
-    <row r="145" spans="1:77" ht="28">
+    <row r="145" spans="1:77" ht="28.5">
       <c r="A145" s="29" t="s">
         <v>376</v>
       </c>
@@ -30174,7 +30175,7 @@
       <c r="BX145" s="49"/>
       <c r="BY145" s="49"/>
     </row>
-    <row r="146" spans="1:77" ht="56">
+    <row r="146" spans="1:77" ht="71.25">
       <c r="A146" s="29" t="s">
         <v>379</v>
       </c>
@@ -30371,7 +30372,7 @@
       <c r="BX146" s="49"/>
       <c r="BY146" s="49"/>
     </row>
-    <row r="147" spans="1:77" ht="28">
+    <row r="147" spans="1:77" ht="28.5">
       <c r="A147" s="29" t="s">
         <v>382</v>
       </c>
@@ -30741,16 +30742,16 @@
       <c r="BX148" s="49"/>
       <c r="BY148" s="49"/>
     </row>
-    <row r="149" spans="1:77" ht="56">
+    <row r="149" spans="1:77" ht="57">
       <c r="A149" s="29" t="s">
         <v>385</v>
       </c>
       <c r="B149" s="29" t="s">
-        <v>386</v>
+        <v>485</v>
       </c>
       <c r="C149" s="29"/>
       <c r="D149" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E149" s="4"/>
       <c r="F149" s="17">
@@ -30760,7 +30761,7 @@
         <v>61</v>
       </c>
       <c r="H149" s="15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I149" s="4">
         <v>1</v>
@@ -30937,25 +30938,25 @@
         <v>1.5</v>
       </c>
       <c r="BW149" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="BX149" s="49">
         <v>5</v>
       </c>
       <c r="BY149" s="49" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="150" spans="1:77" ht="99.75">
+      <c r="A150" s="29" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="150" spans="1:77" ht="98">
-      <c r="A150" s="29" t="s">
-        <v>391</v>
-      </c>
       <c r="B150" s="29" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C150" s="29"/>
       <c r="D150" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E150" s="4"/>
       <c r="F150" s="17">
@@ -30965,7 +30966,7 @@
         <v>61</v>
       </c>
       <c r="H150" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I150" s="4">
         <v>1</v>
@@ -30977,7 +30978,7 @@
         <v>1.6</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M150" s="4" t="s">
         <v>120</v>
@@ -31144,25 +31145,25 @@
         <v>0.6</v>
       </c>
       <c r="BW150" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="BX150" s="49">
         <v>5</v>
       </c>
       <c r="BY150" s="49" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="151" spans="1:77" ht="57">
+      <c r="A151" s="29" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="151" spans="1:77" ht="56">
-      <c r="A151" s="29" t="s">
-        <v>396</v>
-      </c>
       <c r="B151" s="29" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C151" s="29"/>
       <c r="D151" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="17">
@@ -31172,7 +31173,7 @@
         <v>61</v>
       </c>
       <c r="H151" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I151" s="4">
         <v>1</v>
@@ -31349,25 +31350,25 @@
         <v>0.5</v>
       </c>
       <c r="BW151" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="BX151" s="49">
         <v>5</v>
       </c>
       <c r="BY151" s="49" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="152" spans="1:77" ht="42.75">
+      <c r="A152" s="29" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="152" spans="1:77" ht="42">
-      <c r="A152" s="29" t="s">
-        <v>400</v>
-      </c>
       <c r="B152" s="29" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C152" s="29"/>
       <c r="D152" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E152" s="4"/>
       <c r="F152" s="17">
@@ -31377,7 +31378,7 @@
         <v>61</v>
       </c>
       <c r="H152" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I152" s="4">
         <v>1</v>
@@ -31389,7 +31390,7 @@
         <v>4</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="M152" s="4" t="s">
         <v>120</v>
@@ -31556,25 +31557,25 @@
         <v>0.4</v>
       </c>
       <c r="BW152" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="BX152" s="49">
         <v>5</v>
       </c>
       <c r="BY152" s="49" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="153" spans="1:77" ht="28.5">
+      <c r="A153" s="29" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="153" spans="1:77" ht="28">
-      <c r="A153" s="29" t="s">
-        <v>403</v>
-      </c>
       <c r="B153" s="29" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C153" s="29"/>
       <c r="D153" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="17">
@@ -31584,7 +31585,7 @@
         <v>61</v>
       </c>
       <c r="H153" s="17" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I153" s="4">
         <v>1</v>
@@ -31761,25 +31762,25 @@
         <v>1</v>
       </c>
       <c r="BW153" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="BX153" s="49">
         <v>5</v>
       </c>
       <c r="BY153" s="49" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
-    <row r="154" spans="1:77" ht="42">
+    <row r="154" spans="1:77" ht="42.75">
       <c r="A154" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C154" s="8"/>
       <c r="D154" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E154" s="4"/>
       <c r="F154" s="37">
@@ -31789,7 +31790,7 @@
         <v>59</v>
       </c>
       <c r="H154" s="50" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I154" s="8">
         <v>1</v>
@@ -31963,16 +31964,16 @@
       <c r="BX154" s="49"/>
       <c r="BY154" s="49"/>
     </row>
-    <row r="155" spans="1:77" ht="70">
+    <row r="155" spans="1:77" ht="71.25">
       <c r="A155" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C155" s="4"/>
       <c r="D155" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E155" s="4"/>
       <c r="F155" s="37">
@@ -31982,7 +31983,7 @@
         <v>61</v>
       </c>
       <c r="H155" s="37" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I155" s="4">
         <v>10</v>
@@ -32156,16 +32157,16 @@
       <c r="BX155" s="49"/>
       <c r="BY155" s="49"/>
     </row>
-    <row r="156" spans="1:77" ht="70">
+    <row r="156" spans="1:77" ht="71.25">
       <c r="A156" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C156" s="8"/>
       <c r="D156" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E156" s="4"/>
       <c r="F156" s="37">
@@ -32175,7 +32176,7 @@
         <v>61</v>
       </c>
       <c r="H156" s="50" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I156" s="4">
         <v>5</v>
@@ -32349,18 +32350,18 @@
       <c r="BX156" s="49"/>
       <c r="BY156" s="49"/>
     </row>
-    <row r="157" spans="1:77" ht="56">
+    <row r="157" spans="1:77" ht="57">
       <c r="A157" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D157" s="8" t="s">
         <v>484</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="D157" s="8" t="s">
-        <v>485</v>
       </c>
       <c r="E157" s="4"/>
       <c r="F157" s="37">
@@ -32370,7 +32371,7 @@
         <v>61</v>
       </c>
       <c r="H157" s="50" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I157" s="4">
         <v>1</v>
@@ -32544,14 +32545,14 @@
       <c r="BX157" s="49"/>
       <c r="BY157" s="49"/>
     </row>
-    <row r="158" spans="1:77" ht="56">
+    <row r="158" spans="1:77" ht="57">
       <c r="A158" s="51"/>
       <c r="B158" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C158" s="5"/>
       <c r="D158" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E158" s="4"/>
       <c r="F158" s="37">
@@ -32559,7 +32560,7 @@
       </c>
       <c r="G158" s="4"/>
       <c r="H158" s="50" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I158" s="4">
         <v>1</v>

--- a/Assets/StreamingAssets/Excel/CardConfig.xlsx
+++ b/Assets/StreamingAssets/Excel/CardConfig.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8757FBC2-D07E-43E8-B275-9621CBEB44C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BBE53D-C6AB-4BDF-B0E7-F073252F976E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="28800" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -913,10 +913,6 @@
     <t>自热烹饪袋</t>
   </si>
   <si>
-    <t>耐压的双层硅胶袋，在水下也能用。内层装食物，夹层填充燃料和催化剂。仅用于将食物简单做熟，无法制作高端料理，料理烹饪需要使用燃料炉。
-（将自热烹饪袋拖到需要加热的食物上，消耗15分钟加热）</t>
-  </si>
-  <si>
     <t>凝胶装瓶器</t>
   </si>
   <si>
@@ -938,7 +934,8 @@
     <t>矛的尖端生了锈，或许可以造成毒伤（并不能）</t>
   </si>
   <si>
-    <t>用于水下探索的简易氧气面罩,让麦麦能看清水下世界。（佩戴后氧气上限+60。不戴氧气面罩探索水域地点要消耗更多时间，且每次探索时损失生命）</t>
+    <t>用于水下探索的简易氧气面罩,让麦麦能看清水下世界。
+（未装备时探索水域地点消耗更多时间，且会损失生命值）</t>
   </si>
   <si>
     <t>Equipment</t>
@@ -959,17 +956,13 @@
     <t>重型氧气罐</t>
   </si>
   <si>
-    <t>越大的氧气罐就能容纳更多氧气，越大就越好。基于这样的理念，麦麦做了一个巨大的氧气罐。
-（佩戴后氧气上限+800。装备后在地点间的移动额外消耗20%时间，探索额外消耗20%时间。
-）</t>
+    <t>越大的氧气罐就能容纳更多氧气，越大就越好。基于这样的理念，麦麦做了一个巨大的氧气罐。</t>
   </si>
   <si>
     <t>脚蹼</t>
   </si>
   <si>
-    <t>使用白塔星特殊鱼皮制成的潜水脚蹼，让麦麦能在水中更快地移动。
-前往水域地点时-30%移动耗时。
-在水域地点中+30%移动速度。</t>
+    <t>使用白塔星特殊鱼皮制成的潜水脚蹼，让麦麦能在水中更快地移动。</t>
   </si>
   <si>
     <t>Leg</t>
@@ -1092,9 +1085,7 @@
     <t>睡眠脉冲仪</t>
   </si>
   <si>
-    <t>睡眠脉冲仪能通过低频脉冲，刺激大脑释放促进睡眠的神经递质。
-多个睡眠脉冲仪无法叠加效果。
-（开启状态下在安装了睡眠脉冲仪的地点休息，休息时每回合额外+1.2清醒度和1健康，并消耗0.6电力）</t>
+    <t>睡眠脉冲仪能通过低频脉冲，刺激大脑释放促进睡眠的神经递质。</t>
   </si>
   <si>
     <t>精密元件*1+玻璃*1+电池*1</t>
@@ -1131,8 +1122,7 @@
     <t>冰箱</t>
   </si>
   <si>
-    <t>大大延缓食物的腐烂速度。
-（开启状态下每15分钟消耗0.3电力，内容物腐烂速度延缓50%）</t>
+    <t>大大延缓食物的腐烂速度。</t>
   </si>
   <si>
     <t>钢材*1+精密元件*1+石砖*2</t>
@@ -1158,7 +1148,7 @@
   </si>
   <si>
     <t>有了数据传输台后，麦麦就能将自己在这颗星球上记录的样本数据详细地传输出去，这将对科技研究有很大帮助。
-（在建造数据传输台后将解锁中级科技的研究。研究中级科技时每15分钟消耗0.5单位电力，电力不足将无法进行中级科技研究）</t>
+（建造后将解锁中级科技的研究。研究中级科技时将消耗电力，电力不足将无法进行中级科技研究）</t>
   </si>
   <si>
     <t>待机</t>
@@ -1174,9 +1164,6 @@
     <t>燃料蒸馏器</t>
   </si>
   <si>
-    <t>使用燃料加热蒸馏海水的传统蒸馏设施，自带凝胶装瓶功能。将盐水拖入后会增加盐水储量，点燃状态下的燃料蒸馏器能缓慢将盐水蒸馏为淡水。当淡水储量达到12时，会在内容物槽生成一瓶瓶装水。</t>
-  </si>
-  <si>
     <t>韧性胶管*2+钢材*1+玻璃*1</t>
   </si>
   <si>
@@ -1271,8 +1258,7 @@
     <t>Other</t>
   </si>
   <si>
-    <t>无需氧气助燃的化学氧烛,顶部有一个引信,按下后内部就会开始反应,在水下也能轻松点燃。
-(氧烛点燃后每15分钟产生10氧气,氧烛一共能产生140氧气)</t>
+    <t>无需氧气助燃的化学氧烛,顶部有一个引信,按下后内部就会开始反应,在水下也能轻松点燃。</t>
   </si>
   <si>
     <t>氧烛</t>
@@ -1507,6 +1493,15 @@
   </si>
   <si>
     <t>燃烧期间的氧烛会不断产生氧气,可以作为探索时的氧气来源,当氧烛快要燃烧殆尽时,记得及时返回。</t>
+  </si>
+  <si>
+    <t>耐压的双层硅胶袋，在水下也能用。内层装食物，夹层填充燃料和催化剂。仅用于将食物简单做熟，无法制作高端料理，料理烹饪需要使用燃料炉。
+（将自热烹饪袋拖到食物上来进行简单烹饪）</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用燃料加热蒸馏海水的传统蒸馏设施，自带凝胶装瓶功能。</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1627,7 +1622,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1674,11 +1669,6 @@
       <patternFill patternType="none">
         <fgColor auto="1"/>
         <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE3C36"/>
       </patternFill>
     </fill>
     <fill>
@@ -1743,7 +1733,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1840,16 +1830,10 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1858,7 +1842,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1873,13 +1857,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1909,7 +1893,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2246,136 +2230,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BZ160"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="28.58203125" style="61" customWidth="1"/>
-    <col min="2" max="3" width="11.4140625" style="61" customWidth="1"/>
-    <col min="4" max="4" width="28.08203125" style="72" customWidth="1"/>
-    <col min="5" max="5" width="18.75" style="73" customWidth="1"/>
-    <col min="6" max="6" width="15.58203125" style="61" customWidth="1"/>
-    <col min="7" max="7" width="8.58203125" style="61" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" style="61" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" style="61" customWidth="1"/>
-    <col min="10" max="10" width="10.1640625" style="61" customWidth="1"/>
-    <col min="11" max="11" width="6.83203125" style="61" customWidth="1"/>
-    <col min="12" max="12" width="13" style="61" customWidth="1"/>
-    <col min="13" max="13" width="18.75" style="73" customWidth="1"/>
-    <col min="14" max="14" width="12.1640625" style="61" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" style="61" customWidth="1"/>
-    <col min="16" max="25" width="19" style="61" customWidth="1"/>
-    <col min="26" max="26" width="10.1640625" style="61" customWidth="1"/>
-    <col min="27" max="29" width="12.5" style="61" customWidth="1"/>
-    <col min="30" max="32" width="11.1640625" style="61" customWidth="1"/>
-    <col min="33" max="33" width="12.25" style="61" customWidth="1"/>
-    <col min="34" max="42" width="8.58203125" style="61"/>
-    <col min="43" max="43" width="11.6640625" style="61" customWidth="1"/>
-    <col min="44" max="44" width="9.1640625" style="61" customWidth="1"/>
-    <col min="45" max="45" width="12" style="61" customWidth="1"/>
-    <col min="46" max="46" width="11.6640625" style="61" customWidth="1"/>
-    <col min="47" max="47" width="8.58203125" style="61" customWidth="1"/>
-    <col min="48" max="48" width="9.25" style="61" customWidth="1"/>
-    <col min="49" max="49" width="14.5" style="61" customWidth="1"/>
-    <col min="50" max="50" width="12.58203125" style="61" customWidth="1"/>
-    <col min="51" max="51" width="11" style="61" customWidth="1"/>
-    <col min="52" max="52" width="12.4140625" style="61" customWidth="1"/>
-    <col min="53" max="53" width="10.1640625" style="61" customWidth="1"/>
-    <col min="54" max="54" width="11.58203125" style="61" customWidth="1"/>
-    <col min="55" max="55" width="10.08203125" style="61" customWidth="1"/>
-    <col min="56" max="56" width="16.08203125" style="61" customWidth="1"/>
-    <col min="57" max="57" width="14" style="61" customWidth="1"/>
-    <col min="58" max="58" width="12" style="61" customWidth="1"/>
-    <col min="59" max="59" width="13.75" style="74" customWidth="1"/>
-    <col min="60" max="60" width="18.75" style="61" customWidth="1"/>
-    <col min="61" max="61" width="12.4140625" style="61" customWidth="1"/>
-    <col min="62" max="62" width="22.58203125" style="61" customWidth="1"/>
-    <col min="63" max="63" width="15.08203125" style="61" customWidth="1"/>
-    <col min="64" max="64" width="9.9140625" style="61" customWidth="1"/>
-    <col min="65" max="65" width="11.4140625" style="61" customWidth="1"/>
-    <col min="66" max="66" width="7.25" style="61" customWidth="1"/>
-    <col min="67" max="67" width="12.1640625" style="61" customWidth="1"/>
-    <col min="68" max="68" width="12.75" style="61" customWidth="1"/>
-    <col min="69" max="69" width="14.58203125" style="61" customWidth="1"/>
-    <col min="70" max="70" width="14.5" style="61" customWidth="1"/>
-    <col min="71" max="71" width="13.08203125" style="75" customWidth="1"/>
-    <col min="72" max="77" width="8.58203125" style="75"/>
-    <col min="78" max="78" width="18.75" style="70" customWidth="1"/>
+    <col min="1" max="1" width="28.625" style="59" customWidth="1"/>
+    <col min="2" max="3" width="11.375" style="59" customWidth="1"/>
+    <col min="4" max="4" width="28.125" style="70" customWidth="1"/>
+    <col min="5" max="5" width="18.75" style="71" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="59" customWidth="1"/>
+    <col min="7" max="7" width="8.625" style="59" customWidth="1"/>
+    <col min="8" max="8" width="15.375" style="59" customWidth="1"/>
+    <col min="9" max="9" width="10.25" style="59" customWidth="1"/>
+    <col min="10" max="10" width="10.125" style="59" customWidth="1"/>
+    <col min="11" max="11" width="6.875" style="59" customWidth="1"/>
+    <col min="12" max="12" width="13" style="59" customWidth="1"/>
+    <col min="13" max="13" width="18.75" style="71" customWidth="1"/>
+    <col min="14" max="14" width="12.125" style="59" customWidth="1"/>
+    <col min="15" max="15" width="13.125" style="59" customWidth="1"/>
+    <col min="16" max="25" width="19" style="59" customWidth="1"/>
+    <col min="26" max="26" width="10.125" style="59" customWidth="1"/>
+    <col min="27" max="29" width="12.5" style="59" customWidth="1"/>
+    <col min="30" max="32" width="11.125" style="59" customWidth="1"/>
+    <col min="33" max="33" width="12.25" style="59" customWidth="1"/>
+    <col min="34" max="42" width="8.625" style="59"/>
+    <col min="43" max="43" width="11.625" style="59" customWidth="1"/>
+    <col min="44" max="44" width="9.25" style="59" customWidth="1"/>
+    <col min="45" max="45" width="12" style="59" customWidth="1"/>
+    <col min="46" max="46" width="11.75" style="59" customWidth="1"/>
+    <col min="47" max="47" width="8.625" style="59" customWidth="1"/>
+    <col min="48" max="48" width="9.25" style="59" customWidth="1"/>
+    <col min="49" max="49" width="14.5" style="59" customWidth="1"/>
+    <col min="50" max="50" width="12.625" style="59" customWidth="1"/>
+    <col min="51" max="51" width="11" style="59" customWidth="1"/>
+    <col min="52" max="52" width="12.375" style="59" customWidth="1"/>
+    <col min="53" max="53" width="10.25" style="59" customWidth="1"/>
+    <col min="54" max="54" width="11.625" style="59" customWidth="1"/>
+    <col min="55" max="55" width="10.125" style="59" customWidth="1"/>
+    <col min="56" max="56" width="16.125" style="59" customWidth="1"/>
+    <col min="57" max="57" width="14" style="59" customWidth="1"/>
+    <col min="58" max="58" width="12" style="59" customWidth="1"/>
+    <col min="59" max="59" width="13.75" style="72" customWidth="1"/>
+    <col min="60" max="60" width="18.75" style="59" customWidth="1"/>
+    <col min="61" max="61" width="12.375" style="59" customWidth="1"/>
+    <col min="62" max="62" width="22.625" style="59" customWidth="1"/>
+    <col min="63" max="63" width="15.125" style="59" customWidth="1"/>
+    <col min="64" max="64" width="9.875" style="59" customWidth="1"/>
+    <col min="65" max="65" width="11.375" style="59" customWidth="1"/>
+    <col min="66" max="66" width="7.25" style="59" customWidth="1"/>
+    <col min="67" max="67" width="12.125" style="59" customWidth="1"/>
+    <col min="68" max="68" width="12.75" style="59" customWidth="1"/>
+    <col min="69" max="69" width="14.625" style="59" customWidth="1"/>
+    <col min="70" max="70" width="14.5" style="59" customWidth="1"/>
+    <col min="71" max="71" width="13.125" style="73" customWidth="1"/>
+    <col min="72" max="77" width="8.625" style="73"/>
+    <col min="78" max="78" width="18.75" style="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:78" s="71" customFormat="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:78" s="69" customFormat="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>433</v>
       </c>
       <c r="Z1" s="4" t="s">
         <v>4</v>
@@ -2933,7 +2917,7 @@
       <c r="BY3" s="4"/>
       <c r="BZ3" s="4"/>
     </row>
-    <row r="4" spans="1:78" ht="28">
+    <row r="4" spans="1:78" ht="28.5">
       <c r="A4" s="6" t="s">
         <v>71</v>
       </c>
@@ -3329,7 +3313,7 @@
       <c r="BY5" s="4"/>
       <c r="BZ5" s="4"/>
     </row>
-    <row r="6" spans="1:78" ht="84">
+    <row r="6" spans="1:78" ht="85.5">
       <c r="A6" s="13" t="s">
         <v>77</v>
       </c>
@@ -3527,18 +3511,18 @@
       <c r="BY6" s="4"/>
       <c r="BZ6" s="4"/>
     </row>
-    <row r="7" spans="1:78" ht="84">
+    <row r="7" spans="1:78" ht="85.5">
       <c r="A7" s="13" t="s">
         <v>82</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="12">
@@ -3725,11 +3709,11 @@
       <c r="BY7" s="4"/>
       <c r="BZ7" s="4"/>
     </row>
-    <row r="8" spans="1:78" ht="28">
-      <c r="A8" s="39" t="s">
+    <row r="8" spans="1:78" ht="28.5">
+      <c r="A8" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="37" t="s">
         <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -3923,8 +3907,8 @@
       <c r="BY8" s="4"/>
       <c r="BZ8" s="4"/>
     </row>
-    <row r="9" spans="1:78" ht="28">
-      <c r="A9" s="39" t="s">
+    <row r="9" spans="1:78" ht="28.5">
+      <c r="A9" s="37" t="s">
         <v>88</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -4122,7 +4106,7 @@
       <c r="BZ9" s="4"/>
     </row>
     <row r="10" spans="1:78" ht="45" customHeight="1">
-      <c r="A10" s="39" t="s">
+      <c r="A10" s="37" t="s">
         <v>90</v>
       </c>
       <c r="B10" s="30" t="s">
@@ -4320,7 +4304,7 @@
       <c r="BZ10" s="4"/>
     </row>
     <row r="11" spans="1:78" ht="45" customHeight="1">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="37" t="s">
         <v>95</v>
       </c>
       <c r="B11" s="30" t="s">
@@ -4518,7 +4502,7 @@
       <c r="BZ11" s="4"/>
     </row>
     <row r="12" spans="1:78" ht="45" customHeight="1">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="37" t="s">
         <v>97</v>
       </c>
       <c r="B12" s="30" t="s">
@@ -5705,16 +5689,16 @@
       <c r="BY17" s="4"/>
       <c r="BZ17" s="4"/>
     </row>
-    <row r="18" spans="1:78" ht="42">
+    <row r="18" spans="1:78" ht="42.75">
       <c r="A18" s="9" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4">
@@ -5901,12 +5885,12 @@
       <c r="BY18" s="4"/>
       <c r="BZ18" s="4"/>
     </row>
-    <row r="19" spans="1:78" ht="28">
+    <row r="19" spans="1:78" ht="28.5">
       <c r="A19" s="9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="4" t="s">
@@ -6097,16 +6081,16 @@
       <c r="BY19" s="4"/>
       <c r="BZ19" s="4"/>
     </row>
-    <row r="20" spans="1:78" ht="42">
+    <row r="20" spans="1:78" ht="42.75">
       <c r="A20" s="9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4">
@@ -6295,10 +6279,10 @@
     </row>
     <row r="21" spans="1:78">
       <c r="A21" s="9" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="4" t="s">
@@ -6489,7 +6473,7 @@
       <c r="BY21" s="4"/>
       <c r="BZ21" s="4"/>
     </row>
-    <row r="22" spans="1:78" ht="28">
+    <row r="22" spans="1:78" ht="28.5">
       <c r="A22" s="6" t="s">
         <v>127</v>
       </c>
@@ -6500,7 +6484,7 @@
         <v>129</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4">
@@ -6687,16 +6671,16 @@
       <c r="BY22" s="4"/>
       <c r="BZ22" s="4"/>
     </row>
-    <row r="23" spans="1:78" ht="28">
+    <row r="23" spans="1:78" ht="28.5">
       <c r="A23" s="9" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>128</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4">
@@ -6883,12 +6867,12 @@
       <c r="BY23" s="4"/>
       <c r="BZ23" s="4"/>
     </row>
-    <row r="24" spans="1:78" ht="42">
+    <row r="24" spans="1:78" ht="42.75">
       <c r="A24" s="9" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="4" t="s">
@@ -7079,7 +7063,7 @@
       <c r="BY24" s="4"/>
       <c r="BZ24" s="4"/>
     </row>
-    <row r="25" spans="1:78" ht="126">
+    <row r="25" spans="1:78" ht="128.25">
       <c r="A25" s="21" t="s">
         <v>133</v>
       </c>
@@ -7275,7 +7259,7 @@
       <c r="BY25" s="4"/>
       <c r="BZ25" s="4"/>
     </row>
-    <row r="26" spans="1:78" ht="84">
+    <row r="26" spans="1:78" ht="85.5">
       <c r="A26" s="21" t="s">
         <v>135</v>
       </c>
@@ -7471,7 +7455,7 @@
       <c r="BY26" s="4"/>
       <c r="BZ26" s="4"/>
     </row>
-    <row r="27" spans="1:78" ht="70">
+    <row r="27" spans="1:78" ht="85.5">
       <c r="A27" s="21" t="s">
         <v>137</v>
       </c>
@@ -7665,11 +7649,11 @@
       <c r="BY27" s="4"/>
       <c r="BZ27" s="4"/>
     </row>
-    <row r="28" spans="1:78" ht="28">
+    <row r="28" spans="1:78" ht="28.5">
       <c r="A28" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="37" t="s">
         <v>139</v>
       </c>
       <c r="C28" s="26"/>
@@ -7861,11 +7845,11 @@
       <c r="BY28" s="4"/>
       <c r="BZ28" s="4"/>
     </row>
-    <row r="29" spans="1:78" ht="70">
+    <row r="29" spans="1:78" ht="71.25">
       <c r="A29" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="37" t="s">
         <v>141</v>
       </c>
       <c r="C29" s="26"/>
@@ -8055,11 +8039,11 @@
       <c r="BY29" s="4"/>
       <c r="BZ29" s="4"/>
     </row>
-    <row r="30" spans="1:78" ht="70">
+    <row r="30" spans="1:78" ht="71.25">
       <c r="A30" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="37" t="s">
         <v>143</v>
       </c>
       <c r="C30" s="26"/>
@@ -8251,11 +8235,11 @@
       <c r="BY30" s="4"/>
       <c r="BZ30" s="4"/>
     </row>
-    <row r="31" spans="1:78" ht="28">
+    <row r="31" spans="1:78" ht="42.75">
       <c r="A31" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="37" t="s">
         <v>145</v>
       </c>
       <c r="C31" s="26"/>
@@ -8447,11 +8431,11 @@
       <c r="BY31" s="4"/>
       <c r="BZ31" s="4"/>
     </row>
-    <row r="32" spans="1:78" ht="42">
+    <row r="32" spans="1:78" ht="42.75">
       <c r="A32" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B32" s="39" t="s">
+      <c r="B32" s="37" t="s">
         <v>147</v>
       </c>
       <c r="C32" s="26"/>
@@ -8643,11 +8627,11 @@
       <c r="BY32" s="4"/>
       <c r="BZ32" s="4"/>
     </row>
-    <row r="33" spans="1:78" ht="42">
+    <row r="33" spans="1:78" ht="42.75">
       <c r="A33" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="39" t="s">
+      <c r="B33" s="37" t="s">
         <v>149</v>
       </c>
       <c r="C33" s="26"/>
@@ -8839,11 +8823,11 @@
       <c r="BY33" s="4"/>
       <c r="BZ33" s="4"/>
     </row>
-    <row r="34" spans="1:78" ht="28">
+    <row r="34" spans="1:78" ht="42.75">
       <c r="A34" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B34" s="39" t="s">
+      <c r="B34" s="37" t="s">
         <v>151</v>
       </c>
       <c r="C34" s="26"/>
@@ -9035,11 +9019,11 @@
       <c r="BY34" s="4"/>
       <c r="BZ34" s="4"/>
     </row>
-    <row r="35" spans="1:78" ht="42">
+    <row r="35" spans="1:78" ht="42.75">
       <c r="A35" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="37" t="s">
         <v>153</v>
       </c>
       <c r="C35" s="26"/>
@@ -9231,11 +9215,11 @@
       <c r="BY35" s="4"/>
       <c r="BZ35" s="4"/>
     </row>
-    <row r="36" spans="1:78" ht="70">
+    <row r="36" spans="1:78" ht="71.25">
       <c r="A36" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="37" t="s">
         <v>155</v>
       </c>
       <c r="C36" s="26"/>
@@ -9427,11 +9411,11 @@
       <c r="BY36" s="4"/>
       <c r="BZ36" s="4"/>
     </row>
-    <row r="37" spans="1:78" ht="28">
-      <c r="A37" s="39" t="s">
+    <row r="37" spans="1:78" ht="28.5">
+      <c r="A37" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="37" t="s">
         <v>122</v>
       </c>
       <c r="C37" s="4"/>
@@ -9623,11 +9607,11 @@
       <c r="BY37" s="4"/>
       <c r="BZ37" s="4"/>
     </row>
-    <row r="38" spans="1:78" ht="28">
-      <c r="A38" s="39" t="s">
+    <row r="38" spans="1:78" ht="28.5">
+      <c r="A38" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="B38" s="39" t="s">
+      <c r="B38" s="37" t="s">
         <v>123</v>
       </c>
       <c r="C38" s="4"/>
@@ -9819,11 +9803,11 @@
       <c r="BY38" s="4"/>
       <c r="BZ38" s="4"/>
     </row>
-    <row r="39" spans="1:78" ht="28">
-      <c r="A39" s="39" t="s">
+    <row r="39" spans="1:78" ht="28.5">
+      <c r="A39" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="37" t="s">
         <v>159</v>
       </c>
       <c r="C39" s="4"/>
@@ -10015,11 +9999,11 @@
       <c r="BY39" s="4"/>
       <c r="BZ39" s="4"/>
     </row>
-    <row r="40" spans="1:78" ht="56">
-      <c r="A40" s="39" t="s">
+    <row r="40" spans="1:78" ht="57">
+      <c r="A40" s="37" t="s">
         <v>126</v>
       </c>
-      <c r="B40" s="39" t="s">
+      <c r="B40" s="37" t="s">
         <v>126</v>
       </c>
       <c r="C40" s="4"/>
@@ -10211,11 +10195,11 @@
       <c r="BY40" s="4"/>
       <c r="BZ40" s="4"/>
     </row>
-    <row r="41" spans="1:78" ht="28">
+    <row r="41" spans="1:78" ht="28.5">
       <c r="A41" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="B41" s="39" t="s">
+      <c r="B41" s="37" t="s">
         <v>162</v>
       </c>
       <c r="C41" s="4"/>
@@ -10407,11 +10391,11 @@
       <c r="BY41" s="4"/>
       <c r="BZ41" s="4"/>
     </row>
-    <row r="42" spans="1:78" ht="28">
+    <row r="42" spans="1:78" ht="28.5">
       <c r="A42" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="B42" s="39" t="s">
+      <c r="B42" s="37" t="s">
         <v>164</v>
       </c>
       <c r="C42" s="4"/>
@@ -10603,7 +10587,7 @@
       <c r="BY42" s="4"/>
       <c r="BZ42" s="4"/>
     </row>
-    <row r="43" spans="1:78" ht="56">
+    <row r="43" spans="1:78" ht="57">
       <c r="A43" s="31" t="s">
         <v>166</v>
       </c>
@@ -10799,11 +10783,11 @@
       <c r="BY43" s="4"/>
       <c r="BZ43" s="4"/>
     </row>
-    <row r="44" spans="1:78" ht="28">
-      <c r="A44" s="32" t="s">
+    <row r="44" spans="1:78" ht="28.5">
+      <c r="A44" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="32" t="s">
         <v>169</v>
       </c>
       <c r="C44" s="4" t="s">
@@ -10819,7 +10803,7 @@
       <c r="G44" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H44" s="33" t="s">
+      <c r="H44" s="32" t="s">
         <v>117</v>
       </c>
       <c r="I44" s="4">
@@ -10993,8 +10977,8 @@
       <c r="BY44" s="4"/>
       <c r="BZ44" s="4"/>
     </row>
-    <row r="45" spans="1:78" ht="28">
-      <c r="A45" s="34" t="s">
+    <row r="45" spans="1:78" ht="42.75">
+      <c r="A45" s="31" t="s">
         <v>172</v>
       </c>
       <c r="B45" s="30" t="s">
@@ -11186,7 +11170,7 @@
       <c r="BZ45" s="4"/>
     </row>
     <row r="46" spans="1:78">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="31" t="s">
         <v>175</v>
       </c>
       <c r="B46" s="30" t="s">
@@ -11377,7 +11361,7 @@
       <c r="BY46" s="4"/>
       <c r="BZ46" s="4"/>
     </row>
-    <row r="47" spans="1:78" ht="28">
+    <row r="47" spans="1:78" ht="28.5">
       <c r="A47" s="31" t="s">
         <v>177</v>
       </c>
@@ -11569,7 +11553,7 @@
       <c r="BY47" s="4"/>
       <c r="BZ47" s="4"/>
     </row>
-    <row r="48" spans="1:78" ht="28">
+    <row r="48" spans="1:78" ht="28.5">
       <c r="A48" s="31" t="s">
         <v>180</v>
       </c>
@@ -11961,7 +11945,7 @@
       <c r="BY49" s="4"/>
       <c r="BZ49" s="4"/>
     </row>
-    <row r="50" spans="1:78" ht="28">
+    <row r="50" spans="1:78" ht="28.5">
       <c r="A50" s="31" t="s">
         <v>184</v>
       </c>
@@ -12153,7 +12137,7 @@
       <c r="BY50" s="4"/>
       <c r="BZ50" s="4"/>
     </row>
-    <row r="51" spans="1:78" ht="70">
+    <row r="51" spans="1:78" ht="71.25">
       <c r="A51" s="31" t="s">
         <v>187</v>
       </c>
@@ -12345,8 +12329,8 @@
       <c r="BY51" s="4"/>
       <c r="BZ51" s="4"/>
     </row>
-    <row r="52" spans="1:78" ht="42">
-      <c r="A52" s="34" t="s">
+    <row r="52" spans="1:78" ht="42.75">
+      <c r="A52" s="31" t="s">
         <v>189</v>
       </c>
       <c r="B52" s="31" t="s">
@@ -12537,7 +12521,7 @@
       <c r="BY52" s="4"/>
       <c r="BZ52" s="4"/>
     </row>
-    <row r="53" spans="1:78" ht="42">
+    <row r="53" spans="1:78" ht="42.75">
       <c r="A53" s="31" t="s">
         <v>191</v>
       </c>
@@ -12729,7 +12713,7 @@
       <c r="BY53" s="4"/>
       <c r="BZ53" s="4"/>
     </row>
-    <row r="54" spans="1:78" ht="42">
+    <row r="54" spans="1:78" ht="42.75">
       <c r="A54" s="31" t="s">
         <v>193</v>
       </c>
@@ -12921,7 +12905,7 @@
       <c r="BY54" s="4"/>
       <c r="BZ54" s="4"/>
     </row>
-    <row r="55" spans="1:78" ht="70">
+    <row r="55" spans="1:78" ht="71.25">
       <c r="A55" s="31" t="s">
         <v>195</v>
       </c>
@@ -13113,7 +13097,7 @@
       <c r="BY55" s="4"/>
       <c r="BZ55" s="4"/>
     </row>
-    <row r="56" spans="1:78" ht="56">
+    <row r="56" spans="1:78" ht="57">
       <c r="A56" s="31" t="s">
         <v>197</v>
       </c>
@@ -13309,7 +13293,7 @@
       <c r="BY56" s="4"/>
       <c r="BZ56" s="4"/>
     </row>
-    <row r="57" spans="1:78" ht="42">
+    <row r="57" spans="1:78" ht="42.75">
       <c r="A57" s="31" t="s">
         <v>199</v>
       </c>
@@ -13317,7 +13301,7 @@
         <v>199</v>
       </c>
       <c r="C57" s="4"/>
-      <c r="D57" s="35" t="s">
+      <c r="D57" s="33" t="s">
         <v>200</v>
       </c>
       <c r="E57" s="4"/>
@@ -13505,11 +13489,11 @@
       <c r="BY57" s="4"/>
       <c r="BZ57" s="4"/>
     </row>
-    <row r="58" spans="1:78" ht="34" customHeight="1">
-      <c r="A58" s="39" t="s">
+    <row r="58" spans="1:78" ht="33.950000000000003" customHeight="1">
+      <c r="A58" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="B58" s="39" t="s">
+      <c r="B58" s="37" t="s">
         <v>201</v>
       </c>
       <c r="C58" s="26"/>
@@ -13523,7 +13507,7 @@
       <c r="G58" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H58" s="36" t="s">
+      <c r="H58" s="34" t="s">
         <v>117</v>
       </c>
       <c r="I58" s="4">
@@ -13701,11 +13685,11 @@
       <c r="BY58" s="4"/>
       <c r="BZ58" s="4"/>
     </row>
-    <row r="59" spans="1:78" ht="34" customHeight="1">
-      <c r="A59" s="39" t="s">
+    <row r="59" spans="1:78" ht="33.950000000000003" customHeight="1">
+      <c r="A59" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="B59" s="39" t="s">
+      <c r="B59" s="37" t="s">
         <v>203</v>
       </c>
       <c r="C59" s="26"/>
@@ -13719,7 +13703,7 @@
       <c r="G59" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H59" s="36" t="s">
+      <c r="H59" s="34" t="s">
         <v>117</v>
       </c>
       <c r="I59" s="4">
@@ -13897,16 +13881,16 @@
       <c r="BY59" s="4"/>
       <c r="BZ59" s="4"/>
     </row>
-    <row r="60" spans="1:78" ht="42">
-      <c r="A60" s="37" t="s">
-        <v>445</v>
+    <row r="60" spans="1:78" ht="42.75">
+      <c r="A60" s="35" t="s">
+        <v>443</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="12">
@@ -14091,11 +14075,11 @@
       <c r="BY60" s="4"/>
       <c r="BZ60" s="4"/>
     </row>
-    <row r="61" spans="1:78" ht="70">
-      <c r="A61" s="38" t="s">
+    <row r="61" spans="1:78" ht="71.25">
+      <c r="A61" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="B61" s="39" t="s">
+      <c r="B61" s="37" t="s">
         <v>206</v>
       </c>
       <c r="C61" s="4"/>
@@ -14285,11 +14269,11 @@
       <c r="BY61" s="4"/>
       <c r="BZ61" s="4"/>
     </row>
-    <row r="62" spans="1:78" ht="56">
-      <c r="A62" s="38" t="s">
+    <row r="62" spans="1:78" ht="57">
+      <c r="A62" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="B62" s="39" t="s">
+      <c r="B62" s="37" t="s">
         <v>208</v>
       </c>
       <c r="C62" s="4"/>
@@ -14481,11 +14465,11 @@
       <c r="BY62" s="4"/>
       <c r="BZ62" s="4"/>
     </row>
-    <row r="63" spans="1:78">
+    <row r="63" spans="1:78" ht="28.5">
       <c r="A63" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="B63" s="39" t="s">
+      <c r="B63" s="37" t="s">
         <v>210</v>
       </c>
       <c r="C63" s="4"/>
@@ -14499,7 +14483,7 @@
       <c r="G63" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H63" s="39" t="s">
+      <c r="H63" s="37" t="s">
         <v>212</v>
       </c>
       <c r="I63" s="4">
@@ -14675,14 +14659,14 @@
       <c r="BY63" s="4"/>
       <c r="BZ63" s="4"/>
     </row>
-    <row r="64" spans="1:78" ht="140">
-      <c r="A64" s="40" t="s">
+    <row r="64" spans="1:78" ht="142.5">
+      <c r="A64" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="B64" s="39" t="s">
+      <c r="B64" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C64" s="39" t="s">
+      <c r="C64" s="37" t="s">
         <v>214</v>
       </c>
       <c r="D64" s="13" t="s">
@@ -14874,11 +14858,11 @@
       <c r="BZ64" s="4"/>
     </row>
     <row r="65" spans="1:78">
-      <c r="A65" s="40"/>
-      <c r="B65" s="39" t="s">
+      <c r="A65" s="38"/>
+      <c r="B65" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C65" s="39" t="s">
+      <c r="C65" s="37" t="s">
         <v>220</v>
       </c>
       <c r="D65" s="13" t="s">
@@ -15070,11 +15054,11 @@
       <c r="BZ65" s="4"/>
     </row>
     <row r="66" spans="1:78">
-      <c r="A66" s="40"/>
-      <c r="B66" s="39" t="s">
+      <c r="A66" s="38"/>
+      <c r="B66" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C66" s="39" t="s">
+      <c r="C66" s="37" t="s">
         <v>222</v>
       </c>
       <c r="D66" s="13" t="s">
@@ -15266,14 +15250,14 @@
       <c r="BZ66" s="4"/>
     </row>
     <row r="67" spans="1:78">
-      <c r="A67" s="41"/>
+      <c r="A67" s="39"/>
       <c r="B67" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="C67" s="39" t="s">
+      <c r="C67" s="37" t="s">
         <v>222</v>
       </c>
-      <c r="D67" s="39" t="s">
+      <c r="D67" s="37" t="s">
         <v>225</v>
       </c>
       <c r="E67" s="4" t="s">
@@ -15462,14 +15446,14 @@
       <c r="BZ67" s="4"/>
     </row>
     <row r="68" spans="1:78">
-      <c r="A68" s="41"/>
+      <c r="A68" s="39"/>
       <c r="B68" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="C68" s="39" t="s">
+      <c r="C68" s="37" t="s">
         <v>227</v>
       </c>
-      <c r="D68" s="42" t="s">
+      <c r="D68" s="40" t="s">
         <v>228</v>
       </c>
       <c r="E68" s="4" t="s">
@@ -15658,14 +15642,14 @@
       <c r="BZ68" s="4"/>
     </row>
     <row r="69" spans="1:78">
-      <c r="A69" s="41"/>
+      <c r="A69" s="39"/>
       <c r="B69" s="30" t="s">
         <v>213</v>
       </c>
-      <c r="C69" s="39" t="s">
+      <c r="C69" s="37" t="s">
         <v>227</v>
       </c>
-      <c r="D69" s="39" t="s">
+      <c r="D69" s="37" t="s">
         <v>230</v>
       </c>
       <c r="E69" s="4" t="s">
@@ -15853,17 +15837,17 @@
       <c r="BY69" s="4"/>
       <c r="BZ69" s="4"/>
     </row>
-    <row r="70" spans="1:78" ht="70">
+    <row r="70" spans="1:78" ht="85.5">
       <c r="A70" s="30" t="s">
         <v>232</v>
       </c>
       <c r="B70" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="C70" s="39" t="s">
+      <c r="C70" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="D70" s="39" t="s">
+      <c r="D70" s="37" t="s">
         <v>233</v>
       </c>
       <c r="E70" s="4" t="s">
@@ -16054,7 +16038,7 @@
       <c r="BZ70" s="4"/>
     </row>
     <row r="71" spans="1:78">
-      <c r="A71" s="41"/>
+      <c r="A71" s="39"/>
       <c r="B71" s="30" t="s">
         <v>232</v>
       </c>
@@ -16067,7 +16051,7 @@
       <c r="E71" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F71" s="43">
+      <c r="F71" s="41">
         <v>6</v>
       </c>
       <c r="G71" s="4" t="s">
@@ -16250,7 +16234,7 @@
       <c r="BZ71" s="4"/>
     </row>
     <row r="72" spans="1:78">
-      <c r="A72" s="41"/>
+      <c r="A72" s="39"/>
       <c r="B72" s="30" t="s">
         <v>232</v>
       </c>
@@ -16263,7 +16247,7 @@
       <c r="E72" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F72" s="43">
+      <c r="F72" s="41">
         <v>7</v>
       </c>
       <c r="G72" s="4" t="s">
@@ -16446,7 +16430,7 @@
       <c r="BZ72" s="4"/>
     </row>
     <row r="73" spans="1:78">
-      <c r="A73" s="41"/>
+      <c r="A73" s="39"/>
       <c r="B73" s="30" t="s">
         <v>232</v>
       </c>
@@ -16459,7 +16443,7 @@
       <c r="E73" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F73" s="43">
+      <c r="F73" s="41">
         <v>8</v>
       </c>
       <c r="G73" s="4" t="s">
@@ -16641,8 +16625,8 @@
       <c r="BY73" s="4"/>
       <c r="BZ73" s="4"/>
     </row>
-    <row r="74" spans="1:78" ht="70">
-      <c r="A74" s="41" t="s">
+    <row r="74" spans="1:78" ht="71.25">
+      <c r="A74" s="39" t="s">
         <v>218</v>
       </c>
       <c r="B74" s="30" t="s">
@@ -16837,12 +16821,12 @@
       <c r="BY74" s="4"/>
       <c r="BZ74" s="4"/>
     </row>
-    <row r="75" spans="1:78" ht="28">
+    <row r="75" spans="1:78" ht="42.75">
       <c r="A75" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="B75" s="37" t="s">
-        <v>447</v>
+        <v>445</v>
+      </c>
+      <c r="B75" s="35" t="s">
+        <v>445</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="4" t="s">
@@ -17031,7 +17015,7 @@
       <c r="BY75" s="4"/>
       <c r="BZ75" s="4"/>
     </row>
-    <row r="76" spans="1:78" ht="42">
+    <row r="76" spans="1:78" ht="57">
       <c r="A76" s="22" t="s">
         <v>242</v>
       </c>
@@ -17049,7 +17033,7 @@
       <c r="G76" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H76" s="44" t="s">
+      <c r="H76" s="42" t="s">
         <v>241</v>
       </c>
       <c r="I76" s="4">
@@ -17225,7 +17209,7 @@
       <c r="BY76" s="4"/>
       <c r="BZ76" s="4"/>
     </row>
-    <row r="77" spans="1:78" ht="28">
+    <row r="77" spans="1:78" ht="28.5">
       <c r="A77" s="22" t="s">
         <v>244</v>
       </c>
@@ -17243,7 +17227,7 @@
       <c r="G77" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H77" s="44" t="s">
+      <c r="H77" s="42" t="s">
         <v>241</v>
       </c>
       <c r="I77" s="4">
@@ -17419,7 +17403,7 @@
       <c r="BY77" s="4"/>
       <c r="BZ77" s="4"/>
     </row>
-    <row r="78" spans="1:78" ht="28">
+    <row r="78" spans="1:78" ht="28.5">
       <c r="A78" s="22" t="s">
         <v>246</v>
       </c>
@@ -17437,7 +17421,7 @@
       <c r="G78" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H78" s="44" t="s">
+      <c r="H78" s="42" t="s">
         <v>241</v>
       </c>
       <c r="I78" s="4">
@@ -17613,7 +17597,7 @@
       <c r="BY78" s="4"/>
       <c r="BZ78" s="4"/>
     </row>
-    <row r="79" spans="1:78" ht="42">
+    <row r="79" spans="1:78" ht="42.75">
       <c r="A79" s="22" t="s">
         <v>248</v>
       </c>
@@ -17631,7 +17615,7 @@
       <c r="G79" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H79" s="44" t="s">
+      <c r="H79" s="42" t="s">
         <v>241</v>
       </c>
       <c r="I79" s="4">
@@ -17807,7 +17791,7 @@
       <c r="BY79" s="4"/>
       <c r="BZ79" s="4"/>
     </row>
-    <row r="80" spans="1:78" ht="42">
+    <row r="80" spans="1:78" ht="42.75">
       <c r="A80" s="22" t="s">
         <v>250</v>
       </c>
@@ -17825,7 +17809,7 @@
       <c r="G80" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H80" s="44" t="s">
+      <c r="H80" s="42" t="s">
         <v>241</v>
       </c>
       <c r="I80" s="4">
@@ -18195,12 +18179,12 @@
       <c r="BY81" s="4"/>
       <c r="BZ81" s="4"/>
     </row>
-    <row r="82" spans="1:78" ht="42">
+    <row r="82" spans="1:78" ht="42.75">
       <c r="A82" s="9" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="4" t="s">
@@ -18389,16 +18373,16 @@
       <c r="BY82" s="4"/>
       <c r="BZ82" s="4"/>
     </row>
-    <row r="83" spans="1:78" ht="28">
+    <row r="83" spans="1:78" ht="28.5">
       <c r="A83" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="9" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4">
@@ -18583,16 +18567,16 @@
       <c r="BY83" s="4"/>
       <c r="BZ83" s="4"/>
     </row>
-    <row r="84" spans="1:78" ht="70">
+    <row r="84" spans="1:78" ht="71.25">
       <c r="A84" s="9" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="9" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E84" s="4"/>
       <c r="F84" s="4">
@@ -18777,16 +18761,16 @@
       <c r="BY84" s="4"/>
       <c r="BZ84" s="4"/>
     </row>
-    <row r="85" spans="1:78" ht="42">
+    <row r="85" spans="1:78" ht="42.75">
       <c r="A85" s="9" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4">
@@ -18971,12 +18955,12 @@
       <c r="BY85" s="4"/>
       <c r="BZ85" s="4"/>
     </row>
-    <row r="86" spans="1:78" ht="42">
+    <row r="86" spans="1:78" ht="42.75">
       <c r="A86" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C86" s="9"/>
       <c r="D86" s="4" t="s">
@@ -19165,16 +19149,16 @@
       <c r="BY86" s="4"/>
       <c r="BZ86" s="4"/>
     </row>
-    <row r="87" spans="1:78" ht="70">
+    <row r="87" spans="1:78" ht="71.25">
       <c r="A87" s="9" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="9" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="4">
@@ -19361,12 +19345,12 @@
       <c r="BY87" s="4"/>
       <c r="BZ87" s="4"/>
     </row>
-    <row r="88" spans="1:78" ht="42">
+    <row r="88" spans="1:78" ht="42.75">
       <c r="A88" s="9" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="4" t="s">
@@ -19555,7 +19539,7 @@
       <c r="BY88" s="4"/>
       <c r="BZ88" s="4"/>
     </row>
-    <row r="89" spans="1:78" ht="42">
+    <row r="89" spans="1:78" ht="42.75">
       <c r="A89" s="22" t="s">
         <v>259</v>
       </c>
@@ -19749,11 +19733,11 @@
       <c r="BY89" s="4"/>
       <c r="BZ89" s="4"/>
     </row>
-    <row r="90" spans="1:78" ht="28">
-      <c r="A90" s="39" t="s">
+    <row r="90" spans="1:78" ht="28.5">
+      <c r="A90" s="37" t="s">
         <v>261</v>
       </c>
-      <c r="B90" s="39" t="s">
+      <c r="B90" s="37" t="s">
         <v>261</v>
       </c>
       <c r="C90" s="26"/>
@@ -19767,7 +19751,7 @@
       <c r="G90" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H90" s="36" t="s">
+      <c r="H90" s="34" t="s">
         <v>254</v>
       </c>
       <c r="I90" s="4">
@@ -19944,10 +19928,10 @@
       <c r="BZ90" s="4"/>
     </row>
     <row r="91" spans="1:78">
-      <c r="A91" s="39" t="s">
+      <c r="A91" s="37" t="s">
         <v>263</v>
       </c>
-      <c r="B91" s="39" t="s">
+      <c r="B91" s="37" t="s">
         <v>263</v>
       </c>
       <c r="C91" s="26"/>
@@ -19961,7 +19945,7 @@
       <c r="G91" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H91" s="36" t="s">
+      <c r="H91" s="34" t="s">
         <v>254</v>
       </c>
       <c r="I91" s="4">
@@ -20137,8 +20121,8 @@
       <c r="BY91" s="4"/>
       <c r="BZ91" s="4"/>
     </row>
-    <row r="92" spans="1:78" ht="28">
-      <c r="A92" s="39" t="s">
+    <row r="92" spans="1:78" ht="28.5">
+      <c r="A92" s="37" t="s">
         <v>265</v>
       </c>
       <c r="B92" s="30" t="s">
@@ -20149,13 +20133,13 @@
         <v>266</v>
       </c>
       <c r="E92" s="4"/>
-      <c r="F92" s="39">
+      <c r="F92" s="37">
         <v>11</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H92" s="36" t="s">
+      <c r="H92" s="34" t="s">
         <v>254</v>
       </c>
       <c r="I92" s="4">
@@ -20331,11 +20315,11 @@
       <c r="BY92" s="4"/>
       <c r="BZ92" s="4"/>
     </row>
-    <row r="93" spans="1:78" ht="56">
-      <c r="A93" s="39" t="s">
+    <row r="93" spans="1:78" ht="57">
+      <c r="A93" s="37" t="s">
         <v>267</v>
       </c>
-      <c r="B93" s="45" t="s">
+      <c r="B93" s="43" t="s">
         <v>267</v>
       </c>
       <c r="C93" s="26"/>
@@ -20525,11 +20509,11 @@
       <c r="BY93" s="4"/>
       <c r="BZ93" s="4"/>
     </row>
-    <row r="94" spans="1:78" ht="28">
-      <c r="A94" s="39" t="s">
+    <row r="94" spans="1:78" ht="28.5">
+      <c r="A94" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="B94" s="45" t="s">
+      <c r="B94" s="43" t="s">
         <v>269</v>
       </c>
       <c r="C94" s="26"/>
@@ -20719,11 +20703,11 @@
       <c r="BY94" s="4"/>
       <c r="BZ94" s="4"/>
     </row>
-    <row r="95" spans="1:78" ht="34" customHeight="1">
-      <c r="A95" s="39" t="s">
+    <row r="95" spans="1:78" ht="33.950000000000003" customHeight="1">
+      <c r="A95" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="B95" s="45" t="s">
+      <c r="B95" s="43" t="s">
         <v>271</v>
       </c>
       <c r="C95" s="26"/>
@@ -20911,18 +20895,18 @@
       <c r="BY95" s="4"/>
       <c r="BZ95" s="4"/>
     </row>
-    <row r="96" spans="1:78" ht="98">
+    <row r="96" spans="1:78" ht="99.75">
       <c r="A96" s="9" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>272</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="12">
@@ -21107,18 +21091,18 @@
       <c r="BY96" s="4"/>
       <c r="BZ96" s="4"/>
     </row>
-    <row r="97" spans="1:78" ht="98">
+    <row r="97" spans="1:78" ht="99.75">
       <c r="A97" s="9" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>129</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="12">
@@ -21303,18 +21287,18 @@
       <c r="BY97" s="4"/>
       <c r="BZ97" s="4"/>
     </row>
-    <row r="98" spans="1:78" ht="56">
+    <row r="98" spans="1:78" ht="57">
       <c r="A98" s="9" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>272</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="12">
@@ -21499,18 +21483,18 @@
       <c r="BY98" s="4"/>
       <c r="BZ98" s="4"/>
     </row>
-    <row r="99" spans="1:78" ht="56">
+    <row r="99" spans="1:78" ht="57">
       <c r="A99" s="9" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>129</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="12">
@@ -21695,18 +21679,18 @@
       <c r="BY99" s="4"/>
       <c r="BZ99" s="4"/>
     </row>
-    <row r="100" spans="1:78" ht="42">
+    <row r="100" spans="1:78" ht="57">
       <c r="A100" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>272</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="12">
@@ -21891,18 +21875,18 @@
       <c r="BY100" s="4"/>
       <c r="BZ100" s="4"/>
     </row>
-    <row r="101" spans="1:78" ht="42">
+    <row r="101" spans="1:78" ht="57">
       <c r="A101" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="12">
@@ -22087,12 +22071,12 @@
       <c r="BY101" s="4"/>
       <c r="BZ101" s="4"/>
     </row>
-    <row r="102" spans="1:78" ht="28">
+    <row r="102" spans="1:78" ht="28.5">
       <c r="A102" s="9" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>274</v>
@@ -22284,7 +22268,7 @@
       <c r="BR102" s="4">
         <v>10</v>
       </c>
-      <c r="BS102" s="46" t="s">
+      <c r="BS102" s="44" t="s">
         <v>279</v>
       </c>
       <c r="BT102" s="4" t="s">
@@ -22297,12 +22281,12 @@
       <c r="BY102" s="4"/>
       <c r="BZ102" s="4"/>
     </row>
-    <row r="103" spans="1:78" ht="42">
+    <row r="103" spans="1:78" ht="57">
       <c r="A103" s="9" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="4" t="s">
@@ -22492,7 +22476,7 @@
       <c r="BR103" s="4">
         <v>5</v>
       </c>
-      <c r="BS103" s="46" t="s">
+      <c r="BS103" s="44" t="s">
         <v>279</v>
       </c>
       <c r="BT103" s="4" t="s">
@@ -22505,12 +22489,12 @@
       <c r="BY103" s="4"/>
       <c r="BZ103" s="4"/>
     </row>
-    <row r="104" spans="1:78" ht="56">
+    <row r="104" spans="1:78" ht="57">
       <c r="A104" s="9" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C104" s="9"/>
       <c r="D104" s="4" t="s">
@@ -22709,7 +22693,7 @@
       <c r="BY104" s="4"/>
       <c r="BZ104" s="4"/>
     </row>
-    <row r="105" spans="1:78" ht="42">
+    <row r="105" spans="1:78" ht="42.75">
       <c r="A105" s="13" t="s">
         <v>283</v>
       </c>
@@ -22913,7 +22897,7 @@
       <c r="BY105" s="4"/>
       <c r="BZ105" s="4"/>
     </row>
-    <row r="106" spans="1:78" ht="42">
+    <row r="106" spans="1:78" ht="42.75">
       <c r="A106" s="13" t="s">
         <v>285</v>
       </c>
@@ -23108,7 +23092,7 @@
       <c r="BR106" s="4">
         <v>10</v>
       </c>
-      <c r="BS106" s="46" t="s">
+      <c r="BS106" s="44" t="s">
         <v>279</v>
       </c>
       <c r="BT106" s="4" t="s">
@@ -23121,8 +23105,8 @@
       <c r="BY106" s="4"/>
       <c r="BZ106" s="4"/>
     </row>
-    <row r="107" spans="1:78" ht="42">
-      <c r="A107" s="39" t="s">
+    <row r="107" spans="1:78" ht="42.75">
+      <c r="A107" s="37" t="s">
         <v>287</v>
       </c>
       <c r="B107" s="4" t="s">
@@ -23316,7 +23300,7 @@
       <c r="BR107" s="4">
         <v>5</v>
       </c>
-      <c r="BS107" s="46" t="s">
+      <c r="BS107" s="44" t="s">
         <v>279</v>
       </c>
       <c r="BT107" s="4" t="s">
@@ -23329,8 +23313,8 @@
       <c r="BY107" s="4"/>
       <c r="BZ107" s="4"/>
     </row>
-    <row r="108" spans="1:78" ht="56">
-      <c r="A108" s="39" t="s">
+    <row r="108" spans="1:78" ht="57">
+      <c r="A108" s="37" t="s">
         <v>289</v>
       </c>
       <c r="B108" s="4" t="s">
@@ -23533,8 +23517,8 @@
       <c r="BY108" s="4"/>
       <c r="BZ108" s="4"/>
     </row>
-    <row r="109" spans="1:78" ht="28">
-      <c r="A109" s="39" t="s">
+    <row r="109" spans="1:78" ht="28.5">
+      <c r="A109" s="37" t="s">
         <v>291</v>
       </c>
       <c r="B109" s="4" t="s">
@@ -23727,8 +23711,8 @@
       <c r="BY109" s="4"/>
       <c r="BZ109" s="4"/>
     </row>
-    <row r="110" spans="1:78" ht="98">
-      <c r="A110" s="39" t="s">
+    <row r="110" spans="1:78" ht="99.75">
+      <c r="A110" s="37" t="s">
         <v>293</v>
       </c>
       <c r="B110" s="4" t="s">
@@ -23736,7 +23720,7 @@
       </c>
       <c r="C110" s="9"/>
       <c r="D110" s="4" t="s">
-        <v>294</v>
+        <v>485</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="4">
@@ -23921,16 +23905,16 @@
       <c r="BY110" s="4"/>
       <c r="BZ110" s="4"/>
     </row>
-    <row r="111" spans="1:78" ht="70">
-      <c r="A111" s="39" t="s">
-        <v>295</v>
+    <row r="111" spans="1:78" ht="71.25">
+      <c r="A111" s="37" t="s">
+        <v>294</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E111" s="4"/>
       <c r="F111" s="4">
@@ -24116,15 +24100,15 @@
       <c r="BZ111" s="4"/>
     </row>
     <row r="112" spans="1:78">
-      <c r="A112" s="39" t="s">
-        <v>297</v>
-      </c>
-      <c r="B112" s="39" t="s">
-        <v>297</v>
+      <c r="A112" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="B112" s="37" t="s">
+        <v>296</v>
       </c>
       <c r="C112" s="9"/>
       <c r="D112" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="4">
@@ -24134,7 +24118,7 @@
         <v>62</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I112" s="4">
         <v>1</v>
@@ -24286,7 +24270,7 @@
       <c r="BJ112" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="BK112" s="47" t="s">
+      <c r="BK112" s="45" t="s">
         <v>62</v>
       </c>
       <c r="BL112" s="4"/>
@@ -24319,16 +24303,16 @@
       <c r="BY112" s="4"/>
       <c r="BZ112" s="4"/>
     </row>
-    <row r="113" spans="1:78" ht="28">
+    <row r="113" spans="1:78" ht="28.5">
       <c r="A113" s="30" t="s">
-        <v>300</v>
-      </c>
-      <c r="B113" s="39" t="s">
-        <v>300</v>
+        <v>299</v>
+      </c>
+      <c r="B113" s="37" t="s">
+        <v>299</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E113" s="4"/>
       <c r="F113" s="4">
@@ -24338,7 +24322,7 @@
         <v>62</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I113" s="4">
         <v>1</v>
@@ -24523,16 +24507,16 @@
       <c r="BY113" s="4"/>
       <c r="BZ113" s="4"/>
     </row>
-    <row r="114" spans="1:78" ht="70">
+    <row r="114" spans="1:78" ht="57">
       <c r="A114" s="9" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C114" s="9"/>
       <c r="D114" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E114" s="4"/>
       <c r="F114" s="12">
@@ -24542,7 +24526,7 @@
         <v>62</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I114" s="4">
         <v>1</v>
@@ -24585,7 +24569,7 @@
         <v>60</v>
       </c>
       <c r="W114" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="X114" s="11" t="s">
         <v>62</v>
@@ -24719,16 +24703,16 @@
       <c r="BY114" s="4"/>
       <c r="BZ114" s="4"/>
     </row>
-    <row r="115" spans="1:78" ht="28">
+    <row r="115" spans="1:78" ht="28.5">
       <c r="A115" s="9" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E115" s="4"/>
       <c r="F115" s="12">
@@ -24738,7 +24722,7 @@
         <v>62</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I115" s="4">
         <v>1</v>
@@ -24781,7 +24765,7 @@
         <v>60</v>
       </c>
       <c r="W115" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="X115" s="11" t="s">
         <v>62</v>
@@ -24915,16 +24899,16 @@
       <c r="BY115" s="4"/>
       <c r="BZ115" s="4"/>
     </row>
-    <row r="116" spans="1:78" ht="28">
+    <row r="116" spans="1:78" ht="42.75">
       <c r="A116" s="9" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C116" s="9"/>
       <c r="D116" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="12">
@@ -24934,7 +24918,7 @@
         <v>62</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I116" s="4">
         <v>1</v>
@@ -24977,7 +24961,7 @@
         <v>60</v>
       </c>
       <c r="W116" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="X116" s="11" t="s">
         <v>62</v>
@@ -25111,16 +25095,16 @@
       <c r="BY116" s="4"/>
       <c r="BZ116" s="4"/>
     </row>
-    <row r="117" spans="1:78" ht="98">
+    <row r="117" spans="1:78" ht="57">
       <c r="A117" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="12">
@@ -25130,7 +25114,7 @@
         <v>62</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I117" s="4">
         <v>1</v>
@@ -25173,7 +25157,7 @@
         <v>60</v>
       </c>
       <c r="W117" s="11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="X117" s="11" t="s">
         <v>62</v>
@@ -25307,16 +25291,16 @@
       <c r="BY117" s="4"/>
       <c r="BZ117" s="4"/>
     </row>
-    <row r="118" spans="1:78" ht="56">
-      <c r="A118" s="48" t="s">
-        <v>310</v>
+    <row r="118" spans="1:78" ht="42.75">
+      <c r="A118" s="46" t="s">
+        <v>309</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C118" s="4"/>
       <c r="D118" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="12">
@@ -25325,62 +25309,62 @@
       <c r="G118" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H118" s="49" t="s">
-        <v>303</v>
+      <c r="H118" s="47" t="s">
+        <v>302</v>
       </c>
       <c r="I118" s="4">
         <v>1</v>
       </c>
-      <c r="J118" s="47" t="s">
+      <c r="J118" s="45" t="s">
         <v>60</v>
       </c>
       <c r="K118" s="4">
         <v>1.5</v>
       </c>
-      <c r="L118" s="47"/>
+      <c r="L118" s="45"/>
       <c r="M118" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="N118" s="47" t="s">
+      <c r="N118" s="45" t="s">
         <v>62</v>
       </c>
       <c r="O118" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="P118" s="47" t="s">
+      <c r="P118" s="45" t="s">
         <v>60</v>
       </c>
       <c r="Q118" s="4">
         <v>250</v>
       </c>
-      <c r="R118" s="47" t="s">
+      <c r="R118" s="45" t="s">
         <v>62</v>
       </c>
       <c r="S118" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="T118" s="47" t="s">
+      <c r="T118" s="45" t="s">
         <v>62</v>
       </c>
       <c r="U118" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="V118" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="W118" s="47" t="s">
-        <v>312</v>
-      </c>
-      <c r="X118" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y118" s="47"/>
-      <c r="Z118" s="47" t="s">
+      <c r="V118" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="W118" s="45" t="s">
+        <v>311</v>
+      </c>
+      <c r="X118" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y118" s="45"/>
+      <c r="Z118" s="45" t="s">
         <v>62</v>
       </c>
       <c r="AA118" s="4"/>
       <c r="AB118" s="4"/>
-      <c r="AC118" s="47" t="s">
+      <c r="AC118" s="45" t="s">
         <v>60</v>
       </c>
       <c r="AD118" s="4">
@@ -25390,7 +25374,7 @@
         <v>62</v>
       </c>
       <c r="AF118" s="4"/>
-      <c r="AG118" s="47" t="s">
+      <c r="AG118" s="45" t="s">
         <v>62</v>
       </c>
       <c r="AH118" s="4" t="s">
@@ -25420,7 +25404,7 @@
       <c r="AP118" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AQ118" s="47" t="s">
+      <c r="AQ118" s="45" t="s">
         <v>62</v>
       </c>
       <c r="AR118" s="4" t="s">
@@ -25503,16 +25487,16 @@
       <c r="BY118" s="4"/>
       <c r="BZ118" s="4"/>
     </row>
-    <row r="119" spans="1:78" ht="42">
-      <c r="A119" s="39" t="s">
-        <v>313</v>
+    <row r="119" spans="1:78" ht="42.75">
+      <c r="A119" s="37" t="s">
+        <v>312</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C119" s="4"/>
       <c r="D119" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E119" s="4"/>
       <c r="F119" s="18">
@@ -25521,8 +25505,8 @@
       <c r="G119" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H119" s="50" t="s">
-        <v>303</v>
+      <c r="H119" s="48" t="s">
+        <v>302</v>
       </c>
       <c r="I119" s="4">
         <v>1</v>
@@ -25565,7 +25549,7 @@
         <v>60</v>
       </c>
       <c r="W119" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="X119" s="17" t="s">
         <v>62</v>
@@ -25703,16 +25687,16 @@
       <c r="BY119" s="4"/>
       <c r="BZ119" s="4"/>
     </row>
-    <row r="120" spans="1:78" ht="42">
-      <c r="A120" s="39" t="s">
-        <v>315</v>
+    <row r="120" spans="1:78" ht="42.75">
+      <c r="A120" s="37" t="s">
+        <v>314</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C120" s="4"/>
       <c r="D120" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="18">
@@ -25721,8 +25705,8 @@
       <c r="G120" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H120" s="50" t="s">
-        <v>303</v>
+      <c r="H120" s="48" t="s">
+        <v>302</v>
       </c>
       <c r="I120" s="4">
         <v>1</v>
@@ -25765,7 +25749,7 @@
         <v>60</v>
       </c>
       <c r="W120" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="X120" s="17" t="s">
         <v>62</v>
@@ -25903,19 +25887,19 @@
       <c r="BY120" s="4"/>
       <c r="BZ120" s="4"/>
     </row>
-    <row r="121" spans="1:78" ht="42">
+    <row r="121" spans="1:78" ht="42.75">
       <c r="A121" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C121" s="6"/>
       <c r="D121" s="9" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F121" s="4">
         <v>0</v>
@@ -25924,7 +25908,7 @@
         <v>62</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I121" s="9">
         <v>1</v>
@@ -26061,7 +26045,7 @@
         <v>60</v>
       </c>
       <c r="BE121" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="BF121" s="11" t="s">
         <v>62</v>
@@ -26101,17 +26085,17 @@
       <c r="BY121" s="4"/>
       <c r="BZ121" s="4"/>
     </row>
-    <row r="122" spans="1:78" ht="42">
+    <row r="122" spans="1:78" ht="42.75">
       <c r="A122" s="6"/>
       <c r="B122" s="9" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="9" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F122" s="4">
         <v>1</v>
@@ -26120,7 +26104,7 @@
         <v>62</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I122" s="4">
         <v>1</v>
@@ -26163,7 +26147,7 @@
         <v>62</v>
       </c>
       <c r="W122" s="4"/>
-      <c r="X122" s="47" t="s">
+      <c r="X122" s="45" t="s">
         <v>62</v>
       </c>
       <c r="Y122" s="4"/>
@@ -26257,7 +26241,7 @@
         <v>60</v>
       </c>
       <c r="BE122" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="BF122" s="11" t="s">
         <v>62</v>
@@ -26297,16 +26281,16 @@
       <c r="BY122" s="4"/>
       <c r="BZ122" s="4"/>
     </row>
-    <row r="123" spans="1:78" ht="70">
+    <row r="123" spans="1:78" ht="71.25">
       <c r="A123" s="9" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="9" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="4">
@@ -26316,7 +26300,7 @@
         <v>62</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I123" s="9">
         <v>1</v>
@@ -26451,7 +26435,7 @@
         <v>60</v>
       </c>
       <c r="BE123" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BF123" s="11" t="s">
         <v>62</v>
@@ -26491,19 +26475,19 @@
       <c r="BY123" s="4"/>
       <c r="BZ123" s="4"/>
     </row>
-    <row r="124" spans="1:78" ht="84">
+    <row r="124" spans="1:78" ht="99.75">
       <c r="A124" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B124" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="E124" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>326</v>
       </c>
       <c r="F124" s="23">
         <v>3</v>
@@ -26512,7 +26496,7 @@
         <v>62</v>
       </c>
       <c r="H124" s="24" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I124" s="4">
         <v>1</v>
@@ -26649,7 +26633,7 @@
         <v>60</v>
       </c>
       <c r="BE124" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="BF124" s="11" t="s">
         <v>62</v>
@@ -26689,17 +26673,17 @@
       <c r="BY124" s="4"/>
       <c r="BZ124" s="4"/>
     </row>
-    <row r="125" spans="1:78" ht="28">
+    <row r="125" spans="1:78" ht="28.5">
       <c r="A125" s="22"/>
       <c r="B125" s="22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D125" s="6"/>
       <c r="E125" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F125" s="23">
         <v>4</v>
@@ -26787,7 +26771,7 @@
         <v>60</v>
       </c>
       <c r="BE125" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="BF125" s="11" t="s">
         <v>62</v>
@@ -26827,19 +26811,19 @@
       <c r="BY125" s="4"/>
       <c r="BZ125" s="4"/>
     </row>
-    <row r="126" spans="1:78" ht="56">
-      <c r="A126" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="B126" s="39" t="s">
-        <v>330</v>
+    <row r="126" spans="1:78" ht="57">
+      <c r="A126" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="B126" s="37" t="s">
+        <v>329</v>
       </c>
       <c r="C126" s="26"/>
       <c r="D126" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E126" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>332</v>
       </c>
       <c r="F126" s="23">
         <v>5</v>
@@ -26847,8 +26831,8 @@
       <c r="G126" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H126" s="36" t="s">
-        <v>319</v>
+      <c r="H126" s="34" t="s">
+        <v>318</v>
       </c>
       <c r="I126" s="4">
         <v>1</v>
@@ -26987,7 +26971,7 @@
         <v>60</v>
       </c>
       <c r="BE126" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="BF126" s="11" t="s">
         <v>62</v>
@@ -27028,23 +27012,23 @@
       <c r="BZ126" s="4"/>
     </row>
     <row r="127" spans="1:78">
-      <c r="A127" s="39"/>
-      <c r="B127" s="39" t="s">
-        <v>330</v>
+      <c r="A127" s="37"/>
+      <c r="B127" s="37" t="s">
+        <v>329</v>
       </c>
       <c r="C127" s="26" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D127" s="6"/>
       <c r="E127" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F127" s="23">
         <v>6</v>
       </c>
       <c r="G127" s="4"/>
-      <c r="H127" s="36" t="s">
-        <v>319</v>
+      <c r="H127" s="34" t="s">
+        <v>318</v>
       </c>
       <c r="I127" s="4"/>
       <c r="J127" s="15"/>
@@ -27137,16 +27121,16 @@
       <c r="BY127" s="4"/>
       <c r="BZ127" s="4"/>
     </row>
-    <row r="128" spans="1:78" ht="70">
+    <row r="128" spans="1:78" ht="71.25">
       <c r="A128" s="22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B128" s="22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="23">
@@ -27156,7 +27140,7 @@
         <v>62</v>
       </c>
       <c r="H128" s="24" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I128" s="4">
         <v>1</v>
@@ -27295,7 +27279,7 @@
         <v>60</v>
       </c>
       <c r="BE128" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="BF128" s="11" t="s">
         <v>62</v>
@@ -27335,19 +27319,19 @@
       <c r="BY128" s="4"/>
       <c r="BZ128" s="4"/>
     </row>
-    <row r="129" spans="1:78" ht="42">
-      <c r="A129" s="39" t="s">
-        <v>338</v>
-      </c>
-      <c r="B129" s="39" t="s">
-        <v>338</v>
+    <row r="129" spans="1:78" ht="42.75">
+      <c r="A129" s="37" t="s">
+        <v>337</v>
+      </c>
+      <c r="B129" s="37" t="s">
+        <v>337</v>
       </c>
       <c r="C129" s="6"/>
       <c r="D129" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F129" s="27">
         <v>8</v>
@@ -27356,7 +27340,7 @@
         <v>62</v>
       </c>
       <c r="H129" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I129" s="4">
         <v>1</v>
@@ -27491,7 +27475,7 @@
         <v>60</v>
       </c>
       <c r="BE129" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="BF129" s="11" t="s">
         <v>62</v>
@@ -27531,17 +27515,17 @@
       <c r="BY129" s="4"/>
       <c r="BZ129" s="4"/>
     </row>
-    <row r="130" spans="1:78" ht="42">
-      <c r="A130" s="39"/>
-      <c r="B130" s="39" t="s">
-        <v>338</v>
+    <row r="130" spans="1:78" ht="42.75">
+      <c r="A130" s="37"/>
+      <c r="B130" s="37" t="s">
+        <v>337</v>
       </c>
       <c r="C130" s="4"/>
       <c r="D130" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F130" s="27">
         <v>9</v>
@@ -27550,7 +27534,7 @@
         <v>62</v>
       </c>
       <c r="H130" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I130" s="4">
         <v>1</v>
@@ -27685,7 +27669,7 @@
         <v>60</v>
       </c>
       <c r="BE130" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="BF130" s="11" t="s">
         <v>62</v>
@@ -27725,18 +27709,18 @@
       <c r="BY130" s="4"/>
       <c r="BZ130" s="4"/>
     </row>
-    <row r="131" spans="1:78" ht="56">
-      <c r="A131" s="39" t="s">
+    <row r="131" spans="1:78" ht="57">
+      <c r="A131" s="37" t="s">
+        <v>341</v>
+      </c>
+      <c r="B131" s="37" t="s">
         <v>342</v>
       </c>
-      <c r="B131" s="39" t="s">
+      <c r="C131" s="49" t="s">
         <v>343</v>
       </c>
-      <c r="C131" s="51" t="s">
+      <c r="D131" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="E131" s="4"/>
       <c r="F131" s="27">
@@ -27746,7 +27730,7 @@
         <v>62</v>
       </c>
       <c r="H131" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I131" s="4">
         <v>1</v>
@@ -27923,18 +27907,18 @@
       <c r="BY131" s="4"/>
       <c r="BZ131" s="4"/>
     </row>
-    <row r="132" spans="1:78" ht="28">
-      <c r="A132" s="39" t="s">
+    <row r="132" spans="1:78" ht="42.75">
+      <c r="A132" s="37" t="s">
+        <v>345</v>
+      </c>
+      <c r="B132" s="37" t="s">
+        <v>342</v>
+      </c>
+      <c r="C132" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="B132" s="39" t="s">
-        <v>343</v>
-      </c>
-      <c r="C132" s="6" t="s">
+      <c r="D132" s="6" t="s">
         <v>347</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>348</v>
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="27">
@@ -27944,7 +27928,7 @@
         <v>62</v>
       </c>
       <c r="H132" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I132" s="4">
         <v>1</v>
@@ -28083,7 +28067,7 @@
         <v>60</v>
       </c>
       <c r="BE132" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="BF132" s="11" t="s">
         <v>62</v>
@@ -28123,19 +28107,19 @@
       <c r="BY132" s="4"/>
       <c r="BZ132" s="4"/>
     </row>
-    <row r="133" spans="1:78" ht="98">
-      <c r="A133" s="39" t="s">
-        <v>350</v>
-      </c>
-      <c r="B133" s="39" t="s">
-        <v>350</v>
+    <row r="133" spans="1:78" ht="42.75">
+      <c r="A133" s="37" t="s">
+        <v>349</v>
+      </c>
+      <c r="B133" s="37" t="s">
+        <v>349</v>
       </c>
       <c r="C133" s="4"/>
       <c r="D133" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F133" s="4">
         <v>12</v>
@@ -28144,7 +28128,7 @@
         <v>62</v>
       </c>
       <c r="H133" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I133" s="4">
         <v>1</v>
@@ -28279,7 +28263,7 @@
         <v>60</v>
       </c>
       <c r="BE133" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="BF133" s="11" t="s">
         <v>62</v>
@@ -28319,15 +28303,15 @@
       <c r="BY133" s="4"/>
       <c r="BZ133" s="4"/>
     </row>
-    <row r="134" spans="1:78" ht="28">
+    <row r="134" spans="1:78" ht="28.5">
       <c r="A134" s="30"/>
-      <c r="B134" s="39" t="s">
-        <v>350</v>
+      <c r="B134" s="37" t="s">
+        <v>349</v>
       </c>
       <c r="C134" s="4"/>
       <c r="D134" s="21"/>
-      <c r="E134" s="39" t="s">
-        <v>321</v>
+      <c r="E134" s="37" t="s">
+        <v>320</v>
       </c>
       <c r="F134" s="27">
         <v>13</v>
@@ -28336,7 +28320,7 @@
         <v>62</v>
       </c>
       <c r="H134" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I134" s="4">
         <v>1</v>
@@ -28471,7 +28455,7 @@
         <v>60</v>
       </c>
       <c r="BE134" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="BF134" s="11" t="s">
         <v>62</v>
@@ -28511,16 +28495,16 @@
       <c r="BY134" s="4"/>
       <c r="BZ134" s="4"/>
     </row>
-    <row r="135" spans="1:78" ht="42">
+    <row r="135" spans="1:78" ht="42.75">
       <c r="A135" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="B135" s="39" t="s">
-        <v>354</v>
+        <v>353</v>
+      </c>
+      <c r="B135" s="37" t="s">
+        <v>353</v>
       </c>
       <c r="C135" s="21"/>
       <c r="D135" s="21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E135" s="4"/>
       <c r="F135" s="27">
@@ -28530,7 +28514,7 @@
         <v>62</v>
       </c>
       <c r="H135" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I135" s="4">
         <v>1</v>
@@ -28667,7 +28651,7 @@
         <v>60</v>
       </c>
       <c r="BE135" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="BF135" s="11" t="s">
         <v>62</v>
@@ -28707,18 +28691,18 @@
       <c r="BY135" s="4"/>
       <c r="BZ135" s="4"/>
     </row>
-    <row r="136" spans="1:78" ht="56">
+    <row r="136" spans="1:78" ht="57">
       <c r="A136" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B136" s="37" t="s">
         <v>357</v>
       </c>
-      <c r="B136" s="39" t="s">
+      <c r="C136" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="C136" s="21" t="s">
+      <c r="D136" s="21" t="s">
         <v>359</v>
-      </c>
-      <c r="D136" s="21" t="s">
-        <v>360</v>
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="27">
@@ -28728,7 +28712,7 @@
         <v>62</v>
       </c>
       <c r="H136" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I136" s="4">
         <v>1</v>
@@ -28863,7 +28847,7 @@
         <v>60</v>
       </c>
       <c r="BE136" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="BF136" s="11" t="s">
         <v>62</v>
@@ -28903,19 +28887,19 @@
       <c r="BY136" s="4"/>
       <c r="BZ136" s="4"/>
     </row>
-    <row r="137" spans="1:78" ht="42">
+    <row r="137" spans="1:78" ht="28.5">
       <c r="A137" s="30" t="s">
-        <v>362</v>
-      </c>
-      <c r="B137" s="39" t="s">
-        <v>362</v>
+        <v>361</v>
+      </c>
+      <c r="B137" s="37" t="s">
+        <v>361</v>
       </c>
       <c r="C137" s="4"/>
       <c r="D137" s="21" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F137" s="27">
         <v>16</v>
@@ -28924,7 +28908,7 @@
         <v>62</v>
       </c>
       <c r="H137" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I137" s="4">
         <v>1</v>
@@ -29060,8 +29044,8 @@
       <c r="BD137" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="BE137" s="52" t="s">
-        <v>364</v>
+      <c r="BE137" s="50" t="s">
+        <v>363</v>
       </c>
       <c r="BF137" s="11" t="s">
         <v>62</v>
@@ -29103,20 +29087,20 @@
     </row>
     <row r="138" spans="1:78">
       <c r="A138" s="30"/>
-      <c r="B138" s="39" t="s">
-        <v>362</v>
+      <c r="B138" s="37" t="s">
+        <v>361</v>
       </c>
       <c r="C138" s="4"/>
       <c r="D138" s="21"/>
-      <c r="E138" s="39" t="s">
-        <v>321</v>
+      <c r="E138" s="37" t="s">
+        <v>320</v>
       </c>
       <c r="F138" s="27">
         <v>17</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I138" s="4"/>
       <c r="J138" s="15"/>
@@ -29170,7 +29154,7 @@
       <c r="BB138" s="11"/>
       <c r="BC138" s="4"/>
       <c r="BD138" s="11"/>
-      <c r="BE138" s="52"/>
+      <c r="BE138" s="50"/>
       <c r="BF138" s="11" t="s">
         <v>62</v>
       </c>
@@ -29209,19 +29193,19 @@
       <c r="BY138" s="4"/>
       <c r="BZ138" s="4"/>
     </row>
-    <row r="139" spans="1:78" ht="56">
+    <row r="139" spans="1:78" ht="57">
       <c r="A139" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="B139" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="C139" s="51"/>
+      <c r="D139" s="21" t="s">
         <v>365</v>
       </c>
-      <c r="B139" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="C139" s="53"/>
-      <c r="D139" s="21" t="s">
+      <c r="E139" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="E139" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="F139" s="4">
         <v>18</v>
@@ -29230,7 +29214,7 @@
         <v>62</v>
       </c>
       <c r="H139" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I139" s="4">
         <v>1</v>
@@ -29369,7 +29353,7 @@
         <v>60</v>
       </c>
       <c r="BE139" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="BF139" s="11" t="s">
         <v>62</v>
@@ -29412,19 +29396,19 @@
     <row r="140" spans="1:78">
       <c r="A140" s="30"/>
       <c r="B140" s="30" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C140" s="4"/>
       <c r="D140" s="21"/>
-      <c r="E140" s="39" t="s">
-        <v>369</v>
+      <c r="E140" s="37" t="s">
+        <v>368</v>
       </c>
       <c r="F140" s="27">
         <v>19</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I140" s="4"/>
       <c r="J140" s="15"/>
@@ -29517,19 +29501,19 @@
       <c r="BY140" s="4"/>
       <c r="BZ140" s="4"/>
     </row>
-    <row r="141" spans="1:78" ht="112">
-      <c r="A141" s="33" t="s">
-        <v>370</v>
+    <row r="141" spans="1:78" ht="114">
+      <c r="A141" s="32" t="s">
+        <v>369</v>
       </c>
       <c r="B141" s="30" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C141" s="4"/>
       <c r="D141" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="E141" s="4" t="s">
         <v>371</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>372</v>
       </c>
       <c r="F141" s="27">
         <v>20</v>
@@ -29538,7 +29522,7 @@
         <v>62</v>
       </c>
       <c r="H141" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I141" s="4">
         <v>1</v>
@@ -29673,7 +29657,7 @@
         <v>60</v>
       </c>
       <c r="BE141" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="BF141" s="11" t="s">
         <v>62</v>
@@ -29716,19 +29700,19 @@
     <row r="142" spans="1:78">
       <c r="A142" s="30"/>
       <c r="B142" s="30" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C142" s="4"/>
       <c r="D142" s="21"/>
       <c r="E142" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F142" s="27">
         <v>21</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I142" s="4"/>
       <c r="J142" s="15"/>
@@ -29821,19 +29805,19 @@
       <c r="BY142" s="4"/>
       <c r="BZ142" s="4"/>
     </row>
-    <row r="143" spans="1:78" ht="84">
+    <row r="143" spans="1:78" ht="28.5">
       <c r="A143" s="30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B143" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="C143" s="48"/>
-      <c r="D143" s="21" t="s">
-        <v>376</v>
+        <v>374</v>
+      </c>
+      <c r="C143" s="46"/>
+      <c r="D143" s="4" t="s">
+        <v>486</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F143" s="27">
         <v>22</v>
@@ -29842,7 +29826,7 @@
         <v>62</v>
       </c>
       <c r="H143" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I143" s="4">
         <v>1</v>
@@ -29981,7 +29965,7 @@
         <v>60</v>
       </c>
       <c r="BE143" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="BF143" s="11" t="s">
         <v>62</v>
@@ -30024,12 +30008,12 @@
     <row r="144" spans="1:78">
       <c r="A144" s="30"/>
       <c r="B144" s="30" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C144" s="4"/>
       <c r="D144" s="21"/>
-      <c r="E144" s="39" t="s">
-        <v>369</v>
+      <c r="E144" s="37" t="s">
+        <v>368</v>
       </c>
       <c r="F144" s="27">
         <v>23</v>
@@ -30038,7 +30022,7 @@
         <v>62</v>
       </c>
       <c r="H144" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I144" s="4"/>
       <c r="J144" s="15" t="s">
@@ -30155,16 +30139,16 @@
       <c r="BY144" s="4"/>
       <c r="BZ144" s="4"/>
     </row>
-    <row r="145" spans="1:78" ht="28">
+    <row r="145" spans="1:78" ht="28.5">
       <c r="A145" s="30" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B145" s="30" t="s">
-        <v>378</v>
-      </c>
-      <c r="C145" s="48"/>
+        <v>376</v>
+      </c>
+      <c r="C145" s="46"/>
       <c r="D145" s="21" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E145" s="4"/>
       <c r="F145" s="27">
@@ -30174,7 +30158,7 @@
         <v>62</v>
       </c>
       <c r="H145" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I145" s="4">
         <v>1</v>
@@ -30309,7 +30293,7 @@
         <v>60</v>
       </c>
       <c r="BE145" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="BF145" s="11" t="s">
         <v>62</v>
@@ -30349,16 +30333,16 @@
       <c r="BY145" s="4"/>
       <c r="BZ145" s="4"/>
     </row>
-    <row r="146" spans="1:78" ht="56">
+    <row r="146" spans="1:78" ht="71.25">
       <c r="A146" s="30" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B146" s="30" t="s">
-        <v>381</v>
-      </c>
-      <c r="C146" s="48"/>
+        <v>379</v>
+      </c>
+      <c r="C146" s="46"/>
       <c r="D146" s="21" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="27">
@@ -30368,7 +30352,7 @@
         <v>62</v>
       </c>
       <c r="H146" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I146" s="4">
         <v>1</v>
@@ -30507,7 +30491,7 @@
         <v>60</v>
       </c>
       <c r="BE146" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BF146" s="11" t="s">
         <v>62</v>
@@ -30547,19 +30531,19 @@
       <c r="BY146" s="4"/>
       <c r="BZ146" s="4"/>
     </row>
-    <row r="147" spans="1:78" ht="28">
+    <row r="147" spans="1:78" ht="28.5">
       <c r="A147" s="30" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B147" s="30" t="s">
-        <v>384</v>
-      </c>
-      <c r="C147" s="48"/>
+        <v>382</v>
+      </c>
+      <c r="C147" s="46"/>
       <c r="D147" s="21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F147" s="27">
         <v>26</v>
@@ -30568,7 +30552,7 @@
         <v>62</v>
       </c>
       <c r="H147" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I147" s="4">
         <v>1</v>
@@ -30705,7 +30689,7 @@
         <v>60</v>
       </c>
       <c r="BE147" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="BF147" s="11" t="s">
         <v>62</v>
@@ -30748,19 +30732,19 @@
     <row r="148" spans="1:78">
       <c r="A148" s="30"/>
       <c r="B148" s="30" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C148" s="30"/>
       <c r="D148" s="4"/>
-      <c r="E148" s="39" t="s">
-        <v>369</v>
+      <c r="E148" s="37" t="s">
+        <v>368</v>
       </c>
       <c r="F148" s="27"/>
       <c r="G148" s="4" t="s">
         <v>60</v>
       </c>
       <c r="H148" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="I148" s="4">
         <v>1</v>
@@ -30919,16 +30903,16 @@
       <c r="BY148" s="4"/>
       <c r="BZ148" s="4"/>
     </row>
-    <row r="149" spans="1:78" ht="56">
+    <row r="149" spans="1:78" ht="57">
       <c r="A149" s="30" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B149" s="30" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C149" s="30"/>
       <c r="D149" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E149" s="4"/>
       <c r="F149" s="18">
@@ -30938,7 +30922,7 @@
         <v>62</v>
       </c>
       <c r="H149" s="16" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I149" s="4">
         <v>1</v>
@@ -31116,25 +31100,25 @@
         <v>1.5</v>
       </c>
       <c r="BX149" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="BY149" s="4">
         <v>5</v>
       </c>
       <c r="BZ149" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
-    <row r="150" spans="1:78" ht="98">
+    <row r="150" spans="1:78" ht="99.75">
       <c r="A150" s="30" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B150" s="30" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C150" s="30"/>
       <c r="D150" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E150" s="4"/>
       <c r="F150" s="18">
@@ -31144,7 +31128,7 @@
         <v>62</v>
       </c>
       <c r="H150" s="18" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I150" s="4">
         <v>1</v>
@@ -31156,7 +31140,7 @@
         <v>1.6</v>
       </c>
       <c r="L150" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M150" s="4" t="s">
         <v>121</v>
@@ -31324,25 +31308,25 @@
         <v>0.6</v>
       </c>
       <c r="BX150" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="BY150" s="4">
         <v>5</v>
       </c>
       <c r="BZ150" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
-    <row r="151" spans="1:78" ht="56">
+    <row r="151" spans="1:78" ht="57">
       <c r="A151" s="30" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B151" s="30" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C151" s="30"/>
       <c r="D151" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="18">
@@ -31352,7 +31336,7 @@
         <v>62</v>
       </c>
       <c r="H151" s="18" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I151" s="4">
         <v>1</v>
@@ -31530,25 +31514,25 @@
         <v>0.5</v>
       </c>
       <c r="BX151" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="BY151" s="4">
         <v>5</v>
       </c>
       <c r="BZ151" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
-    <row r="152" spans="1:78" ht="42">
+    <row r="152" spans="1:78" ht="42.75">
       <c r="A152" s="30" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B152" s="30" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C152" s="30"/>
       <c r="D152" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E152" s="4"/>
       <c r="F152" s="18">
@@ -31558,7 +31542,7 @@
         <v>62</v>
       </c>
       <c r="H152" s="18" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I152" s="4">
         <v>1</v>
@@ -31570,7 +31554,7 @@
         <v>4</v>
       </c>
       <c r="L152" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M152" s="4" t="s">
         <v>121</v>
@@ -31738,25 +31722,25 @@
         <v>0.4</v>
       </c>
       <c r="BX152" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="BY152" s="4">
         <v>5</v>
       </c>
       <c r="BZ152" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
-    <row r="153" spans="1:78" ht="28">
+    <row r="153" spans="1:78" ht="28.5">
       <c r="A153" s="30" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B153" s="30" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C153" s="30"/>
       <c r="D153" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="18">
@@ -31766,7 +31750,7 @@
         <v>62</v>
       </c>
       <c r="H153" s="18" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I153" s="4">
         <v>1</v>
@@ -31944,35 +31928,35 @@
         <v>1</v>
       </c>
       <c r="BX153" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="BY153" s="4">
         <v>5</v>
       </c>
       <c r="BZ153" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
-    <row r="154" spans="1:78" ht="42">
+    <row r="154" spans="1:78" ht="42.75">
       <c r="A154" s="9" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C154" s="9"/>
       <c r="D154" s="9" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E154" s="4"/>
-      <c r="F154" s="39">
+      <c r="F154" s="37">
         <v>0</v>
       </c>
       <c r="G154" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H154" s="54" t="s">
-        <v>407</v>
+      <c r="H154" s="52" t="s">
+        <v>405</v>
       </c>
       <c r="I154" s="9">
         <v>1</v>
@@ -32147,26 +32131,26 @@
       <c r="BY154" s="4"/>
       <c r="BZ154" s="4"/>
     </row>
-    <row r="155" spans="1:78" ht="70">
+    <row r="155" spans="1:78" ht="71.25">
       <c r="A155" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C155" s="4"/>
       <c r="D155" s="4" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E155" s="4"/>
-      <c r="F155" s="39">
+      <c r="F155" s="37">
         <v>1</v>
       </c>
       <c r="G155" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H155" s="39" t="s">
-        <v>407</v>
+      <c r="H155" s="37" t="s">
+        <v>405</v>
       </c>
       <c r="I155" s="4">
         <v>10</v>
@@ -32341,26 +32325,26 @@
       <c r="BY155" s="4"/>
       <c r="BZ155" s="4"/>
     </row>
-    <row r="156" spans="1:78" ht="70">
+    <row r="156" spans="1:78" ht="42.75">
       <c r="A156" s="9" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C156" s="9"/>
       <c r="D156" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E156" s="4"/>
-      <c r="F156" s="39">
+      <c r="F156" s="37">
         <v>2</v>
       </c>
       <c r="G156" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H156" s="54" t="s">
-        <v>407</v>
+      <c r="H156" s="52" t="s">
+        <v>405</v>
       </c>
       <c r="I156" s="4">
         <v>5</v>
@@ -32535,28 +32519,28 @@
       <c r="BY156" s="4"/>
       <c r="BZ156" s="4"/>
     </row>
-    <row r="157" spans="1:78" ht="56">
+    <row r="157" spans="1:78" ht="57">
       <c r="A157" s="9" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E157" s="4"/>
-      <c r="F157" s="39">
+      <c r="F157" s="37">
         <v>3</v>
       </c>
       <c r="G157" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H157" s="54" t="s">
-        <v>407</v>
+      <c r="H157" s="52" t="s">
+        <v>405</v>
       </c>
       <c r="I157" s="4">
         <v>1</v>
@@ -32731,22 +32715,22 @@
       <c r="BY157" s="4"/>
       <c r="BZ157" s="4"/>
     </row>
-    <row r="158" spans="1:78" ht="56">
-      <c r="A158" s="55"/>
+    <row r="158" spans="1:78" ht="57">
+      <c r="A158" s="53"/>
       <c r="B158" s="13" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E158" s="4"/>
-      <c r="F158" s="39">
+      <c r="F158" s="37">
         <v>4</v>
       </c>
       <c r="G158" s="4"/>
-      <c r="H158" s="54" t="s">
-        <v>407</v>
+      <c r="H158" s="52" t="s">
+        <v>405</v>
       </c>
       <c r="I158" s="4">
         <v>1</v>
@@ -32921,89 +32905,89 @@
     </row>
     <row r="159" spans="1:78">
       <c r="A159" s="9"/>
-      <c r="B159" s="56"/>
-      <c r="C159" s="56"/>
-      <c r="D159" s="57"/>
-      <c r="E159" s="58"/>
-      <c r="F159" s="59"/>
-      <c r="G159" s="58"/>
-      <c r="H159" s="60"/>
-      <c r="J159" s="62"/>
-      <c r="L159" s="63"/>
-      <c r="M159" s="58"/>
-      <c r="N159" s="62"/>
-      <c r="P159" s="62"/>
-      <c r="R159" s="62"/>
-      <c r="T159" s="62"/>
-      <c r="V159" s="62"/>
-      <c r="W159" s="63"/>
-      <c r="X159" s="63"/>
-      <c r="Y159" s="63"/>
-      <c r="Z159" s="63"/>
-      <c r="AB159" s="64"/>
-      <c r="AC159" s="63"/>
-      <c r="AG159" s="63"/>
-      <c r="AQ159" s="63"/>
-      <c r="AU159" s="63"/>
-      <c r="AY159" s="65"/>
-      <c r="AZ159" s="65"/>
-      <c r="BA159" s="65"/>
-      <c r="BB159" s="65"/>
-      <c r="BD159" s="65"/>
-      <c r="BF159" s="65"/>
-      <c r="BK159" s="65"/>
-      <c r="BM159" s="66"/>
-      <c r="BQ159" s="65"/>
-      <c r="BR159" s="67"/>
-      <c r="BT159" s="61"/>
-      <c r="BU159" s="61"/>
-      <c r="BV159" s="68"/>
-      <c r="BW159" s="69"/>
-      <c r="BX159" s="70"/>
-      <c r="BY159" s="70"/>
+      <c r="B159" s="54"/>
+      <c r="C159" s="54"/>
+      <c r="D159" s="55"/>
+      <c r="E159" s="56"/>
+      <c r="F159" s="57"/>
+      <c r="G159" s="56"/>
+      <c r="H159" s="58"/>
+      <c r="J159" s="60"/>
+      <c r="L159" s="61"/>
+      <c r="M159" s="56"/>
+      <c r="N159" s="60"/>
+      <c r="P159" s="60"/>
+      <c r="R159" s="60"/>
+      <c r="T159" s="60"/>
+      <c r="V159" s="60"/>
+      <c r="W159" s="61"/>
+      <c r="X159" s="61"/>
+      <c r="Y159" s="61"/>
+      <c r="Z159" s="61"/>
+      <c r="AB159" s="62"/>
+      <c r="AC159" s="61"/>
+      <c r="AG159" s="61"/>
+      <c r="AQ159" s="61"/>
+      <c r="AU159" s="61"/>
+      <c r="AY159" s="63"/>
+      <c r="AZ159" s="63"/>
+      <c r="BA159" s="63"/>
+      <c r="BB159" s="63"/>
+      <c r="BD159" s="63"/>
+      <c r="BF159" s="63"/>
+      <c r="BK159" s="63"/>
+      <c r="BM159" s="64"/>
+      <c r="BQ159" s="63"/>
+      <c r="BR159" s="65"/>
+      <c r="BT159" s="59"/>
+      <c r="BU159" s="59"/>
+      <c r="BV159" s="66"/>
+      <c r="BW159" s="67"/>
+      <c r="BX159" s="68"/>
+      <c r="BY159" s="68"/>
     </row>
     <row r="160" spans="1:78">
       <c r="A160" s="9"/>
-      <c r="B160" s="56"/>
-      <c r="C160" s="56"/>
-      <c r="D160" s="57"/>
-      <c r="E160" s="58"/>
-      <c r="F160" s="59"/>
-      <c r="G160" s="58"/>
-      <c r="H160" s="60"/>
-      <c r="J160" s="62"/>
-      <c r="L160" s="63"/>
-      <c r="M160" s="58"/>
-      <c r="N160" s="62"/>
-      <c r="P160" s="62"/>
-      <c r="R160" s="62"/>
-      <c r="T160" s="62"/>
-      <c r="V160" s="62"/>
-      <c r="W160" s="63"/>
-      <c r="X160" s="63"/>
-      <c r="Y160" s="63"/>
-      <c r="Z160" s="63"/>
-      <c r="AB160" s="64"/>
-      <c r="AC160" s="63"/>
-      <c r="AG160" s="63"/>
-      <c r="AQ160" s="63"/>
-      <c r="AU160" s="63"/>
-      <c r="AY160" s="65"/>
-      <c r="AZ160" s="65"/>
-      <c r="BA160" s="65"/>
-      <c r="BB160" s="65"/>
-      <c r="BD160" s="65"/>
-      <c r="BF160" s="65"/>
-      <c r="BK160" s="65"/>
-      <c r="BM160" s="66"/>
-      <c r="BQ160" s="65"/>
-      <c r="BR160" s="67"/>
-      <c r="BT160" s="61"/>
-      <c r="BU160" s="61"/>
-      <c r="BV160" s="68"/>
-      <c r="BW160" s="69"/>
-      <c r="BX160" s="70"/>
-      <c r="BY160" s="70"/>
+      <c r="B160" s="54"/>
+      <c r="C160" s="54"/>
+      <c r="D160" s="55"/>
+      <c r="E160" s="56"/>
+      <c r="F160" s="57"/>
+      <c r="G160" s="56"/>
+      <c r="H160" s="58"/>
+      <c r="J160" s="60"/>
+      <c r="L160" s="61"/>
+      <c r="M160" s="56"/>
+      <c r="N160" s="60"/>
+      <c r="P160" s="60"/>
+      <c r="R160" s="60"/>
+      <c r="T160" s="60"/>
+      <c r="V160" s="60"/>
+      <c r="W160" s="61"/>
+      <c r="X160" s="61"/>
+      <c r="Y160" s="61"/>
+      <c r="Z160" s="61"/>
+      <c r="AB160" s="62"/>
+      <c r="AC160" s="61"/>
+      <c r="AG160" s="61"/>
+      <c r="AQ160" s="61"/>
+      <c r="AU160" s="61"/>
+      <c r="AY160" s="63"/>
+      <c r="AZ160" s="63"/>
+      <c r="BA160" s="63"/>
+      <c r="BB160" s="63"/>
+      <c r="BD160" s="63"/>
+      <c r="BF160" s="63"/>
+      <c r="BK160" s="63"/>
+      <c r="BM160" s="64"/>
+      <c r="BQ160" s="63"/>
+      <c r="BR160" s="65"/>
+      <c r="BT160" s="59"/>
+      <c r="BU160" s="59"/>
+      <c r="BV160" s="66"/>
+      <c r="BW160" s="67"/>
+      <c r="BX160" s="68"/>
+      <c r="BY160" s="68"/>
     </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
